--- a/jogos_2026-05-24.xlsx
+++ b/jogos_2026-05-24.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>5.57</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>7.02</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>5.57</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>7.02</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>4.54</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>1.55</v>
+        <v>2.54</v>
       </c>
       <c r="Q61" t="n">
-        <v>4.54</v>
+        <v>3.62</v>
       </c>
       <c r="R61" t="n">
-        <v>6.7</v>
+        <v>2.89</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,22 +13361,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19315,7 +19315,7 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P96" t="n">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19709,7 +19709,7 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P98" t="n">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q100" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q103" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20743,10 +20743,10 @@
         <v>0</v>
       </c>
       <c r="AE103" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF103" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG103" t="n">
         <v>0</v>
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>1.32</v>
+        <v>2.8</v>
       </c>
       <c r="Q104" t="n">
-        <v>5.45</v>
+        <v>3.27</v>
       </c>
       <c r="R104" t="n">
-        <v>9.949999999999999</v>
+        <v>2.64</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -20940,10 +20940,10 @@
         <v>0</v>
       </c>
       <c r="AE104" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF104" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG104" t="n">
         <v>0</v>
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q127" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R127" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q128" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R128" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27790,13 +27790,13 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q139" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R139" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q140" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R140" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>

--- a/jogos_2026-05-24.xlsx
+++ b/jogos_2026-05-24.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>5.57</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>7.02</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>5.57</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>7.02</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>7</v>
+        <v>1.55</v>
       </c>
       <c r="Q54" t="n">
-        <v>4.43</v>
+        <v>4.54</v>
       </c>
       <c r="R54" t="n">
-        <v>1.55</v>
+        <v>6.7</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>4.54</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,22 +13361,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19315,7 +19315,7 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P96" t="n">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19561,10 +19561,10 @@
         <v>0</v>
       </c>
       <c r="AE97" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF97" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG97" t="n">
         <v>0</v>
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20103,17 +20103,17 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P100" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>9.949999999999999</v>
+        <v>0</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -20940,10 +20940,10 @@
         <v>0</v>
       </c>
       <c r="AE104" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF104" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG104" t="n">
         <v>0</v>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q108" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="R108" t="n">
-        <v>0</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q127" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R127" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q128" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R128" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q138" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R138" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q140" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R140" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G142" t="n">

--- a/jogos_2026-05-24.xlsx
+++ b/jogos_2026-05-24.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>5.57</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>7.02</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.55</v>
+        <v>2.25</v>
       </c>
       <c r="Q54" t="n">
-        <v>4.54</v>
+        <v>3.73</v>
       </c>
       <c r="R54" t="n">
-        <v>6.7</v>
+        <v>3.31</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>5.57</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>7.02</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.54</v>
+        <v>1.55</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.62</v>
+        <v>4.54</v>
       </c>
       <c r="R61" t="n">
-        <v>2.89</v>
+        <v>6.7</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19561,10 +19561,10 @@
         <v>0</v>
       </c>
       <c r="AE97" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF97" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG97" t="n">
         <v>0</v>
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20103,7 +20103,7 @@
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P100" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q101" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Q108" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="R108" t="n">
-        <v>9.949999999999999</v>
+        <v>0</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q109" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="R109" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -21925,10 +21925,10 @@
         <v>0</v>
       </c>
       <c r="AE109" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF109" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG109" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G136" t="n">

--- a/jogos_2026-05-24.xlsx
+++ b/jogos_2026-05-24.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>5.57</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>7.02</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.25</v>
+        <v>2.54</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.73</v>
+        <v>3.62</v>
       </c>
       <c r="R54" t="n">
-        <v>3.31</v>
+        <v>2.89</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>5.57</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>7.02</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>4.54</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>4.54</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,22 +13361,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>9.949999999999999</v>
+        <v>0</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q104" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q106" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="R106" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21334,10 +21334,10 @@
         <v>0</v>
       </c>
       <c r="AE106" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF106" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG106" t="n">
         <v>0</v>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q109" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="R109" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -21925,10 +21925,10 @@
         <v>0</v>
       </c>
       <c r="AE109" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF109" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG109" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q127" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R127" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q128" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R128" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q138" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R138" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q140" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R140" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G142" t="n">

--- a/jogos_2026-05-24.xlsx
+++ b/jogos_2026-05-24.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>4.92</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6959,10 +6959,10 @@
         <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>5.41</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -8923,10 +8923,10 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>4.54</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>5.57</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>7.02</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>5.57</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>7.02</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>4.54</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>5.37</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13460,10 +13460,10 @@
         <v>0</v>
       </c>
       <c r="AG66" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH66" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI66" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q101" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20349,10 +20349,10 @@
         <v>0</v>
       </c>
       <c r="AE101" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF101" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG101" t="n">
         <v>0</v>
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Q104" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>9.949999999999999</v>
+        <v>0</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q106" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="R106" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21334,10 +21334,10 @@
         <v>0</v>
       </c>
       <c r="AE106" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF106" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG106" t="n">
         <v>0</v>
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q108" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="R108" t="n">
-        <v>0</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Q124" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="R124" t="n">
-        <v>0</v>
+        <v>6.19</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24886,10 +24886,10 @@
         <v>0</v>
       </c>
       <c r="AG124" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH124" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI124" t="n">
         <v>0</v>
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q127" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R127" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q128" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R128" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Q132" t="n">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="R132" t="n">
-        <v>0</v>
+        <v>7.08</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26462,10 +26462,10 @@
         <v>0</v>
       </c>
       <c r="AG132" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH132" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI132" t="n">
         <v>0</v>
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q138" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R138" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q140" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R140" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28578,13 +28578,13 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q143" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="R143" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="S143" t="n">
         <v>0</v>
@@ -28623,10 +28623,10 @@
         <v>0</v>
       </c>
       <c r="AE143" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF143" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG143" t="n">
         <v>0</v>

--- a/jogos_2026-05-24.xlsx
+++ b/jogos_2026-05-24.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.29</v>
+        <v>1.97</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.95</v>
+        <v>3.18</v>
       </c>
       <c r="R9" t="n">
-        <v>8.199999999999999</v>
+        <v>3.61</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.97</v>
+        <v>1.29</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.18</v>
+        <v>4.95</v>
       </c>
       <c r="R10" t="n">
-        <v>3.61</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>5.14</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.92</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6959,10 +6959,10 @@
         <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>4.92</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7156,10 +7156,10 @@
         <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.63</v>
+        <v>1.28</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.96</v>
+        <v>5.41</v>
       </c>
       <c r="R35" t="n">
-        <v>4.85</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.95</v>
+        <v>1.63</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.53</v>
+        <v>3.96</v>
       </c>
       <c r="R40" t="n">
-        <v>2.2</v>
+        <v>4.85</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.53</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>5.41</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>8.039999999999999</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.66</v>
+        <v>3.6</v>
       </c>
       <c r="R43" t="n">
-        <v>2.13</v>
+        <v>2.6</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -8923,10 +8923,10 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.25</v>
+        <v>7</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.73</v>
+        <v>4.43</v>
       </c>
       <c r="R46" t="n">
-        <v>3.31</v>
+        <v>1.55</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>7</v>
+        <v>2.25</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.43</v>
+        <v>3.73</v>
       </c>
       <c r="R47" t="n">
-        <v>1.55</v>
+        <v>3.31</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>5.57</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>7.02</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>5.57</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>7.02</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>5.37</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12869,10 +12869,10 @@
         <v>0</v>
       </c>
       <c r="AG63" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH63" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI63" t="n">
         <v>0</v>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,22 +13361,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>5.37</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13460,10 +13460,10 @@
         <v>0</v>
       </c>
       <c r="AG66" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH66" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI66" t="n">
         <v>0</v>
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,22 +13952,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q99" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="R99" t="n">
-        <v>0</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20349,10 +20349,10 @@
         <v>0</v>
       </c>
       <c r="AE101" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF101" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG101" t="n">
         <v>0</v>
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>1.32</v>
+        <v>2.8</v>
       </c>
       <c r="Q108" t="n">
-        <v>5.45</v>
+        <v>3.27</v>
       </c>
       <c r="R108" t="n">
-        <v>9.949999999999999</v>
+        <v>2.64</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21728,10 +21728,10 @@
         <v>0</v>
       </c>
       <c r="AE108" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF108" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG108" t="n">
         <v>0</v>
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Q123" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="R123" t="n">
-        <v>0</v>
+        <v>6.19</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24689,10 +24689,10 @@
         <v>0</v>
       </c>
       <c r="AG123" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH123" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI123" t="n">
         <v>0</v>
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Q124" t="n">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="R124" t="n">
-        <v>6.19</v>
+        <v>0</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24886,10 +24886,10 @@
         <v>0</v>
       </c>
       <c r="AG124" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH124" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI124" t="n">
         <v>0</v>
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q127" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R127" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q128" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R128" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Q132" t="n">
-        <v>5.24</v>
+        <v>0</v>
       </c>
       <c r="R132" t="n">
-        <v>7.08</v>
+        <v>0</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26462,10 +26462,10 @@
         <v>0</v>
       </c>
       <c r="AG132" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH132" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI132" t="n">
         <v>0</v>
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Q136" t="n">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="R136" t="n">
-        <v>0</v>
+        <v>7.08</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27250,10 +27250,10 @@
         <v>0</v>
       </c>
       <c r="AG136" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH136" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI136" t="n">
         <v>0</v>
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G142" t="n">

--- a/jogos_2026-05-24.xlsx
+++ b/jogos_2026-05-24.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.57</v>
+        <v>2.54</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.1</v>
+        <v>3.42</v>
       </c>
       <c r="R22" t="n">
-        <v>5.14</v>
+        <v>2.59</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.28</v>
+        <v>2.95</v>
       </c>
       <c r="Q35" t="n">
-        <v>5.41</v>
+        <v>3.53</v>
       </c>
       <c r="R35" t="n">
-        <v>8.039999999999999</v>
+        <v>2.2</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7347,10 +7347,10 @@
         <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.66</v>
+        <v>3.6</v>
       </c>
       <c r="R39" t="n">
-        <v>2.13</v>
+        <v>2.6</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.63</v>
+        <v>1.42</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.96</v>
+        <v>4.58</v>
       </c>
       <c r="R40" t="n">
-        <v>4.85</v>
+        <v>6</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.95</v>
+        <v>1.33</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.53</v>
+        <v>5</v>
       </c>
       <c r="R41" t="n">
-        <v>2.2</v>
+        <v>6</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>5.41</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.3</v>
+        <v>1.63</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.6</v>
+        <v>3.96</v>
       </c>
       <c r="R43" t="n">
-        <v>2.6</v>
+        <v>4.85</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.33</v>
+        <v>3</v>
       </c>
       <c r="Q44" t="n">
-        <v>5</v>
+        <v>3.66</v>
       </c>
       <c r="R44" t="n">
-        <v>6</v>
+        <v>2.13</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>4.54</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.25</v>
+        <v>1.55</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.73</v>
+        <v>4.54</v>
       </c>
       <c r="R47" t="n">
-        <v>3.31</v>
+        <v>6.7</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>5.57</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>7.02</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>5.57</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>7.02</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,22 +13952,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>5.21</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Q99" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>9.949999999999999</v>
+        <v>0</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q102" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q104" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -20940,10 +20940,10 @@
         <v>0</v>
       </c>
       <c r="AE104" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF104" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG104" t="n">
         <v>0</v>
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q108" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="R108" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21728,10 +21728,10 @@
         <v>0</v>
       </c>
       <c r="AE108" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF108" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG108" t="n">
         <v>0</v>
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Q121" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="R121" t="n">
-        <v>0</v>
+        <v>6.19</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24295,10 +24295,10 @@
         <v>0</v>
       </c>
       <c r="AG121" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH121" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI121" t="n">
         <v>0</v>
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Q123" t="n">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>6.19</v>
+        <v>0</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24689,10 +24689,10 @@
         <v>0</v>
       </c>
       <c r="AG123" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH123" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI123" t="n">
         <v>0</v>
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Q135" t="n">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="R135" t="n">
-        <v>0</v>
+        <v>7.08</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -27053,10 +27053,10 @@
         <v>0</v>
       </c>
       <c r="AG135" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH135" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI135" t="n">
         <v>0</v>
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Q136" t="n">
-        <v>5.24</v>
+        <v>0</v>
       </c>
       <c r="R136" t="n">
-        <v>7.08</v>
+        <v>0</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27250,10 +27250,10 @@
         <v>0</v>
       </c>
       <c r="AG136" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH136" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI136" t="n">
         <v>0</v>

--- a/jogos_2026-05-24.xlsx
+++ b/jogos_2026-05-24.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.97</v>
+        <v>1.29</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.18</v>
+        <v>4.95</v>
       </c>
       <c r="R9" t="n">
-        <v>3.61</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.29</v>
+        <v>1.97</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.95</v>
+        <v>3.18</v>
       </c>
       <c r="R10" t="n">
-        <v>8.199999999999999</v>
+        <v>3.61</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>5.14</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>4.92</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6959,10 +6959,10 @@
         <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.92</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7156,10 +7156,10 @@
         <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7347,10 +7347,10 @@
         <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>5.41</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.93</v>
+        <v>1.63</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.99</v>
+        <v>3.96</v>
       </c>
       <c r="R38" t="n">
-        <v>3.22</v>
+        <v>4.85</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.3</v>
+        <v>1.33</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="R39" t="n">
-        <v>2.6</v>
+        <v>6</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.42</v>
+        <v>2.95</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.58</v>
+        <v>3.53</v>
       </c>
       <c r="R40" t="n">
-        <v>6</v>
+        <v>2.2</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.33</v>
+        <v>3</v>
       </c>
       <c r="Q41" t="n">
-        <v>5</v>
+        <v>3.66</v>
       </c>
       <c r="R41" t="n">
-        <v>6</v>
+        <v>2.13</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q42" t="n">
-        <v>5.41</v>
+        <v>3.6</v>
       </c>
       <c r="R42" t="n">
-        <v>8.039999999999999</v>
+        <v>2.6</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.63</v>
+        <v>1.93</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.96</v>
+        <v>3.99</v>
       </c>
       <c r="R43" t="n">
-        <v>4.85</v>
+        <v>3.22</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>3</v>
+        <v>1.42</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.66</v>
+        <v>4.58</v>
       </c>
       <c r="R44" t="n">
-        <v>2.13</v>
+        <v>6</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>4.54</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.54</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>5.57</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>7.02</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>7</v>
+        <v>2.25</v>
       </c>
       <c r="Q61" t="n">
-        <v>4.43</v>
+        <v>3.73</v>
       </c>
       <c r="R61" t="n">
-        <v>1.55</v>
+        <v>3.31</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>2.25</v>
+        <v>1.44</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.73</v>
+        <v>5.57</v>
       </c>
       <c r="R62" t="n">
-        <v>3.31</v>
+        <v>7.02</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>5.37</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12869,10 +12869,10 @@
         <v>0</v>
       </c>
       <c r="AG63" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH63" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI63" t="n">
         <v>0</v>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,22 +13361,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>5.37</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13460,10 +13460,10 @@
         <v>0</v>
       </c>
       <c r="AG66" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH66" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI66" t="n">
         <v>0</v>
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,22 +13952,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>1.32</v>
+        <v>2.8</v>
       </c>
       <c r="Q102" t="n">
-        <v>5.45</v>
+        <v>3.27</v>
       </c>
       <c r="R102" t="n">
-        <v>9.949999999999999</v>
+        <v>2.64</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20546,10 +20546,10 @@
         <v>0</v>
       </c>
       <c r="AE102" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF102" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG102" t="n">
         <v>0</v>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -20940,10 +20940,10 @@
         <v>0</v>
       </c>
       <c r="AE104" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF104" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG104" t="n">
         <v>0</v>
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q105" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="R105" t="n">
-        <v>0</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Q121" t="n">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="R121" t="n">
-        <v>6.19</v>
+        <v>0</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24295,10 +24295,10 @@
         <v>0</v>
       </c>
       <c r="AG121" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH121" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI121" t="n">
         <v>0</v>
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Q122" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="R122" t="n">
-        <v>0</v>
+        <v>6.19</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24492,10 +24492,10 @@
         <v>0</v>
       </c>
       <c r="AG122" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH122" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI122" t="n">
         <v>0</v>
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q127" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R127" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q128" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R128" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q138" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R138" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q140" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R140" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>

--- a/jogos_2026-05-24.xlsx
+++ b/jogos_2026-05-24.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="R23" t="n">
-        <v>5.14</v>
+        <v>3.8</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.92</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6959,10 +6959,10 @@
         <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>4.92</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7156,10 +7156,10 @@
         <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.28</v>
+        <v>1.93</v>
       </c>
       <c r="Q36" t="n">
-        <v>5.41</v>
+        <v>3.99</v>
       </c>
       <c r="R36" t="n">
-        <v>8.039999999999999</v>
+        <v>3.22</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.63</v>
+        <v>3</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.96</v>
+        <v>3.66</v>
       </c>
       <c r="R38" t="n">
-        <v>4.85</v>
+        <v>2.13</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -7938,10 +7938,10 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Q39" t="n">
-        <v>5</v>
+        <v>5.41</v>
       </c>
       <c r="R39" t="n">
-        <v>6</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.66</v>
+        <v>3.6</v>
       </c>
       <c r="R41" t="n">
-        <v>2.13</v>
+        <v>2.6</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.3</v>
+        <v>2.95</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.6</v>
+        <v>3.53</v>
       </c>
       <c r="R42" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.93</v>
+        <v>1.63</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.99</v>
+        <v>3.96</v>
       </c>
       <c r="R43" t="n">
-        <v>3.22</v>
+        <v>4.85</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,10 +9075,10 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="Q44" t="n">
-        <v>4.58</v>
+        <v>5</v>
       </c>
       <c r="R44" t="n">
         <v>6</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.54</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>4.54</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>7</v>
+        <v>3.82</v>
       </c>
       <c r="Q56" t="n">
-        <v>4.43</v>
+        <v>3.82</v>
       </c>
       <c r="R56" t="n">
-        <v>1.55</v>
+        <v>2.03</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.25</v>
+        <v>1.44</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.73</v>
+        <v>5.57</v>
       </c>
       <c r="R61" t="n">
-        <v>3.31</v>
+        <v>7.02</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1.44</v>
+        <v>7</v>
       </c>
       <c r="Q62" t="n">
-        <v>5.57</v>
+        <v>4.43</v>
       </c>
       <c r="R62" t="n">
-        <v>7.02</v>
+        <v>1.55</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,22 +13361,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>5.37</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13460,10 +13460,10 @@
         <v>0</v>
       </c>
       <c r="AG66" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH66" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI66" t="n">
         <v>0</v>
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>5.37</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13657,10 +13657,10 @@
         <v>0</v>
       </c>
       <c r="AG67" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH67" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI67" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14439,10 +14439,10 @@
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF71" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF72" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15036,10 +15036,10 @@
         <v>0</v>
       </c>
       <c r="AG74" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH74" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AI74" t="n">
         <v>0</v>
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>5.41</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>6.22</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17000,10 +17000,10 @@
         <v>0</v>
       </c>
       <c r="AE84" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF84" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG84" t="n">
         <v>0</v>
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>5.21</v>
+        <v>0</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>5.21</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q103" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>1.32</v>
+        <v>1.77</v>
       </c>
       <c r="Q105" t="n">
-        <v>5.45</v>
+        <v>3.32</v>
       </c>
       <c r="R105" t="n">
-        <v>9.949999999999999</v>
+        <v>4.83</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21137,10 +21137,10 @@
         <v>0</v>
       </c>
       <c r="AE105" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AF105" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG105" t="n">
         <v>0</v>
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q119" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R119" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q121" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R121" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Q122" t="n">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="R122" t="n">
-        <v>6.19</v>
+        <v>0</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24492,10 +24492,10 @@
         <v>0</v>
       </c>
       <c r="AG122" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH122" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI122" t="n">
         <v>0</v>
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Q124" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="R124" t="n">
-        <v>0</v>
+        <v>6.19</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24886,10 +24886,10 @@
         <v>0</v>
       </c>
       <c r="AG124" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH124" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI124" t="n">
         <v>0</v>
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q127" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R127" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="Q128" t="n">
-        <v>3.38</v>
+        <v>3.32</v>
       </c>
       <c r="R128" t="n">
-        <v>4.32</v>
+        <v>3.49</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25668,10 +25668,10 @@
         <v>0</v>
       </c>
       <c r="AE128" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF128" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG128" t="n">
         <v>0</v>
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Q134" t="n">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="R134" t="n">
-        <v>0</v>
+        <v>7.08</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -26856,10 +26856,10 @@
         <v>0</v>
       </c>
       <c r="AG134" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH134" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI134" t="n">
         <v>0</v>
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Q135" t="n">
-        <v>5.24</v>
+        <v>0</v>
       </c>
       <c r="R135" t="n">
-        <v>7.08</v>
+        <v>0</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -27053,10 +27053,10 @@
         <v>0</v>
       </c>
       <c r="AG135" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH135" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI135" t="n">
         <v>0</v>
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27396,13 +27396,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q137" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R137" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27790,13 +27790,13 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q139" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R139" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -27835,10 +27835,10 @@
         <v>0</v>
       </c>
       <c r="AE139" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF139" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG139" t="n">
         <v>0</v>

--- a/jogos_2026-05-24.xlsx
+++ b/jogos_2026-05-24.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.29</v>
+        <v>1.97</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.95</v>
+        <v>3.18</v>
       </c>
       <c r="R9" t="n">
-        <v>8.199999999999999</v>
+        <v>3.61</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.97</v>
+        <v>1.29</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.18</v>
+        <v>4.95</v>
       </c>
       <c r="R10" t="n">
-        <v>3.61</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>5.14</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>4.92</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6762,10 +6762,10 @@
         <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.92</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7156,10 +7156,10 @@
         <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.93</v>
+        <v>1.42</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.99</v>
+        <v>4.58</v>
       </c>
       <c r="R36" t="n">
-        <v>3.22</v>
+        <v>6</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.42</v>
+        <v>2.3</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.58</v>
+        <v>3.6</v>
       </c>
       <c r="R37" t="n">
-        <v>6</v>
+        <v>2.6</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>5.41</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>8.039999999999999</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.3</v>
+        <v>1.33</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="R41" t="n">
-        <v>2.6</v>
+        <v>6</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Q44" t="n">
-        <v>5</v>
+        <v>5.41</v>
       </c>
       <c r="R44" t="n">
-        <v>6</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="R45" t="n">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>4.54</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>4.54</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>5.57</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>7.02</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>5.57</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>7.02</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>5.37</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13263,10 +13263,10 @@
         <v>0</v>
       </c>
       <c r="AG65" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH65" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI65" t="n">
         <v>0</v>
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>5.37</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13657,10 +13657,10 @@
         <v>0</v>
       </c>
       <c r="AG67" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH67" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI67" t="n">
         <v>0</v>
@@ -13952,22 +13952,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14439,10 +14439,10 @@
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF71" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>5.25</v>
+        <v>3.77</v>
       </c>
       <c r="Q72" t="n">
-        <v>4.22</v>
+        <v>4.17</v>
       </c>
       <c r="R72" t="n">
-        <v>1.63</v>
+        <v>1.86</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF72" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>4.06</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1.7</v>
+        <v>2.59</v>
       </c>
       <c r="Q74" t="n">
-        <v>4.53</v>
+        <v>3.42</v>
       </c>
       <c r="R74" t="n">
-        <v>4.32</v>
+        <v>2.75</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15036,10 +15036,10 @@
         <v>0</v>
       </c>
       <c r="AG74" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH74" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AI74" t="n">
         <v>0</v>
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>2.59</v>
+        <v>1.52</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.42</v>
+        <v>4.46</v>
       </c>
       <c r="R75" t="n">
-        <v>2.75</v>
+        <v>6.22</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF75" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1.67</v>
+        <v>3.19</v>
       </c>
       <c r="Q77" t="n">
-        <v>4.17</v>
+        <v>3.19</v>
       </c>
       <c r="R77" t="n">
-        <v>4.94</v>
+        <v>2.41</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>1.59</v>
+        <v>1.96</v>
       </c>
       <c r="Q78" t="n">
-        <v>4.37</v>
+        <v>3.81</v>
       </c>
       <c r="R78" t="n">
-        <v>5.41</v>
+        <v>3.73</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15818,10 +15818,10 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF78" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG78" t="n">
         <v>0</v>
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF80" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="Q82" t="n">
-        <v>4.06</v>
+        <v>4.53</v>
       </c>
       <c r="R82" t="n">
-        <v>4.06</v>
+        <v>4.32</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16612,10 +16612,10 @@
         <v>0</v>
       </c>
       <c r="AG82" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH82" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AI82" t="n">
         <v>0</v>
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>4.46</v>
+        <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>6.22</v>
+        <v>0</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17000,10 +17000,10 @@
         <v>0</v>
       </c>
       <c r="AE84" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF84" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG84" t="n">
         <v>0</v>
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>3.77</v>
+        <v>1.59</v>
       </c>
       <c r="Q85" t="n">
-        <v>4.17</v>
+        <v>4.37</v>
       </c>
       <c r="R85" t="n">
-        <v>1.86</v>
+        <v>5.41</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q100" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20152,10 +20152,10 @@
         <v>0</v>
       </c>
       <c r="AE100" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AF100" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG100" t="n">
         <v>0</v>
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20546,10 +20546,10 @@
         <v>0</v>
       </c>
       <c r="AE102" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF102" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG102" t="n">
         <v>0</v>
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Q103" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>9.949999999999999</v>
+        <v>0</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20847,22 +20847,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q105" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R105" t="n">
-        <v>4.83</v>
+        <v>0</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21137,10 +21137,10 @@
         <v>0</v>
       </c>
       <c r="AE105" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AF105" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AG105" t="n">
         <v>0</v>
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q109" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="R109" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -21925,10 +21925,10 @@
         <v>0</v>
       </c>
       <c r="AE109" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF109" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG109" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q121" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="R121" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Q122" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="R122" t="n">
-        <v>0</v>
+        <v>6.19</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24492,10 +24492,10 @@
         <v>0</v>
       </c>
       <c r="AG122" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH122" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI122" t="n">
         <v>0</v>
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Q124" t="n">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="R124" t="n">
-        <v>6.19</v>
+        <v>0</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24886,10 +24886,10 @@
         <v>0</v>
       </c>
       <c r="AG124" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH124" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI124" t="n">
         <v>0</v>
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q125" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R125" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="Q127" t="n">
-        <v>3.38</v>
+        <v>3.32</v>
       </c>
       <c r="R127" t="n">
-        <v>4.32</v>
+        <v>3.49</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25471,10 +25471,10 @@
         <v>0</v>
       </c>
       <c r="AE127" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF127" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG127" t="n">
         <v>0</v>
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="Q128" t="n">
-        <v>3.32</v>
+        <v>3.38</v>
       </c>
       <c r="R128" t="n">
-        <v>3.49</v>
+        <v>4.32</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25668,10 +25668,10 @@
         <v>0</v>
       </c>
       <c r="AE128" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF128" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG128" t="n">
         <v>0</v>
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q138" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R138" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -27638,10 +27638,10 @@
         <v>0</v>
       </c>
       <c r="AE138" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF138" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG138" t="n">
         <v>0</v>
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27790,13 +27790,13 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="Q139" t="n">
-        <v>3.06</v>
+        <v>3.42</v>
       </c>
       <c r="R139" t="n">
-        <v>3.42</v>
+        <v>3.76</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -27835,10 +27835,10 @@
         <v>0</v>
       </c>
       <c r="AE139" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF139" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG139" t="n">
         <v>0</v>
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q140" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R140" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G142" t="n">

--- a/jogos_2026-05-24.xlsx
+++ b/jogos_2026-05-24.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.97</v>
+        <v>1.29</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.18</v>
+        <v>4.95</v>
       </c>
       <c r="R9" t="n">
-        <v>3.61</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.29</v>
+        <v>1.97</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.95</v>
+        <v>3.18</v>
       </c>
       <c r="R10" t="n">
-        <v>8.199999999999999</v>
+        <v>3.61</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>5.14</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.42</v>
+        <v>2.95</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.58</v>
+        <v>3.53</v>
       </c>
       <c r="R36" t="n">
-        <v>6</v>
+        <v>2.2</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.3</v>
+        <v>1.33</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="R37" t="n">
-        <v>2.6</v>
+        <v>6</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.66</v>
+        <v>3.6</v>
       </c>
       <c r="R38" t="n">
-        <v>2.13</v>
+        <v>2.6</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -7938,10 +7938,10 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Q41" t="n">
-        <v>5</v>
+        <v>5.41</v>
       </c>
       <c r="R41" t="n">
-        <v>6</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.95</v>
+        <v>1.42</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.53</v>
+        <v>4.58</v>
       </c>
       <c r="R42" t="n">
-        <v>2.2</v>
+        <v>6</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.28</v>
+        <v>1.63</v>
       </c>
       <c r="Q44" t="n">
-        <v>5.41</v>
+        <v>3.96</v>
       </c>
       <c r="R44" t="n">
-        <v>8.039999999999999</v>
+        <v>4.85</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>5.57</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>7.02</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.54</v>
+        <v>2.29</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.62</v>
+        <v>3.4</v>
       </c>
       <c r="R53" t="n">
-        <v>2.89</v>
+        <v>2.83</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>4.54</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.63</v>
+        <v>7</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.82</v>
+        <v>4.43</v>
       </c>
       <c r="R57" t="n">
-        <v>2.68</v>
+        <v>1.55</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF57" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1.55</v>
+        <v>2.52</v>
       </c>
       <c r="Q58" t="n">
-        <v>4.54</v>
+        <v>3.6</v>
       </c>
       <c r="R58" t="n">
-        <v>6.7</v>
+        <v>2.94</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>5.57</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>7.02</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.25</v>
+        <v>3.82</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.73</v>
+        <v>3.82</v>
       </c>
       <c r="R60" t="n">
-        <v>3.31</v>
+        <v>2.03</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12469,10 +12469,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF61" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>5.37</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13263,10 +13263,10 @@
         <v>0</v>
       </c>
       <c r="AG65" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH65" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI65" t="n">
         <v>0</v>
@@ -13361,22 +13361,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>5.37</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13460,10 +13460,10 @@
         <v>0</v>
       </c>
       <c r="AG66" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH66" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI66" t="n">
         <v>0</v>
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>5.41</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>3.77</v>
+        <v>1.77</v>
       </c>
       <c r="Q72" t="n">
-        <v>4.17</v>
+        <v>4.07</v>
       </c>
       <c r="R72" t="n">
-        <v>1.86</v>
+        <v>4.22</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>1.82</v>
+        <v>5.25</v>
       </c>
       <c r="Q73" t="n">
-        <v>4.06</v>
+        <v>4.22</v>
       </c>
       <c r="R73" t="n">
-        <v>4.06</v>
+        <v>1.63</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14833,10 +14833,10 @@
         <v>0</v>
       </c>
       <c r="AE73" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF73" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG73" t="n">
         <v>0</v>
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>1.52</v>
+        <v>1.82</v>
       </c>
       <c r="Q75" t="n">
-        <v>4.46</v>
+        <v>4.06</v>
       </c>
       <c r="R75" t="n">
-        <v>6.22</v>
+        <v>4.06</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF75" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>6.19</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>3.19</v>
+        <v>1.7</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.19</v>
+        <v>4.53</v>
       </c>
       <c r="R77" t="n">
-        <v>2.41</v>
+        <v>4.32</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15627,10 +15627,10 @@
         <v>0</v>
       </c>
       <c r="AG77" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH77" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AI77" t="n">
         <v>0</v>
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>1.96</v>
+        <v>2.59</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.81</v>
+        <v>3.42</v>
       </c>
       <c r="R78" t="n">
-        <v>3.73</v>
+        <v>2.75</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15818,10 +15818,10 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF78" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG78" t="n">
         <v>0</v>
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>5.25</v>
+        <v>1.52</v>
       </c>
       <c r="Q80" t="n">
-        <v>4.22</v>
+        <v>4.46</v>
       </c>
       <c r="R80" t="n">
-        <v>1.63</v>
+        <v>6.22</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AF80" t="n">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>4.15</v>
+        <v>3.19</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.73</v>
+        <v>3.19</v>
       </c>
       <c r="R81" t="n">
-        <v>1.88</v>
+        <v>2.41</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16612,10 +16612,10 @@
         <v>0</v>
       </c>
       <c r="AG82" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH82" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AI82" t="n">
         <v>0</v>
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>1.67</v>
+        <v>1.96</v>
       </c>
       <c r="Q83" t="n">
-        <v>4.17</v>
+        <v>3.81</v>
       </c>
       <c r="R83" t="n">
-        <v>4.94</v>
+        <v>3.73</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF83" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>5.88</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="Q85" t="n">
-        <v>4.37</v>
+        <v>4.17</v>
       </c>
       <c r="R85" t="n">
-        <v>5.41</v>
+        <v>4.94</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>1.32</v>
+        <v>1.77</v>
       </c>
       <c r="Q98" t="n">
-        <v>5.45</v>
+        <v>3.32</v>
       </c>
       <c r="R98" t="n">
-        <v>9.949999999999999</v>
+        <v>4.83</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19758,10 +19758,10 @@
         <v>0</v>
       </c>
       <c r="AE98" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AF98" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG98" t="n">
         <v>0</v>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>4.83</v>
+        <v>0</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20152,10 +20152,10 @@
         <v>0</v>
       </c>
       <c r="AE100" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AF100" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AG100" t="n">
         <v>0</v>
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q102" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q103" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20743,10 +20743,10 @@
         <v>0</v>
       </c>
       <c r="AE103" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF103" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG103" t="n">
         <v>0</v>
@@ -20847,22 +20847,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q109" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="R109" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -21925,10 +21925,10 @@
         <v>0</v>
       </c>
       <c r="AE109" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF109" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG109" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Q121" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="R121" t="n">
-        <v>0</v>
+        <v>6.19</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24295,10 +24295,10 @@
         <v>0</v>
       </c>
       <c r="AG121" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH121" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI121" t="n">
         <v>0</v>
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Q122" t="n">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="R122" t="n">
-        <v>6.19</v>
+        <v>0</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24492,10 +24492,10 @@
         <v>0</v>
       </c>
       <c r="AG122" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH122" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI122" t="n">
         <v>0</v>
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Q132" t="n">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="R132" t="n">
-        <v>0</v>
+        <v>7.08</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26462,10 +26462,10 @@
         <v>0</v>
       </c>
       <c r="AG132" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH132" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI132" t="n">
         <v>0</v>
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Q134" t="n">
-        <v>5.24</v>
+        <v>0</v>
       </c>
       <c r="R134" t="n">
-        <v>7.08</v>
+        <v>0</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -26856,10 +26856,10 @@
         <v>0</v>
       </c>
       <c r="AG134" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH134" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI134" t="n">
         <v>0</v>
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q138" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="R138" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -27638,10 +27638,10 @@
         <v>0</v>
       </c>
       <c r="AE138" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF138" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG138" t="n">
         <v>0</v>
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27790,14 +27790,14 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="Q139" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="R139" t="n">
         <v>3.42</v>
       </c>
-      <c r="R139" t="n">
-        <v>3.76</v>
-      </c>
       <c r="S139" t="n">
         <v>0</v>
       </c>
@@ -27835,10 +27835,10 @@
         <v>0</v>
       </c>
       <c r="AE139" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF139" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG139" t="n">
         <v>0</v>
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q140" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R140" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>

--- a/jogos_2026-05-24.xlsx
+++ b/jogos_2026-05-24.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.29</v>
+        <v>1.97</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.95</v>
+        <v>3.18</v>
       </c>
       <c r="R9" t="n">
-        <v>8.199999999999999</v>
+        <v>3.61</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.97</v>
+        <v>1.29</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.18</v>
+        <v>4.95</v>
       </c>
       <c r="R10" t="n">
-        <v>3.61</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="R21" t="n">
-        <v>5.14</v>
+        <v>3.8</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.92</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6762,10 +6762,10 @@
         <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>4.92</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6959,10 +6959,10 @@
         <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.95</v>
+        <v>1.28</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.53</v>
+        <v>5.41</v>
       </c>
       <c r="R36" t="n">
-        <v>2.2</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,10 +7696,10 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="Q37" t="n">
-        <v>5</v>
+        <v>4.58</v>
       </c>
       <c r="R37" t="n">
         <v>6</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.3</v>
+        <v>1.93</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.6</v>
+        <v>3.99</v>
       </c>
       <c r="R38" t="n">
-        <v>2.6</v>
+        <v>3.22</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.28</v>
+        <v>2.95</v>
       </c>
       <c r="Q41" t="n">
-        <v>5.41</v>
+        <v>3.53</v>
       </c>
       <c r="R41" t="n">
-        <v>8.039999999999999</v>
+        <v>2.2</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.93</v>
+        <v>3</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.99</v>
+        <v>3.66</v>
       </c>
       <c r="R43" t="n">
-        <v>3.22</v>
+        <v>2.13</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -8923,10 +8923,10 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>5.57</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>7.02</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>4.54</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.44</v>
+        <v>3.82</v>
       </c>
       <c r="Q51" t="n">
-        <v>5.57</v>
+        <v>3.82</v>
       </c>
       <c r="R51" t="n">
-        <v>7.02</v>
+        <v>2.03</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.29</v>
+        <v>2.52</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R53" t="n">
-        <v>2.83</v>
+        <v>2.94</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>4.54</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF58" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.63</v>
+        <v>2.29</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.82</v>
+        <v>3.4</v>
       </c>
       <c r="R61" t="n">
-        <v>2.68</v>
+        <v>2.83</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12469,10 +12469,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF61" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -13361,22 +13361,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>5.37</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13460,10 +13460,10 @@
         <v>0</v>
       </c>
       <c r="AG66" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH66" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI66" t="n">
         <v>0</v>
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>5.37</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13657,10 +13657,10 @@
         <v>0</v>
       </c>
       <c r="AG67" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH67" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI67" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="Q69" t="n">
-        <v>4.37</v>
+        <v>4.46</v>
       </c>
       <c r="R69" t="n">
-        <v>5.41</v>
+        <v>6.22</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF69" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14833,10 +14833,10 @@
         <v>0</v>
       </c>
       <c r="AE73" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF73" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG73" t="n">
         <v>0</v>
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15030,10 +15030,10 @@
         <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF74" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG74" t="n">
         <v>0</v>
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>1.82</v>
+        <v>1.96</v>
       </c>
       <c r="Q75" t="n">
-        <v>4.06</v>
+        <v>3.81</v>
       </c>
       <c r="R75" t="n">
-        <v>4.06</v>
+        <v>3.73</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF75" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1.53</v>
+        <v>1.82</v>
       </c>
       <c r="Q76" t="n">
-        <v>4.33</v>
+        <v>4.06</v>
       </c>
       <c r="R76" t="n">
-        <v>6.19</v>
+        <v>4.06</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1.7</v>
+        <v>1.59</v>
       </c>
       <c r="Q77" t="n">
-        <v>4.53</v>
+        <v>4.37</v>
       </c>
       <c r="R77" t="n">
-        <v>4.32</v>
+        <v>5.41</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15627,10 +15627,10 @@
         <v>0</v>
       </c>
       <c r="AG77" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH77" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AI77" t="n">
         <v>0</v>
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2.59</v>
+        <v>4.15</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.42</v>
+        <v>3.73</v>
       </c>
       <c r="R78" t="n">
-        <v>2.75</v>
+        <v>1.88</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>3.77</v>
+        <v>1.53</v>
       </c>
       <c r="Q79" t="n">
-        <v>4.17</v>
+        <v>4.33</v>
       </c>
       <c r="R79" t="n">
-        <v>1.86</v>
+        <v>6.19</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1.52</v>
+        <v>3.19</v>
       </c>
       <c r="Q80" t="n">
-        <v>4.46</v>
+        <v>3.19</v>
       </c>
       <c r="R80" t="n">
-        <v>6.22</v>
+        <v>2.41</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF80" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>3.19</v>
+        <v>1.7</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.19</v>
+        <v>4.53</v>
       </c>
       <c r="R81" t="n">
-        <v>2.41</v>
+        <v>4.32</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16415,10 +16415,10 @@
         <v>0</v>
       </c>
       <c r="AG81" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH81" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AI81" t="n">
         <v>0</v>
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>5.88</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>1.96</v>
+        <v>1.77</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.81</v>
+        <v>4.07</v>
       </c>
       <c r="R83" t="n">
-        <v>3.73</v>
+        <v>4.22</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF83" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>1.32</v>
+        <v>1.67</v>
       </c>
       <c r="Q84" t="n">
-        <v>5.88</v>
+        <v>4.17</v>
       </c>
       <c r="R84" t="n">
-        <v>8.4</v>
+        <v>4.94</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>1.67</v>
+        <v>2.59</v>
       </c>
       <c r="Q85" t="n">
-        <v>4.17</v>
+        <v>3.42</v>
       </c>
       <c r="R85" t="n">
-        <v>4.94</v>
+        <v>2.75</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AF96" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>4.83</v>
+        <v>0</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19758,10 +19758,10 @@
         <v>0</v>
       </c>
       <c r="AE98" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AF98" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AG98" t="n">
         <v>0</v>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q103" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20743,10 +20743,10 @@
         <v>0</v>
       </c>
       <c r="AE103" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF103" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG103" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q104" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -20940,10 +20940,10 @@
         <v>0</v>
       </c>
       <c r="AE104" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF104" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG104" t="n">
         <v>0</v>
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Q121" t="n">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="R121" t="n">
-        <v>6.19</v>
+        <v>0</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24295,10 +24295,10 @@
         <v>0</v>
       </c>
       <c r="AG121" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH121" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI121" t="n">
         <v>0</v>
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Q124" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="R124" t="n">
-        <v>0</v>
+        <v>6.19</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24886,10 +24886,10 @@
         <v>0</v>
       </c>
       <c r="AG124" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH124" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI124" t="n">
         <v>0</v>
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Q132" t="n">
-        <v>5.24</v>
+        <v>0</v>
       </c>
       <c r="R132" t="n">
-        <v>7.08</v>
+        <v>0</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26462,10 +26462,10 @@
         <v>0</v>
       </c>
       <c r="AG132" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH132" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI132" t="n">
         <v>0</v>
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26608,13 +26608,13 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Q133" t="n">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="R133" t="n">
-        <v>0</v>
+        <v>7.08</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -26659,10 +26659,10 @@
         <v>0</v>
       </c>
       <c r="AG133" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH133" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI133" t="n">
         <v>0</v>
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G142" t="n">

--- a/jogos_2026-05-24.xlsx
+++ b/jogos_2026-05-24.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.97</v>
+        <v>1.29</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.18</v>
+        <v>4.95</v>
       </c>
       <c r="R9" t="n">
-        <v>3.61</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.29</v>
+        <v>1.97</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.95</v>
+        <v>3.18</v>
       </c>
       <c r="R10" t="n">
-        <v>8.199999999999999</v>
+        <v>3.61</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="R21" t="n">
-        <v>3.8</v>
+        <v>5.14</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="R25" t="n">
-        <v>5.14</v>
+        <v>3.8</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.92</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6959,10 +6959,10 @@
         <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>4.92</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7156,10 +7156,10 @@
         <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.3</v>
+        <v>2.95</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.6</v>
+        <v>3.53</v>
       </c>
       <c r="R35" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7347,10 +7347,10 @@
         <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>5.41</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>8.039999999999999</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,10 +7696,10 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.58</v>
+        <v>5</v>
       </c>
       <c r="R37" t="n">
         <v>6</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.33</v>
+        <v>1.63</v>
       </c>
       <c r="Q40" t="n">
-        <v>5</v>
+        <v>3.96</v>
       </c>
       <c r="R40" t="n">
-        <v>6</v>
+        <v>4.85</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.53</v>
+        <v>3.66</v>
       </c>
       <c r="R41" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.93</v>
+        <v>1.78</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.83</v>
+        <v>1.99</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>3</v>
+        <v>1.93</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.66</v>
+        <v>3.99</v>
       </c>
       <c r="R43" t="n">
-        <v>2.13</v>
+        <v>3.22</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -8923,10 +8923,10 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.63</v>
+        <v>1.28</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.96</v>
+        <v>5.41</v>
       </c>
       <c r="R44" t="n">
-        <v>4.85</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>7</v>
+        <v>2.29</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.43</v>
+        <v>3.4</v>
       </c>
       <c r="R46" t="n">
-        <v>1.55</v>
+        <v>2.83</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>5.57</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>7.02</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.54</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.54</v>
+        <v>2.8</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.62</v>
+        <v>3.81</v>
       </c>
       <c r="R50" t="n">
-        <v>2.89</v>
+        <v>2.53</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.25</v>
+        <v>1.55</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.73</v>
+        <v>4.54</v>
       </c>
       <c r="R52" t="n">
-        <v>3.31</v>
+        <v>6.7</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="R53" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.82</v>
+        <v>3.73</v>
       </c>
       <c r="R54" t="n">
-        <v>2.68</v>
+        <v>3.31</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.29</v>
+        <v>2.63</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.4</v>
+        <v>3.82</v>
       </c>
       <c r="R61" t="n">
-        <v>2.83</v>
+        <v>2.68</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12469,10 +12469,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF61" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>5.57</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>7.02</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>5.37</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13657,10 +13657,10 @@
         <v>0</v>
       </c>
       <c r="AG67" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH67" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI67" t="n">
         <v>0</v>
@@ -13755,22 +13755,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>5.37</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13854,10 +13854,10 @@
         <v>0</v>
       </c>
       <c r="AG68" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH68" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1.52</v>
+        <v>4.15</v>
       </c>
       <c r="Q69" t="n">
-        <v>4.46</v>
+        <v>3.73</v>
       </c>
       <c r="R69" t="n">
-        <v>6.22</v>
+        <v>1.88</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF69" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14248,10 +14248,10 @@
         <v>0</v>
       </c>
       <c r="AG70" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH70" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AI70" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>3.77</v>
+        <v>2.59</v>
       </c>
       <c r="Q71" t="n">
-        <v>4.17</v>
+        <v>3.42</v>
       </c>
       <c r="R71" t="n">
-        <v>1.86</v>
+        <v>2.75</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF72" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>5.41</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>5.25</v>
+        <v>1.82</v>
       </c>
       <c r="Q74" t="n">
-        <v>4.22</v>
+        <v>4.06</v>
       </c>
       <c r="R74" t="n">
-        <v>1.63</v>
+        <v>4.06</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15030,10 +15030,10 @@
         <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF74" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG74" t="n">
         <v>0</v>
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>1.96</v>
+        <v>1.67</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.81</v>
+        <v>4.17</v>
       </c>
       <c r="R75" t="n">
-        <v>3.73</v>
+        <v>4.94</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF75" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>5.41</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>4.15</v>
+        <v>1.52</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.73</v>
+        <v>4.46</v>
       </c>
       <c r="R78" t="n">
-        <v>1.88</v>
+        <v>6.22</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15818,10 +15818,10 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF78" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1.53</v>
+        <v>3.19</v>
       </c>
       <c r="Q79" t="n">
-        <v>4.33</v>
+        <v>3.19</v>
       </c>
       <c r="R79" t="n">
-        <v>6.19</v>
+        <v>2.41</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>3.19</v>
+        <v>1.96</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.19</v>
+        <v>3.81</v>
       </c>
       <c r="R80" t="n">
-        <v>2.41</v>
+        <v>3.73</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF80" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="Q81" t="n">
-        <v>4.53</v>
+        <v>4.33</v>
       </c>
       <c r="R81" t="n">
-        <v>4.32</v>
+        <v>6.19</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16415,10 +16415,10 @@
         <v>0</v>
       </c>
       <c r="AG81" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH81" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AI81" t="n">
         <v>0</v>
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="Q84" t="n">
-        <v>4.17</v>
+        <v>4.07</v>
       </c>
       <c r="R84" t="n">
-        <v>4.94</v>
+        <v>4.22</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>2.59</v>
+        <v>3.77</v>
       </c>
       <c r="Q85" t="n">
-        <v>3.42</v>
+        <v>4.17</v>
       </c>
       <c r="R85" t="n">
-        <v>2.75</v>
+        <v>1.86</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>5.21</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>5.21</v>
+        <v>0</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>4.97</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1.77</v>
+        <v>2.29</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.32</v>
+        <v>2.69</v>
       </c>
       <c r="R96" t="n">
-        <v>4.83</v>
+        <v>3.43</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AF96" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q99" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="R99" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q100" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>9.949999999999999</v>
+        <v>0</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Q107" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R107" t="n">
-        <v>0</v>
+        <v>7.25</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q108" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R108" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21728,10 +21728,10 @@
         <v>0</v>
       </c>
       <c r="AE108" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AF108" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG108" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q115" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R115" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Q122" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="R122" t="n">
-        <v>0</v>
+        <v>6.19</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24492,10 +24492,10 @@
         <v>0</v>
       </c>
       <c r="AG122" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH122" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI122" t="n">
         <v>0</v>
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Q124" t="n">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="R124" t="n">
-        <v>6.19</v>
+        <v>0</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24886,10 +24886,10 @@
         <v>0</v>
       </c>
       <c r="AG124" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH124" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI124" t="n">
         <v>0</v>
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26214,13 +26214,13 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q131" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="R131" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="S131" t="n">
         <v>0</v>
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="G135" t="n">

--- a/jogos_2026-05-24.xlsx
+++ b/jogos_2026-05-24.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.95</v>
+        <v>2.3</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.53</v>
+        <v>3.6</v>
       </c>
       <c r="R35" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7347,10 +7347,10 @@
         <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.33</v>
+        <v>3</v>
       </c>
       <c r="Q37" t="n">
-        <v>5</v>
+        <v>3.66</v>
       </c>
       <c r="R37" t="n">
-        <v>6</v>
+        <v>2.13</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7741,10 +7741,10 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>5.41</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.3</v>
+        <v>1.42</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.6</v>
+        <v>4.58</v>
       </c>
       <c r="R39" t="n">
-        <v>2.6</v>
+        <v>6</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,55 +8878,55 @@
         </is>
       </c>
       <c r="P43" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="R43" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="n">
         <v>1.93</v>
       </c>
-      <c r="Q43" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="R43" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="S43" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" t="n">
-        <v>0</v>
-      </c>
-      <c r="U43" t="n">
-        <v>0</v>
-      </c>
-      <c r="V43" t="n">
-        <v>0</v>
-      </c>
-      <c r="W43" t="n">
-        <v>0</v>
-      </c>
-      <c r="X43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>0</v>
-      </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.28</v>
+        <v>1.93</v>
       </c>
       <c r="Q44" t="n">
-        <v>5.41</v>
+        <v>3.99</v>
       </c>
       <c r="R44" t="n">
-        <v>8.039999999999999</v>
+        <v>3.22</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.29</v>
+        <v>2.52</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R46" t="n">
-        <v>2.83</v>
+        <v>2.94</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.8</v>
+        <v>3.82</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.81</v>
+        <v>3.82</v>
       </c>
       <c r="R50" t="n">
-        <v>2.53</v>
+        <v>2.03</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.55</v>
+        <v>2.29</v>
       </c>
       <c r="Q52" t="n">
-        <v>4.54</v>
+        <v>3.4</v>
       </c>
       <c r="R52" t="n">
-        <v>6.7</v>
+        <v>2.83</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.73</v>
+        <v>3.82</v>
       </c>
       <c r="R54" t="n">
-        <v>3.31</v>
+        <v>2.68</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.52</v>
+        <v>1.55</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.6</v>
+        <v>4.54</v>
       </c>
       <c r="R56" t="n">
-        <v>2.94</v>
+        <v>6.7</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>3.82</v>
+        <v>1.44</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.82</v>
+        <v>5.57</v>
       </c>
       <c r="R59" t="n">
-        <v>2.03</v>
+        <v>7.02</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.82</v>
+        <v>3.73</v>
       </c>
       <c r="R61" t="n">
-        <v>2.68</v>
+        <v>3.31</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12469,10 +12469,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF61" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>5.57</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>7.02</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,22 +12770,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>5.37</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12869,10 +12869,10 @@
         <v>0</v>
       </c>
       <c r="AG63" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH63" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI63" t="n">
         <v>0</v>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13755,22 +13755,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>5.37</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13854,10 +13854,10 @@
         <v>0</v>
       </c>
       <c r="AG68" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH68" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI68" t="n">
         <v>0</v>
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14248,10 +14248,10 @@
         <v>0</v>
       </c>
       <c r="AG70" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH70" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AI70" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>2.59</v>
+        <v>3.19</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.42</v>
+        <v>3.19</v>
       </c>
       <c r="R71" t="n">
-        <v>2.75</v>
+        <v>2.41</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>5.25</v>
+        <v>2.59</v>
       </c>
       <c r="Q72" t="n">
-        <v>4.22</v>
+        <v>3.42</v>
       </c>
       <c r="R72" t="n">
-        <v>1.63</v>
+        <v>2.75</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF72" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="Q73" t="n">
-        <v>4.37</v>
+        <v>4.46</v>
       </c>
       <c r="R73" t="n">
-        <v>5.41</v>
+        <v>6.22</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14833,10 +14833,10 @@
         <v>0</v>
       </c>
       <c r="AE73" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF73" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG73" t="n">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1.82</v>
+        <v>1.59</v>
       </c>
       <c r="Q74" t="n">
-        <v>4.06</v>
+        <v>4.37</v>
       </c>
       <c r="R74" t="n">
-        <v>4.06</v>
+        <v>5.41</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>1.67</v>
+        <v>3.77</v>
       </c>
       <c r="Q75" t="n">
         <v>4.17</v>
       </c>
       <c r="R75" t="n">
-        <v>4.94</v>
+        <v>1.86</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>6.19</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15627,10 +15627,10 @@
         <v>0</v>
       </c>
       <c r="AG77" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH77" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AI77" t="n">
         <v>0</v>
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="Q78" t="n">
-        <v>4.46</v>
+        <v>4.17</v>
       </c>
       <c r="R78" t="n">
-        <v>6.22</v>
+        <v>4.94</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15818,10 +15818,10 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF78" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG78" t="n">
         <v>0</v>
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1.96</v>
+        <v>1.32</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.81</v>
+        <v>5.88</v>
       </c>
       <c r="R80" t="n">
-        <v>3.73</v>
+        <v>8.4</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF80" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1.53</v>
+        <v>5.25</v>
       </c>
       <c r="Q81" t="n">
-        <v>4.33</v>
+        <v>4.22</v>
       </c>
       <c r="R81" t="n">
-        <v>6.19</v>
+        <v>1.63</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16409,10 +16409,10 @@
         <v>0</v>
       </c>
       <c r="AE81" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF81" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG81" t="n">
         <v>0</v>
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1.32</v>
+        <v>1.77</v>
       </c>
       <c r="Q82" t="n">
-        <v>5.88</v>
+        <v>4.07</v>
       </c>
       <c r="R82" t="n">
-        <v>8.4</v>
+        <v>4.22</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF83" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="Q84" t="n">
-        <v>4.07</v>
+        <v>4.06</v>
       </c>
       <c r="R84" t="n">
-        <v>4.22</v>
+        <v>4.06</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>5.21</v>
+        <v>0</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>5.21</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>2.29</v>
+        <v>2.8</v>
       </c>
       <c r="Q96" t="n">
-        <v>2.69</v>
+        <v>3.27</v>
       </c>
       <c r="R96" t="n">
-        <v>3.43</v>
+        <v>2.64</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF96" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="Q99" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>9.949999999999999</v>
+        <v>0</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q101" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20349,10 +20349,10 @@
         <v>0</v>
       </c>
       <c r="AE101" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AF101" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG101" t="n">
         <v>0</v>
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Q102" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>7.25</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -20940,10 +20940,10 @@
         <v>0</v>
       </c>
       <c r="AE104" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF104" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG104" t="n">
         <v>0</v>
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q106" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="R106" t="n">
-        <v>0</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Q107" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>7.25</v>
+        <v>0</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q108" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R108" t="n">
-        <v>4.83</v>
+        <v>0</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21728,10 +21728,10 @@
         <v>0</v>
       </c>
       <c r="AE108" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AF108" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AG108" t="n">
         <v>0</v>
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q109" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="R109" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q115" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R115" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q118" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R118" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Q122" t="n">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="R122" t="n">
-        <v>6.19</v>
+        <v>0</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24492,10 +24492,10 @@
         <v>0</v>
       </c>
       <c r="AG122" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH122" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI122" t="n">
         <v>0</v>
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q123" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R123" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Q124" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="R124" t="n">
-        <v>0</v>
+        <v>6.19</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24886,10 +24886,10 @@
         <v>0</v>
       </c>
       <c r="AG124" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH124" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI124" t="n">
         <v>0</v>
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q125" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="R125" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q129" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="R129" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26214,13 +26214,13 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q131" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="R131" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="S131" t="n">
         <v>0</v>
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26608,13 +26608,13 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Q133" t="n">
-        <v>5.24</v>
+        <v>0</v>
       </c>
       <c r="R133" t="n">
-        <v>7.08</v>
+        <v>0</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -26659,10 +26659,10 @@
         <v>0</v>
       </c>
       <c r="AG133" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH133" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI133" t="n">
         <v>0</v>
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Q135" t="n">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="R135" t="n">
-        <v>0</v>
+        <v>7.08</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -27053,10 +27053,10 @@
         <v>0</v>
       </c>
       <c r="AG135" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH135" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI135" t="n">
         <v>0</v>
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q138" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R138" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -27638,10 +27638,10 @@
         <v>0</v>
       </c>
       <c r="AE138" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF138" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG138" t="n">
         <v>0</v>
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27790,13 +27790,13 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q139" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="R139" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -27835,10 +27835,10 @@
         <v>0</v>
       </c>
       <c r="AE139" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF139" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG139" t="n">
         <v>0</v>
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G142" t="n">

--- a/jogos_2026-05-24.xlsx
+++ b/jogos_2026-05-24.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI143"/>
+  <dimension ref="A1:BI150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.29</v>
+        <v>1.97</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.95</v>
+        <v>3.18</v>
       </c>
       <c r="R9" t="n">
-        <v>8.199999999999999</v>
+        <v>3.61</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.97</v>
+        <v>1.29</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.18</v>
+        <v>4.95</v>
       </c>
       <c r="R10" t="n">
-        <v>3.61</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>5.14</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="R25" t="n">
-        <v>3.8</v>
+        <v>5.14</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AR29" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AS29" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AU29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV29" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AW29" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AX29" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AY29" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BA29" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="BB29" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BC29" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BD29" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE29" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BF29" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6658,12 +6658,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6846,7 +6846,7 @@
         <v>0</v>
       </c>
       <c r="BI32" s="3" t="n">
-        <v>46166.45833333334</v>
+        <v>46166.41666666666</v>
       </c>
     </row>
     <row r="33">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>4.92</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6959,10 +6959,10 @@
         <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.92</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7156,10 +7156,10 @@
         <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -7249,27 +7249,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7437,7 +7437,7 @@
         <v>0</v>
       </c>
       <c r="BI35" s="3" t="n">
-        <v>46166.47916666666</v>
+        <v>46166.45833333334</v>
       </c>
     </row>
     <row r="36">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.33</v>
+        <v>1.63</v>
       </c>
       <c r="Q36" t="n">
-        <v>5</v>
+        <v>3.96</v>
       </c>
       <c r="R36" t="n">
-        <v>6</v>
+        <v>4.85</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>3</v>
+        <v>1.33</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.66</v>
+        <v>5</v>
       </c>
       <c r="R37" t="n">
-        <v>2.13</v>
+        <v>6</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7741,10 +7741,10 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q38" t="n">
-        <v>5.41</v>
+        <v>3.6</v>
       </c>
       <c r="R38" t="n">
-        <v>8.039999999999999</v>
+        <v>2.6</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.42</v>
+        <v>3</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.58</v>
+        <v>3.66</v>
       </c>
       <c r="R39" t="n">
-        <v>6</v>
+        <v>2.13</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.63</v>
+        <v>2.95</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.96</v>
+        <v>3.53</v>
       </c>
       <c r="R40" t="n">
-        <v>4.85</v>
+        <v>2.2</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.53</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -8923,10 +8923,10 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
@@ -9219,12 +9219,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>5.41</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9407,7 +9407,7 @@
         <v>0</v>
       </c>
       <c r="BI45" s="3" t="n">
-        <v>46166.5</v>
+        <v>46166.47916666666</v>
       </c>
     </row>
     <row r="46">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.52</v>
+        <v>1.44</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.6</v>
+        <v>5.57</v>
       </c>
       <c r="R46" t="n">
-        <v>2.94</v>
+        <v>7.02</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.8</v>
+        <v>1.55</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.81</v>
+        <v>4.54</v>
       </c>
       <c r="R47" t="n">
-        <v>2.53</v>
+        <v>6.7</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>7</v>
+        <v>2.52</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.43</v>
+        <v>3.6</v>
       </c>
       <c r="R49" t="n">
-        <v>1.55</v>
+        <v>2.94</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>3.82</v>
+        <v>7</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.82</v>
+        <v>4.43</v>
       </c>
       <c r="R50" t="n">
-        <v>2.03</v>
+        <v>1.55</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.29</v>
+        <v>2.8</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.4</v>
+        <v>3.81</v>
       </c>
       <c r="R52" t="n">
-        <v>2.83</v>
+        <v>2.53</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.63</v>
+        <v>2.54</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.82</v>
+        <v>3.62</v>
       </c>
       <c r="R54" t="n">
-        <v>2.68</v>
+        <v>2.89</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.55</v>
+        <v>2.63</v>
       </c>
       <c r="Q56" t="n">
-        <v>4.54</v>
+        <v>3.82</v>
       </c>
       <c r="R56" t="n">
-        <v>6.7</v>
+        <v>2.68</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>5.57</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>7.02</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12765,27 +12765,27 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>5.37</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12869,10 +12869,10 @@
         <v>0</v>
       </c>
       <c r="AG63" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH63" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI63" t="n">
         <v>0</v>
@@ -12953,7 +12953,7 @@
         <v>0</v>
       </c>
       <c r="BI63" s="3" t="n">
-        <v>46166.54166666666</v>
+        <v>46166.5</v>
       </c>
     </row>
     <row r="64">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,22 +13755,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>5.37</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13854,10 +13854,10 @@
         <v>0</v>
       </c>
       <c r="AG68" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH68" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI68" t="n">
         <v>0</v>
@@ -13947,12 +13947,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14135,7 +14135,7 @@
         <v>0</v>
       </c>
       <c r="BI69" s="3" t="n">
-        <v>46166.5625</v>
+        <v>46166.54166666666</v>
       </c>
     </row>
     <row r="70">
@@ -14144,27 +14144,27 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,133 +14197,133 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="S70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T70" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U70" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V70" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W70" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="X70" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Y70" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z70" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA70" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC70" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AD70" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="AE70" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF70" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG70" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AH70" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AI70" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AJ70" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL70" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AM70" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN70" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AO70" t="n">
         <v>0</v>
       </c>
       <c r="AP70" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ70" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AR70" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AS70" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AT70" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AU70" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AV70" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AW70" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AX70" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AY70" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ70" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BA70" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BB70" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BC70" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD70" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE70" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BF70" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG70" t="n">
         <v>0</v>
@@ -14332,7 +14332,7 @@
         <v>0</v>
       </c>
       <c r="BI70" s="3" t="n">
-        <v>46166.5625</v>
+        <v>46166.54166666666</v>
       </c>
     </row>
     <row r="71">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>2.59</v>
+        <v>1.59</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.42</v>
+        <v>4.37</v>
       </c>
       <c r="R72" t="n">
-        <v>2.75</v>
+        <v>5.41</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>1.52</v>
+        <v>1.82</v>
       </c>
       <c r="Q73" t="n">
-        <v>4.46</v>
+        <v>4.06</v>
       </c>
       <c r="R73" t="n">
-        <v>6.22</v>
+        <v>4.06</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14833,10 +14833,10 @@
         <v>0</v>
       </c>
       <c r="AE73" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF73" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG73" t="n">
         <v>0</v>
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>4.37</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>5.41</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>3.77</v>
+        <v>1.53</v>
       </c>
       <c r="Q75" t="n">
-        <v>4.17</v>
+        <v>4.33</v>
       </c>
       <c r="R75" t="n">
-        <v>1.86</v>
+        <v>6.19</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1.53</v>
+        <v>4.15</v>
       </c>
       <c r="Q76" t="n">
-        <v>4.33</v>
+        <v>3.73</v>
       </c>
       <c r="R76" t="n">
-        <v>6.19</v>
+        <v>1.88</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1.7</v>
+        <v>2.59</v>
       </c>
       <c r="Q77" t="n">
-        <v>4.53</v>
+        <v>3.42</v>
       </c>
       <c r="R77" t="n">
-        <v>4.32</v>
+        <v>2.75</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15627,10 +15627,10 @@
         <v>0</v>
       </c>
       <c r="AG77" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH77" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AI77" t="n">
         <v>0</v>
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>4.94</v>
+        <v>0</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>5.88</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>5.25</v>
+        <v>1.32</v>
       </c>
       <c r="Q81" t="n">
-        <v>4.22</v>
+        <v>5.88</v>
       </c>
       <c r="R81" t="n">
-        <v>1.63</v>
+        <v>8.4</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16409,10 +16409,10 @@
         <v>0</v>
       </c>
       <c r="AE81" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF81" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="Q82" t="n">
-        <v>4.07</v>
+        <v>4.53</v>
       </c>
       <c r="R82" t="n">
-        <v>4.22</v>
+        <v>4.32</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16612,10 +16612,10 @@
         <v>0</v>
       </c>
       <c r="AG82" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH82" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AI82" t="n">
         <v>0</v>
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>1.96</v>
+        <v>3.77</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.81</v>
+        <v>4.17</v>
       </c>
       <c r="R83" t="n">
-        <v>3.73</v>
+        <v>1.86</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF83" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>1.82</v>
+        <v>1.96</v>
       </c>
       <c r="Q84" t="n">
-        <v>4.06</v>
+        <v>3.81</v>
       </c>
       <c r="R84" t="n">
-        <v>4.06</v>
+        <v>3.73</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17000,10 +17000,10 @@
         <v>0</v>
       </c>
       <c r="AE84" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF84" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG84" t="n">
         <v>0</v>
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>6.22</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17197,10 +17197,10 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF85" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG85" t="n">
         <v>0</v>
@@ -17296,27 +17296,27 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17484,7 +17484,7 @@
         <v>0</v>
       </c>
       <c r="BI86" s="3" t="n">
-        <v>46166.58333333334</v>
+        <v>46166.5625</v>
       </c>
     </row>
     <row r="87">
@@ -17493,27 +17493,27 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF87" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17681,7 +17681,7 @@
         <v>0</v>
       </c>
       <c r="BI87" s="3" t="n">
-        <v>46166.58333333334</v>
+        <v>46166.5625</v>
       </c>
     </row>
     <row r="88">
@@ -17690,27 +17690,27 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17878,7 +17878,7 @@
         <v>0</v>
       </c>
       <c r="BI88" s="3" t="n">
-        <v>46166.60416666666</v>
+        <v>46166.58333333334</v>
       </c>
     </row>
     <row r="89">
@@ -17887,27 +17887,27 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18075,7 +18075,7 @@
         <v>0</v>
       </c>
       <c r="BI89" s="3" t="n">
-        <v>46166.60416666666</v>
+        <v>46166.58333333334</v>
       </c>
     </row>
     <row r="90">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18478,27 +18478,27 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18666,7 +18666,7 @@
         <v>0</v>
       </c>
       <c r="BI92" s="3" t="n">
-        <v>46166.625</v>
+        <v>46166.60416666666</v>
       </c>
     </row>
     <row r="93">
@@ -18675,27 +18675,27 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>5.21</v>
+        <v>0</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18863,7 +18863,7 @@
         <v>0</v>
       </c>
       <c r="BI93" s="3" t="n">
-        <v>46166.625</v>
+        <v>46166.60416666666</v>
       </c>
     </row>
     <row r="94">
@@ -18872,12 +18872,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1.76</v>
+        <v>1.66</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.19</v>
+        <v>3.46</v>
       </c>
       <c r="R94" t="n">
-        <v>4.97</v>
+        <v>5.21</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19060,7 +19060,7 @@
         <v>0</v>
       </c>
       <c r="BI94" s="3" t="n">
-        <v>46166.64583333334</v>
+        <v>46166.625</v>
       </c>
     </row>
     <row r="95">
@@ -19069,12 +19069,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19257,7 +19257,7 @@
         <v>0</v>
       </c>
       <c r="BI95" s="3" t="n">
-        <v>46166.64583333334</v>
+        <v>46166.625</v>
       </c>
     </row>
     <row r="96">
@@ -19266,12 +19266,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>2.8</v>
+        <v>1.76</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.27</v>
+        <v>3.19</v>
       </c>
       <c r="R96" t="n">
-        <v>2.64</v>
+        <v>4.97</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF96" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -19454,7 +19454,7 @@
         <v>0</v>
       </c>
       <c r="BI96" s="3" t="n">
-        <v>46166.66666666666</v>
+        <v>46166.64583333334</v>
       </c>
     </row>
     <row r="97">
@@ -19463,7 +19463,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19651,7 +19651,7 @@
         <v>0</v>
       </c>
       <c r="BI97" s="3" t="n">
-        <v>46166.66666666666</v>
+        <v>46166.64583333334</v>
       </c>
     </row>
     <row r="98">
@@ -19660,27 +19660,27 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,133 +19713,133 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>2.29</v>
+        <v>1.7</v>
       </c>
       <c r="Q98" t="n">
-        <v>2.76</v>
+        <v>3.68</v>
       </c>
       <c r="R98" t="n">
-        <v>3.61</v>
+        <v>5.1</v>
       </c>
       <c r="S98" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T98" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="U98" t="n">
-        <v>0</v>
+        <v>4.54</v>
       </c>
       <c r="V98" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W98" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="X98" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Y98" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z98" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AA98" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB98" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC98" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD98" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AE98" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AF98" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG98" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AH98" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI98" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AJ98" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK98" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AL98" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AM98" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AN98" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AO98" t="n">
         <v>0</v>
       </c>
       <c r="AP98" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AQ98" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR98" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AS98" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AT98" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AU98" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV98" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AW98" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AX98" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AY98" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AZ98" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BA98" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="BB98" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BC98" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BD98" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE98" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BF98" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG98" t="n">
         <v>0</v>
@@ -19848,7 +19848,7 @@
         <v>0</v>
       </c>
       <c r="BI98" s="3" t="n">
-        <v>46166.66666666666</v>
+        <v>46166.65625</v>
       </c>
     </row>
     <row r="99">
@@ -19857,12 +19857,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,133 +19910,133 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Q99" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="R99" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S99" t="n">
-        <v>0</v>
+        <v>5.51</v>
       </c>
       <c r="T99" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U99" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="V99" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W99" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="X99" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Y99" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z99" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA99" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB99" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC99" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AD99" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AE99" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF99" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG99" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AH99" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI99" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AJ99" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK99" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AL99" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AM99" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN99" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AO99" t="n">
         <v>0</v>
       </c>
       <c r="AP99" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AQ99" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AR99" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AS99" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AT99" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AU99" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AV99" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AW99" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AX99" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AY99" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AZ99" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BA99" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BB99" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BC99" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BD99" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="BE99" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF99" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG99" t="n">
         <v>0</v>
@@ -20045,7 +20045,7 @@
         <v>0</v>
       </c>
       <c r="BI99" s="3" t="n">
-        <v>46166.66666666666</v>
+        <v>46166.65625</v>
       </c>
     </row>
     <row r="100">
@@ -20054,27 +20054,27 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,133 +20107,133 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q100" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S100" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="T100" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U100" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="V100" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W100" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="X100" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Y100" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z100" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AA100" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC100" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AD100" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AE100" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF100" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG100" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AH100" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI100" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AJ100" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK100" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL100" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AM100" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN100" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AO100" t="n">
         <v>0</v>
       </c>
       <c r="AP100" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AQ100" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AR100" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AS100" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AT100" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AU100" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AV100" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AW100" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AX100" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AY100" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AZ100" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BA100" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BB100" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC100" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BD100" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="BE100" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="BF100" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BG100" t="n">
         <v>0</v>
@@ -20242,7 +20242,7 @@
         <v>0</v>
       </c>
       <c r="BI100" s="3" t="n">
-        <v>46166.66666666666</v>
+        <v>46166.65625</v>
       </c>
     </row>
     <row r="101">
@@ -20251,27 +20251,27 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,133 +20304,133 @@
         </is>
       </c>
       <c r="P101" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="R101" t="n">
+        <v>9</v>
+      </c>
+      <c r="S101" t="n">
         <v>1.77</v>
       </c>
-      <c r="Q101" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="R101" t="n">
-        <v>4.83</v>
-      </c>
-      <c r="S101" t="n">
-        <v>0</v>
-      </c>
       <c r="T101" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U101" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="V101" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W101" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="X101" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Y101" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z101" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AA101" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC101" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD101" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE101" t="n">
-        <v>2.37</v>
+        <v>1.79</v>
       </c>
       <c r="AF101" t="n">
-        <v>1.51</v>
+        <v>2.19</v>
       </c>
       <c r="AG101" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AH101" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI101" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AJ101" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK101" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AL101" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AM101" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN101" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AO101" t="n">
         <v>0</v>
       </c>
       <c r="AP101" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AQ101" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR101" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AS101" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AT101" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AU101" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AV101" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW101" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AX101" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY101" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ101" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BA101" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BB101" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC101" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BD101" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE101" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BF101" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG101" t="n">
         <v>0</v>
@@ -20439,7 +20439,7 @@
         <v>0</v>
       </c>
       <c r="BI101" s="3" t="n">
-        <v>46166.66666666666</v>
+        <v>46166.65625</v>
       </c>
     </row>
     <row r="102">
@@ -20448,27 +20448,27 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,133 +20501,133 @@
         </is>
       </c>
       <c r="P102" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="R102" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="S102" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="T102" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="U102" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="V102" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W102" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="X102" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="Y102" t="n">
         <v>1.51</v>
       </c>
-      <c r="Q102" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R102" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="S102" t="n">
-        <v>0</v>
-      </c>
-      <c r="T102" t="n">
-        <v>0</v>
-      </c>
-      <c r="U102" t="n">
-        <v>0</v>
-      </c>
-      <c r="V102" t="n">
-        <v>0</v>
-      </c>
-      <c r="W102" t="n">
-        <v>0</v>
-      </c>
-      <c r="X102" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y102" t="n">
-        <v>0</v>
-      </c>
       <c r="Z102" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA102" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC102" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD102" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AE102" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF102" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AG102" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AH102" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI102" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AJ102" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK102" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL102" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AM102" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN102" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AO102" t="n">
         <v>0</v>
       </c>
       <c r="AP102" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AQ102" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AR102" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AS102" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AT102" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AU102" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AV102" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AW102" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AX102" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AY102" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AZ102" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BA102" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BB102" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC102" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD102" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="BE102" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BF102" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BG102" t="n">
         <v>0</v>
@@ -20636,7 +20636,7 @@
         <v>0</v>
       </c>
       <c r="BI102" s="3" t="n">
-        <v>46166.66666666666</v>
+        <v>46166.65625</v>
       </c>
     </row>
     <row r="103">
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q103" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>1.32</v>
+        <v>1.77</v>
       </c>
       <c r="Q106" t="n">
-        <v>5.45</v>
+        <v>3.32</v>
       </c>
       <c r="R106" t="n">
-        <v>9.949999999999999</v>
+        <v>4.83</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21334,10 +21334,10 @@
         <v>0</v>
       </c>
       <c r="AE106" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AF106" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG106" t="n">
         <v>0</v>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Q107" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R107" t="n">
-        <v>0</v>
+        <v>7.25</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="Q109" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="R109" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -22024,12 +22024,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22212,7 +22212,7 @@
         <v>0</v>
       </c>
       <c r="BI110" s="3" t="n">
-        <v>46166.6875</v>
+        <v>46166.66666666666</v>
       </c>
     </row>
     <row r="111">
@@ -22221,12 +22221,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q111" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="BI111" s="3" t="n">
-        <v>46166.6875</v>
+        <v>46166.66666666666</v>
       </c>
     </row>
     <row r="112">
@@ -22418,7 +22418,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22606,7 +22606,7 @@
         <v>0</v>
       </c>
       <c r="BI112" s="3" t="n">
-        <v>46166.6875</v>
+        <v>46166.66666666666</v>
       </c>
     </row>
     <row r="113">
@@ -22615,12 +22615,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q113" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="R113" t="n">
-        <v>0</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22803,7 +22803,7 @@
         <v>0</v>
       </c>
       <c r="BI113" s="3" t="n">
-        <v>46166.6875</v>
+        <v>46166.66666666666</v>
       </c>
     </row>
     <row r="114">
@@ -22812,27 +22812,27 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23000,7 +23000,7 @@
         <v>0</v>
       </c>
       <c r="BI114" s="3" t="n">
-        <v>46166.6875</v>
+        <v>46166.66666666666</v>
       </c>
     </row>
     <row r="115">
@@ -23009,7 +23009,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23197,7 +23197,7 @@
         <v>0</v>
       </c>
       <c r="BI115" s="3" t="n">
-        <v>46166.70833333334</v>
+        <v>46166.66666666666</v>
       </c>
     </row>
     <row r="116">
@@ -23206,12 +23206,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q116" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="R116" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23304,10 +23304,10 @@
         <v>0</v>
       </c>
       <c r="AE116" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF116" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG116" t="n">
         <v>0</v>
@@ -23394,7 +23394,7 @@
         <v>0</v>
       </c>
       <c r="BI116" s="3" t="n">
-        <v>46166.70833333334</v>
+        <v>46166.66666666666</v>
       </c>
     </row>
     <row r="117">
@@ -23403,12 +23403,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23591,7 +23591,7 @@
         <v>0</v>
       </c>
       <c r="BI117" s="3" t="n">
-        <v>46166.70833333334</v>
+        <v>46166.6875</v>
       </c>
     </row>
     <row r="118">
@@ -23600,12 +23600,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q118" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R118" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23788,7 +23788,7 @@
         <v>0</v>
       </c>
       <c r="BI118" s="3" t="n">
-        <v>46166.70833333334</v>
+        <v>46166.6875</v>
       </c>
     </row>
     <row r="119">
@@ -23797,12 +23797,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Q119" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R119" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23985,7 +23985,7 @@
         <v>0</v>
       </c>
       <c r="BI119" s="3" t="n">
-        <v>46166.72916666666</v>
+        <v>46166.6875</v>
       </c>
     </row>
     <row r="120">
@@ -23994,12 +23994,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24182,7 +24182,7 @@
         <v>0</v>
       </c>
       <c r="BI120" s="3" t="n">
-        <v>46166.75</v>
+        <v>46166.6875</v>
       </c>
     </row>
     <row r="121">
@@ -24191,12 +24191,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24379,7 +24379,7 @@
         <v>0</v>
       </c>
       <c r="BI121" s="3" t="n">
-        <v>46166.75</v>
+        <v>46166.6875</v>
       </c>
     </row>
     <row r="122">
@@ -24388,12 +24388,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24576,7 +24576,7 @@
         <v>0</v>
       </c>
       <c r="BI122" s="3" t="n">
-        <v>46166.75</v>
+        <v>46166.70833333334</v>
       </c>
     </row>
     <row r="123">
@@ -24585,12 +24585,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="Q123" t="n">
-        <v>3.04</v>
+        <v>2.75</v>
       </c>
       <c r="R123" t="n">
-        <v>3.12</v>
+        <v>3.26</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24773,7 +24773,7 @@
         <v>0</v>
       </c>
       <c r="BI123" s="3" t="n">
-        <v>46166.75</v>
+        <v>46166.70833333334</v>
       </c>
     </row>
     <row r="124">
@@ -24782,12 +24782,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Q124" t="n">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="R124" t="n">
-        <v>6.19</v>
+        <v>0</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24886,10 +24886,10 @@
         <v>0</v>
       </c>
       <c r="AG124" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH124" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI124" t="n">
         <v>0</v>
@@ -24970,7 +24970,7 @@
         <v>0</v>
       </c>
       <c r="BI124" s="3" t="n">
-        <v>46166.75</v>
+        <v>46166.70833333334</v>
       </c>
     </row>
     <row r="125">
@@ -24979,12 +24979,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25167,7 +25167,7 @@
         <v>0</v>
       </c>
       <c r="BI125" s="3" t="n">
-        <v>46166.75</v>
+        <v>46166.70833333334</v>
       </c>
     </row>
     <row r="126">
@@ -25176,12 +25176,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25229,13 +25229,13 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q126" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R126" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -25364,7 +25364,7 @@
         <v>0</v>
       </c>
       <c r="BI126" s="3" t="n">
-        <v>46166.76041666666</v>
+        <v>46166.72916666666</v>
       </c>
     </row>
     <row r="127">
@@ -25373,12 +25373,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q127" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R127" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25471,10 +25471,10 @@
         <v>0</v>
       </c>
       <c r="AE127" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF127" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG127" t="n">
         <v>0</v>
@@ -25561,7 +25561,7 @@
         <v>0</v>
       </c>
       <c r="BI127" s="3" t="n">
-        <v>46166.77083333334</v>
+        <v>46166.75</v>
       </c>
     </row>
     <row r="128">
@@ -25570,12 +25570,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q128" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R128" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25758,7 +25758,7 @@
         <v>0</v>
       </c>
       <c r="BI128" s="3" t="n">
-        <v>46166.77083333334</v>
+        <v>46166.75</v>
       </c>
     </row>
     <row r="129">
@@ -25767,12 +25767,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>2.13</v>
+        <v>1.51</v>
       </c>
       <c r="Q129" t="n">
-        <v>2.73</v>
+        <v>4.84</v>
       </c>
       <c r="R129" t="n">
-        <v>3.79</v>
+        <v>6.19</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -25871,10 +25871,10 @@
         <v>0</v>
       </c>
       <c r="AG129" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH129" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI129" t="n">
         <v>0</v>
@@ -25955,7 +25955,7 @@
         <v>0</v>
       </c>
       <c r="BI129" s="3" t="n">
-        <v>46166.79166666666</v>
+        <v>46166.75</v>
       </c>
     </row>
     <row r="130">
@@ -25964,12 +25964,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26017,13 +26017,13 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q130" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R130" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="S130" t="n">
         <v>0</v>
@@ -26152,7 +26152,7 @@
         <v>0</v>
       </c>
       <c r="BI130" s="3" t="n">
-        <v>46166.79166666666</v>
+        <v>46166.75</v>
       </c>
     </row>
     <row r="131">
@@ -26161,12 +26161,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26349,7 +26349,7 @@
         <v>0</v>
       </c>
       <c r="BI131" s="3" t="n">
-        <v>46166.79166666666</v>
+        <v>46166.75</v>
       </c>
     </row>
     <row r="132">
@@ -26358,12 +26358,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26546,7 +26546,7 @@
         <v>0</v>
       </c>
       <c r="BI132" s="3" t="n">
-        <v>46166.83333333334</v>
+        <v>46166.75</v>
       </c>
     </row>
     <row r="133">
@@ -26555,12 +26555,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26743,7 +26743,7 @@
         <v>0</v>
       </c>
       <c r="BI133" s="3" t="n">
-        <v>46166.83333333334</v>
+        <v>46166.76041666666</v>
       </c>
     </row>
     <row r="134">
@@ -26752,12 +26752,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q134" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R134" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -26940,7 +26940,7 @@
         <v>0</v>
       </c>
       <c r="BI134" s="3" t="n">
-        <v>46166.83333333334</v>
+        <v>46166.77083333334</v>
       </c>
     </row>
     <row r="135">
@@ -26949,12 +26949,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>1.43</v>
+        <v>2.06</v>
       </c>
       <c r="Q135" t="n">
-        <v>5.24</v>
+        <v>3.32</v>
       </c>
       <c r="R135" t="n">
-        <v>7.08</v>
+        <v>3.49</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -27047,16 +27047,16 @@
         <v>0</v>
       </c>
       <c r="AE135" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF135" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG135" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH135" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI135" t="n">
         <v>0</v>
@@ -27137,7 +27137,7 @@
         <v>0</v>
       </c>
       <c r="BI135" s="3" t="n">
-        <v>46166.83333333334</v>
+        <v>46166.77083333334</v>
       </c>
     </row>
     <row r="136">
@@ -27146,12 +27146,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q136" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="R136" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27334,7 +27334,7 @@
         <v>0</v>
       </c>
       <c r="BI136" s="3" t="n">
-        <v>46166.83333333334</v>
+        <v>46166.79166666666</v>
       </c>
     </row>
     <row r="137">
@@ -27343,12 +27343,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27396,13 +27396,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q137" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="R137" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -27531,7 +27531,7 @@
         <v>0</v>
       </c>
       <c r="BI137" s="3" t="n">
-        <v>46166.84027777778</v>
+        <v>46166.79166666666</v>
       </c>
     </row>
     <row r="138">
@@ -27540,12 +27540,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q138" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="R138" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -27638,10 +27638,10 @@
         <v>0</v>
       </c>
       <c r="AE138" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF138" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG138" t="n">
         <v>0</v>
@@ -27728,7 +27728,7 @@
         <v>0</v>
       </c>
       <c r="BI138" s="3" t="n">
-        <v>46166.85416666666</v>
+        <v>46166.79166666666</v>
       </c>
     </row>
     <row r="139">
@@ -27737,12 +27737,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27790,13 +27790,13 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Q139" t="n">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="R139" t="n">
-        <v>0</v>
+        <v>7.08</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -27841,10 +27841,10 @@
         <v>0</v>
       </c>
       <c r="AG139" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH139" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI139" t="n">
         <v>0</v>
@@ -27925,7 +27925,7 @@
         <v>0</v>
       </c>
       <c r="BI139" s="3" t="n">
-        <v>46166.85416666666</v>
+        <v>46166.83333333334</v>
       </c>
     </row>
     <row r="140">
@@ -27934,12 +27934,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q140" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R140" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28122,7 +28122,7 @@
         <v>0</v>
       </c>
       <c r="BI140" s="3" t="n">
-        <v>46166.85416666666</v>
+        <v>46166.83333333334</v>
       </c>
     </row>
     <row r="141">
@@ -28131,12 +28131,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28319,7 +28319,7 @@
         <v>0</v>
       </c>
       <c r="BI141" s="3" t="n">
-        <v>46166.875</v>
+        <v>46166.83333333334</v>
       </c>
     </row>
     <row r="142">
@@ -28328,12 +28328,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28516,7 +28516,7 @@
         <v>0</v>
       </c>
       <c r="BI142" s="3" t="n">
-        <v>46166.875</v>
+        <v>46166.83333333334</v>
       </c>
     </row>
     <row r="143">
@@ -28525,12 +28525,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28578,141 +28578,1520 @@
         </is>
       </c>
       <c r="P143" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI143" s="3" t="n">
+        <v>46166.83333333334</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Delfin SC</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="G144" t="n">
+        <v>0</v>
+      </c>
+      <c r="H144" t="n">
+        <v>0</v>
+      </c>
+      <c r="I144" t="n">
+        <v>0</v>
+      </c>
+      <c r="J144" t="n">
+        <v>0</v>
+      </c>
+      <c r="K144" t="n">
+        <v>0</v>
+      </c>
+      <c r="L144" t="n">
+        <v>0</v>
+      </c>
+      <c r="M144" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N144" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P144" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Q144" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="R144" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="S144" t="n">
+        <v>0</v>
+      </c>
+      <c r="T144" t="n">
+        <v>0</v>
+      </c>
+      <c r="U144" t="n">
+        <v>0</v>
+      </c>
+      <c r="V144" t="n">
+        <v>0</v>
+      </c>
+      <c r="W144" t="n">
+        <v>0</v>
+      </c>
+      <c r="X144" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y144" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ144" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA144" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB144" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC144" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD144" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE144" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF144" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG144" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH144" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI144" s="3" t="n">
+        <v>46166.84027777778</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Operário PR</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Criciúma</t>
+        </is>
+      </c>
+      <c r="G145" t="n">
+        <v>0</v>
+      </c>
+      <c r="H145" t="n">
+        <v>0</v>
+      </c>
+      <c r="I145" t="n">
+        <v>0</v>
+      </c>
+      <c r="J145" t="n">
+        <v>0</v>
+      </c>
+      <c r="K145" t="n">
+        <v>0</v>
+      </c>
+      <c r="L145" t="n">
+        <v>0</v>
+      </c>
+      <c r="M145" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N145" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P145" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q145" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="R145" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="S145" t="n">
+        <v>0</v>
+      </c>
+      <c r="T145" t="n">
+        <v>0</v>
+      </c>
+      <c r="U145" t="n">
+        <v>0</v>
+      </c>
+      <c r="V145" t="n">
+        <v>0</v>
+      </c>
+      <c r="W145" t="n">
+        <v>0</v>
+      </c>
+      <c r="X145" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y145" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE145" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AF145" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH145" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI145" s="3" t="n">
+        <v>46166.85416666666</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Oriente Petrolero</t>
+        </is>
+      </c>
+      <c r="G146" t="n">
+        <v>0</v>
+      </c>
+      <c r="H146" t="n">
+        <v>0</v>
+      </c>
+      <c r="I146" t="n">
+        <v>0</v>
+      </c>
+      <c r="J146" t="n">
+        <v>0</v>
+      </c>
+      <c r="K146" t="n">
+        <v>0</v>
+      </c>
+      <c r="L146" t="n">
+        <v>0</v>
+      </c>
+      <c r="M146" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N146" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P146" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q146" t="n">
+        <v>0</v>
+      </c>
+      <c r="R146" t="n">
+        <v>0</v>
+      </c>
+      <c r="S146" t="n">
+        <v>0</v>
+      </c>
+      <c r="T146" t="n">
+        <v>0</v>
+      </c>
+      <c r="U146" t="n">
+        <v>0</v>
+      </c>
+      <c r="V146" t="n">
+        <v>0</v>
+      </c>
+      <c r="W146" t="n">
+        <v>0</v>
+      </c>
+      <c r="X146" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y146" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ146" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA146" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB146" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC146" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD146" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE146" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF146" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG146" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH146" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI146" s="3" t="n">
+        <v>46166.85416666666</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Vasco da Gama</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Bragantino</t>
+        </is>
+      </c>
+      <c r="G147" t="n">
+        <v>0</v>
+      </c>
+      <c r="H147" t="n">
+        <v>0</v>
+      </c>
+      <c r="I147" t="n">
+        <v>0</v>
+      </c>
+      <c r="J147" t="n">
+        <v>0</v>
+      </c>
+      <c r="K147" t="n">
+        <v>0</v>
+      </c>
+      <c r="L147" t="n">
+        <v>0</v>
+      </c>
+      <c r="M147" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N147" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P147" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Q147" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="R147" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="S147" t="n">
+        <v>0</v>
+      </c>
+      <c r="T147" t="n">
+        <v>0</v>
+      </c>
+      <c r="U147" t="n">
+        <v>0</v>
+      </c>
+      <c r="V147" t="n">
+        <v>0</v>
+      </c>
+      <c r="W147" t="n">
+        <v>0</v>
+      </c>
+      <c r="X147" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y147" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ147" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA147" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB147" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC147" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD147" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE147" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF147" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG147" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH147" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI147" s="3" t="n">
+        <v>46166.85416666666</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Chile Primera B</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>San Luis</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="G148" t="n">
+        <v>0</v>
+      </c>
+      <c r="H148" t="n">
+        <v>0</v>
+      </c>
+      <c r="I148" t="n">
+        <v>0</v>
+      </c>
+      <c r="J148" t="n">
+        <v>0</v>
+      </c>
+      <c r="K148" t="n">
+        <v>0</v>
+      </c>
+      <c r="L148" t="n">
+        <v>0</v>
+      </c>
+      <c r="M148" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N148" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P148" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q148" t="n">
+        <v>0</v>
+      </c>
+      <c r="R148" t="n">
+        <v>0</v>
+      </c>
+      <c r="S148" t="n">
+        <v>0</v>
+      </c>
+      <c r="T148" t="n">
+        <v>0</v>
+      </c>
+      <c r="U148" t="n">
+        <v>0</v>
+      </c>
+      <c r="V148" t="n">
+        <v>0</v>
+      </c>
+      <c r="W148" t="n">
+        <v>0</v>
+      </c>
+      <c r="X148" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y148" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ148" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA148" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB148" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC148" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD148" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE148" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF148" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG148" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH148" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI148" s="3" t="n">
+        <v>46166.875</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Columbus Crew II</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Toronto II</t>
+        </is>
+      </c>
+      <c r="G149" t="n">
+        <v>0</v>
+      </c>
+      <c r="H149" t="n">
+        <v>0</v>
+      </c>
+      <c r="I149" t="n">
+        <v>0</v>
+      </c>
+      <c r="J149" t="n">
+        <v>0</v>
+      </c>
+      <c r="K149" t="n">
+        <v>0</v>
+      </c>
+      <c r="L149" t="n">
+        <v>0</v>
+      </c>
+      <c r="M149" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N149" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P149" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q149" t="n">
+        <v>0</v>
+      </c>
+      <c r="R149" t="n">
+        <v>0</v>
+      </c>
+      <c r="S149" t="n">
+        <v>0</v>
+      </c>
+      <c r="T149" t="n">
+        <v>0</v>
+      </c>
+      <c r="U149" t="n">
+        <v>0</v>
+      </c>
+      <c r="V149" t="n">
+        <v>0</v>
+      </c>
+      <c r="W149" t="n">
+        <v>0</v>
+      </c>
+      <c r="X149" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y149" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY149" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ149" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA149" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB149" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC149" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD149" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE149" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF149" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG149" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH149" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI149" s="3" t="n">
+        <v>46166.875</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Los Angeles FC</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Seattle Sounders</t>
+        </is>
+      </c>
+      <c r="G150" t="n">
+        <v>0</v>
+      </c>
+      <c r="H150" t="n">
+        <v>0</v>
+      </c>
+      <c r="I150" t="n">
+        <v>0</v>
+      </c>
+      <c r="J150" t="n">
+        <v>0</v>
+      </c>
+      <c r="K150" t="n">
+        <v>0</v>
+      </c>
+      <c r="L150" t="n">
+        <v>0</v>
+      </c>
+      <c r="M150" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N150" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P150" t="n">
         <v>2</v>
       </c>
-      <c r="Q143" t="n">
+      <c r="Q150" t="n">
         <v>3.83</v>
       </c>
-      <c r="R143" t="n">
+      <c r="R150" t="n">
         <v>3.72</v>
       </c>
-      <c r="S143" t="n">
-        <v>0</v>
-      </c>
-      <c r="T143" t="n">
-        <v>0</v>
-      </c>
-      <c r="U143" t="n">
-        <v>0</v>
-      </c>
-      <c r="V143" t="n">
-        <v>0</v>
-      </c>
-      <c r="W143" t="n">
-        <v>0</v>
-      </c>
-      <c r="X143" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y143" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE143" t="n">
+      <c r="S150" t="n">
+        <v>0</v>
+      </c>
+      <c r="T150" t="n">
+        <v>0</v>
+      </c>
+      <c r="U150" t="n">
+        <v>0</v>
+      </c>
+      <c r="V150" t="n">
+        <v>0</v>
+      </c>
+      <c r="W150" t="n">
+        <v>0</v>
+      </c>
+      <c r="X150" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y150" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE150" t="n">
         <v>1.62</v>
       </c>
-      <c r="AF143" t="n">
+      <c r="AF150" t="n">
         <v>2.15</v>
       </c>
-      <c r="AG143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY143" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ143" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA143" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB143" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC143" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD143" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE143" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF143" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG143" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH143" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI143" s="3" t="n">
+      <c r="AG150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ150" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA150" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB150" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC150" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD150" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE150" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF150" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG150" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH150" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI150" s="3" t="n">
         <v>46166.91666666666</v>
       </c>
     </row>

--- a/jogos_2026-05-24.xlsx
+++ b/jogos_2026-05-24.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.97</v>
+        <v>1.29</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.18</v>
+        <v>4.95</v>
       </c>
       <c r="R9" t="n">
-        <v>3.61</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.29</v>
+        <v>1.97</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.95</v>
+        <v>3.18</v>
       </c>
       <c r="R10" t="n">
-        <v>8.199999999999999</v>
+        <v>3.61</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="R25" t="n">
-        <v>5.14</v>
+        <v>3.8</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AL29" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AN29" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AS29" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AT29" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AU29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AV29" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BA29" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BC29" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="BD29" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AR30" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AS30" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AY30" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BA30" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="BB30" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BF30" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.92</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6959,10 +6959,10 @@
         <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>4.92</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7156,10 +7156,10 @@
         <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.63</v>
+        <v>1.28</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.96</v>
+        <v>5.41</v>
       </c>
       <c r="R36" t="n">
-        <v>4.85</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,10 +7696,10 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="Q37" t="n">
-        <v>5</v>
+        <v>4.58</v>
       </c>
       <c r="R37" t="n">
         <v>6</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.3</v>
+        <v>1.93</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.6</v>
+        <v>3.99</v>
       </c>
       <c r="R38" t="n">
-        <v>2.6</v>
+        <v>3.22</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.42</v>
+        <v>2.3</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.58</v>
+        <v>3.6</v>
       </c>
       <c r="R42" t="n">
-        <v>6</v>
+        <v>2.6</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.93</v>
+        <v>3</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.99</v>
+        <v>3.66</v>
       </c>
       <c r="R44" t="n">
-        <v>3.22</v>
+        <v>2.13</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.28</v>
+        <v>1.63</v>
       </c>
       <c r="Q45" t="n">
-        <v>5.41</v>
+        <v>3.96</v>
       </c>
       <c r="R45" t="n">
-        <v>8.039999999999999</v>
+        <v>4.85</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>5.57</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>7.02</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.55</v>
+        <v>2.52</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.54</v>
+        <v>3.6</v>
       </c>
       <c r="R47" t="n">
-        <v>6.7</v>
+        <v>2.94</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.25</v>
+        <v>7</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.73</v>
+        <v>4.43</v>
       </c>
       <c r="R48" t="n">
-        <v>3.31</v>
+        <v>1.55</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.52</v>
+        <v>2.29</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="R49" t="n">
-        <v>2.94</v>
+        <v>2.83</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>7</v>
+        <v>2.54</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.43</v>
+        <v>3.62</v>
       </c>
       <c r="R50" t="n">
-        <v>1.55</v>
+        <v>2.89</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>5.57</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>7.02</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.8</v>
+        <v>1.55</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.81</v>
+        <v>4.54</v>
       </c>
       <c r="R52" t="n">
-        <v>2.53</v>
+        <v>6.7</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.54</v>
+        <v>2.25</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.62</v>
+        <v>3.73</v>
       </c>
       <c r="R54" t="n">
-        <v>2.89</v>
+        <v>3.31</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.82</v>
+        <v>3.81</v>
       </c>
       <c r="R56" t="n">
-        <v>2.68</v>
+        <v>2.53</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,7 +11484,7 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AF56" t="n">
         <v>2.2</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12863,10 +12863,10 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF63" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,22 +13755,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,133 +13803,133 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>8.25</v>
+        <v>1.53</v>
       </c>
       <c r="Q68" t="n">
-        <v>5.37</v>
+        <v>4.2</v>
       </c>
       <c r="R68" t="n">
-        <v>1.35</v>
+        <v>6.75</v>
       </c>
       <c r="S68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T68" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U68" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V68" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W68" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="X68" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Y68" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z68" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB68" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC68" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AD68" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="AE68" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF68" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG68" t="n">
-        <v>1.95</v>
+        <v>3.12</v>
       </c>
       <c r="AH68" t="n">
-        <v>1.85</v>
+        <v>1.31</v>
       </c>
       <c r="AI68" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AJ68" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL68" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AM68" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN68" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AO68" t="n">
         <v>0</v>
       </c>
       <c r="AP68" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ68" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AR68" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AS68" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AT68" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AU68" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AV68" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AW68" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AX68" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AY68" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ68" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BA68" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BB68" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BC68" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD68" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE68" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BF68" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG68" t="n">
         <v>0</v>
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,133 +14197,133 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1.53</v>
+        <v>8.25</v>
       </c>
       <c r="Q70" t="n">
-        <v>4.2</v>
+        <v>5.37</v>
       </c>
       <c r="R70" t="n">
-        <v>6.75</v>
+        <v>1.35</v>
       </c>
       <c r="S70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T70" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U70" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="V70" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W70" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="X70" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z70" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA70" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB70" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC70" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AD70" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF70" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG70" t="n">
-        <v>3.12</v>
+        <v>1.95</v>
       </c>
       <c r="AH70" t="n">
-        <v>1.31</v>
+        <v>1.85</v>
       </c>
       <c r="AI70" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AJ70" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL70" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AM70" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN70" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="AO70" t="n">
         <v>0</v>
       </c>
       <c r="AP70" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ70" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AR70" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AS70" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AT70" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AU70" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AV70" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AW70" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AX70" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AY70" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AZ70" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BA70" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BB70" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BC70" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BD70" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BE70" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BF70" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>3.19</v>
+        <v>1.53</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.19</v>
+        <v>4.33</v>
       </c>
       <c r="R71" t="n">
-        <v>2.41</v>
+        <v>6.19</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="Q72" t="n">
-        <v>4.37</v>
+        <v>4.46</v>
       </c>
       <c r="R72" t="n">
-        <v>5.41</v>
+        <v>6.22</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF72" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="Q75" t="n">
-        <v>4.33</v>
+        <v>4.37</v>
       </c>
       <c r="R75" t="n">
-        <v>6.19</v>
+        <v>5.41</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.59</v>
+        <v>4.15</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.42</v>
+        <v>3.73</v>
       </c>
       <c r="R77" t="n">
-        <v>2.75</v>
+        <v>1.88</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15818,10 +15818,10 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF78" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG78" t="n">
         <v>0</v>
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1.67</v>
+        <v>2.59</v>
       </c>
       <c r="Q79" t="n">
-        <v>4.17</v>
+        <v>3.42</v>
       </c>
       <c r="R79" t="n">
-        <v>4.94</v>
+        <v>2.75</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1.32</v>
+        <v>1.77</v>
       </c>
       <c r="Q81" t="n">
-        <v>5.88</v>
+        <v>4.07</v>
       </c>
       <c r="R81" t="n">
-        <v>8.4</v>
+        <v>4.22</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1.7</v>
+        <v>3.77</v>
       </c>
       <c r="Q82" t="n">
-        <v>4.53</v>
+        <v>4.17</v>
       </c>
       <c r="R82" t="n">
-        <v>4.32</v>
+        <v>1.86</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16612,10 +16612,10 @@
         <v>0</v>
       </c>
       <c r="AG82" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH82" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AI82" t="n">
         <v>0</v>
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>3.77</v>
+        <v>5.25</v>
       </c>
       <c r="Q83" t="n">
-        <v>4.17</v>
+        <v>4.22</v>
       </c>
       <c r="R83" t="n">
-        <v>1.86</v>
+        <v>1.63</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF83" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>1.96</v>
+        <v>1.32</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.81</v>
+        <v>5.88</v>
       </c>
       <c r="R84" t="n">
-        <v>3.73</v>
+        <v>8.4</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17000,10 +17000,10 @@
         <v>0</v>
       </c>
       <c r="AE84" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF84" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG84" t="n">
         <v>0</v>
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>4.46</v>
+        <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>6.22</v>
+        <v>0</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17197,10 +17197,10 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF85" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG85" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="Q86" t="n">
-        <v>4.07</v>
+        <v>4.53</v>
       </c>
       <c r="R86" t="n">
-        <v>4.22</v>
+        <v>4.32</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17400,10 +17400,10 @@
         <v>0</v>
       </c>
       <c r="AG86" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH86" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AI86" t="n">
         <v>0</v>
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>5.25</v>
+        <v>3.19</v>
       </c>
       <c r="Q87" t="n">
-        <v>4.22</v>
+        <v>3.19</v>
       </c>
       <c r="R87" t="n">
-        <v>1.63</v>
+        <v>2.41</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF87" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>5.21</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>5.21</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,133 +19713,133 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>1.7</v>
+        <v>5</v>
       </c>
       <c r="Q98" t="n">
-        <v>3.68</v>
+        <v>4.26</v>
       </c>
       <c r="R98" t="n">
-        <v>5.1</v>
+        <v>1.63</v>
       </c>
       <c r="S98" t="n">
-        <v>2.31</v>
+        <v>5.05</v>
       </c>
       <c r="T98" t="n">
-        <v>2.09</v>
+        <v>2.35</v>
       </c>
       <c r="U98" t="n">
-        <v>4.54</v>
+        <v>2.16</v>
       </c>
       <c r="V98" t="n">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="W98" t="n">
-        <v>2.55</v>
+        <v>3.28</v>
       </c>
       <c r="X98" t="n">
-        <v>3.34</v>
+        <v>2.53</v>
       </c>
       <c r="Y98" t="n">
-        <v>1.32</v>
+        <v>1.51</v>
       </c>
       <c r="Z98" t="n">
-        <v>8.6</v>
+        <v>5.8</v>
       </c>
       <c r="AA98" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AC98" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD98" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AE98" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF98" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AG98" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AH98" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI98" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AJ98" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK98" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AL98" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AM98" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN98" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AO98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP98" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AQ98" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AR98" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AS98" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AT98" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AU98" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AV98" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AW98" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AX98" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AY98" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AZ98" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BA98" t="n">
         <v>1.4</v>
       </c>
-      <c r="AD98" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AE98" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AF98" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AG98" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AH98" t="n">
+      <c r="BB98" t="n">
         <v>1.18</v>
       </c>
-      <c r="AI98" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AJ98" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK98" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AL98" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AM98" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN98" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AO98" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP98" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AQ98" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR98" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AS98" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AT98" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AU98" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV98" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AW98" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AX98" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AY98" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AZ98" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BA98" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BB98" t="n">
-        <v>1.33</v>
-      </c>
       <c r="BC98" t="n">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="BD98" t="n">
-        <v>3.28</v>
+        <v>4.45</v>
       </c>
       <c r="BE98" t="n">
-        <v>1.52</v>
+        <v>1.88</v>
       </c>
       <c r="BF98" t="n">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="BG98" t="n">
         <v>0</v>
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,28 +19910,28 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>7.5</v>
+        <v>1.33</v>
       </c>
       <c r="Q99" t="n">
-        <v>4.78</v>
+        <v>5.2</v>
       </c>
       <c r="R99" t="n">
-        <v>1.4</v>
+        <v>9</v>
       </c>
       <c r="S99" t="n">
-        <v>5.51</v>
+        <v>1.77</v>
       </c>
       <c r="T99" t="n">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="U99" t="n">
-        <v>1.86</v>
+        <v>8.1</v>
       </c>
       <c r="V99" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W99" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="X99" t="n">
         <v>2.59</v>
@@ -19940,100 +19940,100 @@
         <v>1.49</v>
       </c>
       <c r="Z99" t="n">
-        <v>6</v>
+        <v>6.05</v>
       </c>
       <c r="AA99" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AC99" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AD99" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AE99" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AF99" t="n">
-        <v>2.08</v>
+        <v>2.19</v>
       </c>
       <c r="AG99" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AH99" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI99" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AJ99" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK99" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AL99" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AM99" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN99" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AO99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP99" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AQ99" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR99" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AS99" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AT99" t="n">
         <v>2.85</v>
       </c>
-      <c r="AH99" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AI99" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AJ99" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK99" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AL99" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AM99" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AN99" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AO99" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP99" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AQ99" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AR99" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS99" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AT99" t="n">
-        <v>3.45</v>
-      </c>
       <c r="AU99" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="AV99" t="n">
-        <v>2.15</v>
+        <v>2.48</v>
       </c>
       <c r="AW99" t="n">
-        <v>1.7</v>
+        <v>1.92</v>
       </c>
       <c r="AX99" t="n">
-        <v>1.43</v>
+        <v>1.58</v>
       </c>
       <c r="AY99" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AZ99" t="n">
-        <v>3.1</v>
+        <v>1.2</v>
       </c>
       <c r="BA99" t="n">
-        <v>1.47</v>
+        <v>5.3</v>
       </c>
       <c r="BB99" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="BC99" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="BD99" t="n">
-        <v>4.35</v>
+        <v>4.5</v>
       </c>
       <c r="BE99" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="BF99" t="n">
         <v>1.23</v>
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,28 +20304,28 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>1.33</v>
+        <v>7.5</v>
       </c>
       <c r="Q101" t="n">
-        <v>5.2</v>
+        <v>4.78</v>
       </c>
       <c r="R101" t="n">
-        <v>9</v>
+        <v>1.4</v>
       </c>
       <c r="S101" t="n">
-        <v>1.77</v>
+        <v>5.51</v>
       </c>
       <c r="T101" t="n">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="U101" t="n">
-        <v>8.1</v>
+        <v>1.86</v>
       </c>
       <c r="V101" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W101" t="n">
-        <v>3.25</v>
+        <v>3.27</v>
       </c>
       <c r="X101" t="n">
         <v>2.59</v>
@@ -20334,100 +20334,100 @@
         <v>1.49</v>
       </c>
       <c r="Z101" t="n">
-        <v>6.05</v>
+        <v>6</v>
       </c>
       <c r="AA101" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AB101" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC101" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AD101" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AE101" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF101" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AG101" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AH101" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AI101" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AJ101" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK101" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AL101" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AM101" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AN101" t="n">
         <v>1.09</v>
       </c>
-      <c r="AB101" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC101" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AD101" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE101" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AF101" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AG101" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="AH101" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI101" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AJ101" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK101" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AL101" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AM101" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AN101" t="n">
-        <v>3.44</v>
-      </c>
       <c r="AO101" t="n">
         <v>0</v>
       </c>
       <c r="AP101" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="AQ101" t="n">
-        <v>1.46</v>
+        <v>1.61</v>
       </c>
       <c r="AR101" t="n">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="AS101" t="n">
-        <v>2.18</v>
+        <v>2.6</v>
       </c>
       <c r="AT101" t="n">
-        <v>2.85</v>
+        <v>3.45</v>
       </c>
       <c r="AU101" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="AV101" t="n">
-        <v>2.48</v>
+        <v>2.15</v>
       </c>
       <c r="AW101" t="n">
-        <v>1.92</v>
+        <v>1.7</v>
       </c>
       <c r="AX101" t="n">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="AY101" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AZ101" t="n">
-        <v>1.2</v>
+        <v>3.1</v>
       </c>
       <c r="BA101" t="n">
-        <v>5.3</v>
+        <v>1.47</v>
       </c>
       <c r="BB101" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="BC101" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="BD101" t="n">
-        <v>4.5</v>
+        <v>4.35</v>
       </c>
       <c r="BE101" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="BF101" t="n">
         <v>1.23</v>
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,133 +20501,133 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>5</v>
+        <v>1.7</v>
       </c>
       <c r="Q102" t="n">
-        <v>4.26</v>
+        <v>3.68</v>
       </c>
       <c r="R102" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="S102" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="T102" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="U102" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="V102" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="W102" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="X102" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="Y102" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z102" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AA102" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB102" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC102" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD102" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AE102" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AF102" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG102" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AH102" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI102" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AJ102" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK102" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AL102" t="n">
         <v>1.63</v>
       </c>
-      <c r="S102" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="T102" t="n">
+      <c r="AM102" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN102" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AO102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP102" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ102" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR102" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AS102" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AT102" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU102" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV102" t="n">
         <v>2.35</v>
       </c>
-      <c r="U102" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="V102" t="n">
+      <c r="AW102" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AX102" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AY102" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AZ102" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BA102" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BB102" t="n">
         <v>1.33</v>
       </c>
-      <c r="W102" t="n">
+      <c r="BC102" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BD102" t="n">
         <v>3.28</v>
       </c>
-      <c r="X102" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="Y102" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Z102" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AA102" t="n">
+      <c r="BE102" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BF102" t="n">
         <v>1.1</v>
-      </c>
-      <c r="AB102" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC102" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AD102" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AE102" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AF102" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AG102" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AH102" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AI102" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AJ102" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK102" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AL102" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AM102" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN102" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AO102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP102" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AQ102" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AR102" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AS102" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AT102" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AU102" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AV102" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AW102" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AX102" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AY102" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AZ102" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BA102" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BB102" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC102" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BD102" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="BE102" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="BF102" t="n">
-        <v>1.24</v>
       </c>
       <c r="BG102" t="n">
         <v>0</v>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="Q103" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>1.77</v>
+        <v>1.51</v>
       </c>
       <c r="Q106" t="n">
-        <v>3.32</v>
+        <v>3.5</v>
       </c>
       <c r="R106" t="n">
-        <v>4.83</v>
+        <v>7.25</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21334,10 +21334,10 @@
         <v>0</v>
       </c>
       <c r="AE106" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AF106" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AG106" t="n">
         <v>0</v>
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>1.51</v>
+        <v>2.29</v>
       </c>
       <c r="Q107" t="n">
-        <v>3.5</v>
+        <v>2.76</v>
       </c>
       <c r="R107" t="n">
-        <v>7.25</v>
+        <v>3.61</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q109" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="R109" t="n">
-        <v>0</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>2.29</v>
+        <v>2.8</v>
       </c>
       <c r="Q111" t="n">
-        <v>2.76</v>
+        <v>3.27</v>
       </c>
       <c r="R111" t="n">
-        <v>3.61</v>
+        <v>2.64</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22319,10 +22319,10 @@
         <v>0</v>
       </c>
       <c r="AE111" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF111" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG111" t="n">
         <v>0</v>
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>1.32</v>
+        <v>2.29</v>
       </c>
       <c r="Q113" t="n">
-        <v>5.45</v>
+        <v>2.69</v>
       </c>
       <c r="R113" t="n">
-        <v>9.949999999999999</v>
+        <v>3.43</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22817,22 +22817,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>2.8</v>
+        <v>1.77</v>
       </c>
       <c r="Q116" t="n">
-        <v>3.27</v>
+        <v>3.32</v>
       </c>
       <c r="R116" t="n">
-        <v>2.64</v>
+        <v>4.83</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23304,10 +23304,10 @@
         <v>0</v>
       </c>
       <c r="AE116" t="n">
-        <v>2.05</v>
+        <v>2.37</v>
       </c>
       <c r="AF116" t="n">
-        <v>1.8</v>
+        <v>1.51</v>
       </c>
       <c r="AG116" t="n">
         <v>0</v>
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q123" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q125" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R125" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Q128" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="R128" t="n">
-        <v>0</v>
+        <v>6.19</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25674,10 +25674,10 @@
         <v>0</v>
       </c>
       <c r="AG128" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH128" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI128" t="n">
         <v>0</v>
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Q129" t="n">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="R129" t="n">
-        <v>6.19</v>
+        <v>0</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -25871,10 +25871,10 @@
         <v>0</v>
       </c>
       <c r="AG129" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH129" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI129" t="n">
         <v>0</v>
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26017,13 +26017,13 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q130" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="R130" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="S130" t="n">
         <v>0</v>
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q132" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R132" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="Q134" t="n">
-        <v>3.38</v>
+        <v>3.32</v>
       </c>
       <c r="R134" t="n">
-        <v>4.32</v>
+        <v>3.49</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -26850,10 +26850,10 @@
         <v>0</v>
       </c>
       <c r="AE134" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF134" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG134" t="n">
         <v>0</v>
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="Q135" t="n">
-        <v>3.32</v>
+        <v>3.38</v>
       </c>
       <c r="R135" t="n">
-        <v>3.49</v>
+        <v>4.32</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -27047,10 +27047,10 @@
         <v>0</v>
       </c>
       <c r="AE135" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF135" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG135" t="n">
         <v>0</v>
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q136" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="R136" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q138" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="R138" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G142" t="n">

--- a/jogos_2026-05-24.xlsx
+++ b/jogos_2026-05-24.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.29</v>
+        <v>1.97</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.95</v>
+        <v>3.18</v>
       </c>
       <c r="R9" t="n">
-        <v>8.199999999999999</v>
+        <v>3.61</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.97</v>
+        <v>1.29</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.18</v>
+        <v>4.95</v>
       </c>
       <c r="R10" t="n">
-        <v>3.61</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AR29" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AS29" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AU29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV29" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AW29" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AX29" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AY29" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BA29" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="BB29" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BC29" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BD29" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE29" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BF29" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AN30" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AS30" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AT30" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AU30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AV30" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BA30" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BC30" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="BD30" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.92</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7156,10 +7156,10 @@
         <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>4.92</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7353,10 +7353,10 @@
         <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>5.41</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>8.039999999999999</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.42</v>
+        <v>2.3</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.58</v>
+        <v>3.6</v>
       </c>
       <c r="R37" t="n">
-        <v>6</v>
+        <v>2.6</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.93</v>
+        <v>1.28</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.99</v>
+        <v>5.41</v>
       </c>
       <c r="R38" t="n">
-        <v>3.22</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.53</v>
+        <v>3.66</v>
       </c>
       <c r="R40" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.93</v>
+        <v>1.78</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.83</v>
+        <v>1.99</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.3</v>
+        <v>1.42</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.6</v>
+        <v>4.58</v>
       </c>
       <c r="R42" t="n">
-        <v>2.6</v>
+        <v>6</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>3</v>
+        <v>1.63</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.66</v>
+        <v>3.96</v>
       </c>
       <c r="R44" t="n">
-        <v>2.13</v>
+        <v>4.85</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.63</v>
+        <v>2.95</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.96</v>
+        <v>3.53</v>
       </c>
       <c r="R45" t="n">
-        <v>4.85</v>
+        <v>2.2</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>7</v>
+        <v>2.63</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.43</v>
+        <v>3.82</v>
       </c>
       <c r="R48" t="n">
-        <v>1.55</v>
+        <v>2.68</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.29</v>
+        <v>7</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.4</v>
+        <v>4.43</v>
       </c>
       <c r="R49" t="n">
-        <v>2.83</v>
+        <v>1.55</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>5.57</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>7.02</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>4.54</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>5.57</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>7.02</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>3.82</v>
+        <v>2.52</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.82</v>
+        <v>3.6</v>
       </c>
       <c r="R59" t="n">
-        <v>2.03</v>
+        <v>2.94</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12075,10 +12075,10 @@
         <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF59" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG59" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2.63</v>
+        <v>1.55</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.82</v>
+        <v>4.54</v>
       </c>
       <c r="R63" t="n">
-        <v>2.68</v>
+        <v>6.7</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12863,10 +12863,10 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF63" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,22 +13361,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>5.37</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13460,10 +13460,10 @@
         <v>0</v>
       </c>
       <c r="AG66" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH66" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI66" t="n">
         <v>0</v>
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>5.37</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14248,10 +14248,10 @@
         <v>0</v>
       </c>
       <c r="AG70" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH70" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI70" t="n">
         <v>0</v>
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>6.19</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>1.52</v>
+        <v>4.15</v>
       </c>
       <c r="Q72" t="n">
-        <v>4.46</v>
+        <v>3.73</v>
       </c>
       <c r="R72" t="n">
-        <v>6.22</v>
+        <v>1.88</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF72" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>1.82</v>
+        <v>2.59</v>
       </c>
       <c r="Q73" t="n">
-        <v>4.06</v>
+        <v>3.42</v>
       </c>
       <c r="R73" t="n">
-        <v>4.06</v>
+        <v>2.75</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>6.22</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15030,10 +15030,10 @@
         <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF74" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG74" t="n">
         <v>0</v>
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="Q75" t="n">
-        <v>4.37</v>
+        <v>4.17</v>
       </c>
       <c r="R75" t="n">
-        <v>5.41</v>
+        <v>4.94</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF76" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>4.15</v>
+        <v>1.7</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.73</v>
+        <v>4.53</v>
       </c>
       <c r="R77" t="n">
-        <v>1.88</v>
+        <v>4.32</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15627,10 +15627,10 @@
         <v>0</v>
       </c>
       <c r="AG77" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH77" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AI77" t="n">
         <v>0</v>
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>1.96</v>
+        <v>3.77</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.81</v>
+        <v>4.17</v>
       </c>
       <c r="R78" t="n">
-        <v>3.73</v>
+        <v>1.86</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15818,10 +15818,10 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF78" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG78" t="n">
         <v>0</v>
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1.67</v>
+        <v>3.19</v>
       </c>
       <c r="Q80" t="n">
-        <v>4.17</v>
+        <v>3.19</v>
       </c>
       <c r="R80" t="n">
-        <v>4.94</v>
+        <v>2.41</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1.77</v>
+        <v>1.53</v>
       </c>
       <c r="Q81" t="n">
-        <v>4.07</v>
+        <v>4.33</v>
       </c>
       <c r="R81" t="n">
-        <v>4.22</v>
+        <v>6.19</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>3.77</v>
+        <v>1.32</v>
       </c>
       <c r="Q82" t="n">
-        <v>4.17</v>
+        <v>5.88</v>
       </c>
       <c r="R82" t="n">
-        <v>1.86</v>
+        <v>8.4</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>5.25</v>
+        <v>1.82</v>
       </c>
       <c r="Q83" t="n">
-        <v>4.22</v>
+        <v>4.06</v>
       </c>
       <c r="R83" t="n">
-        <v>1.63</v>
+        <v>4.06</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF83" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>1.32</v>
+        <v>1.77</v>
       </c>
       <c r="Q84" t="n">
-        <v>5.88</v>
+        <v>4.07</v>
       </c>
       <c r="R84" t="n">
-        <v>8.4</v>
+        <v>4.22</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>1.7</v>
+        <v>1.96</v>
       </c>
       <c r="Q86" t="n">
-        <v>4.53</v>
+        <v>3.81</v>
       </c>
       <c r="R86" t="n">
-        <v>4.32</v>
+        <v>3.73</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,16 +17394,16 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF86" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG86" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH86" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AI86" t="n">
         <v>0</v>
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>3.19</v>
+        <v>1.59</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.19</v>
+        <v>4.37</v>
       </c>
       <c r="R87" t="n">
-        <v>2.41</v>
+        <v>5.41</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,133 +19713,133 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>5</v>
+        <v>1.7</v>
       </c>
       <c r="Q98" t="n">
-        <v>4.26</v>
+        <v>3.68</v>
       </c>
       <c r="R98" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="S98" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="T98" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="U98" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="V98" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="W98" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="X98" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="Y98" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z98" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AA98" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB98" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC98" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD98" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AE98" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AF98" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG98" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AH98" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI98" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AJ98" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK98" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AL98" t="n">
         <v>1.63</v>
       </c>
-      <c r="S98" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="T98" t="n">
+      <c r="AM98" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN98" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AO98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP98" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ98" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR98" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AS98" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AT98" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU98" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV98" t="n">
         <v>2.35</v>
       </c>
-      <c r="U98" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="V98" t="n">
+      <c r="AW98" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AX98" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AY98" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AZ98" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BA98" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BB98" t="n">
         <v>1.33</v>
       </c>
-      <c r="W98" t="n">
+      <c r="BC98" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BD98" t="n">
         <v>3.28</v>
       </c>
-      <c r="X98" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="Y98" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Z98" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AA98" t="n">
+      <c r="BE98" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BF98" t="n">
         <v>1.1</v>
-      </c>
-      <c r="AB98" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC98" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AD98" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AE98" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AF98" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AG98" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AH98" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AI98" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AJ98" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK98" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AL98" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AM98" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN98" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AO98" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP98" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AQ98" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AR98" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AS98" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AT98" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AU98" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AV98" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AW98" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AX98" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AY98" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AZ98" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BA98" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BB98" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC98" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BD98" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="BE98" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="BF98" t="n">
-        <v>1.24</v>
       </c>
       <c r="BG98" t="n">
         <v>0</v>
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,28 +19910,28 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>1.33</v>
+        <v>7.5</v>
       </c>
       <c r="Q99" t="n">
-        <v>5.2</v>
+        <v>4.78</v>
       </c>
       <c r="R99" t="n">
-        <v>9</v>
+        <v>1.4</v>
       </c>
       <c r="S99" t="n">
-        <v>1.77</v>
+        <v>5.51</v>
       </c>
       <c r="T99" t="n">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="U99" t="n">
-        <v>8.1</v>
+        <v>1.86</v>
       </c>
       <c r="V99" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W99" t="n">
-        <v>3.25</v>
+        <v>3.27</v>
       </c>
       <c r="X99" t="n">
         <v>2.59</v>
@@ -19940,100 +19940,100 @@
         <v>1.49</v>
       </c>
       <c r="Z99" t="n">
-        <v>6.05</v>
+        <v>6</v>
       </c>
       <c r="AA99" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AB99" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC99" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AD99" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AE99" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF99" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AG99" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AH99" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AI99" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AJ99" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK99" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AL99" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AM99" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AN99" t="n">
         <v>1.09</v>
       </c>
-      <c r="AB99" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC99" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AD99" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE99" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AF99" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AG99" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="AH99" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI99" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AJ99" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK99" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AL99" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AM99" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AN99" t="n">
-        <v>3.44</v>
-      </c>
       <c r="AO99" t="n">
         <v>0</v>
       </c>
       <c r="AP99" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="AQ99" t="n">
-        <v>1.46</v>
+        <v>1.61</v>
       </c>
       <c r="AR99" t="n">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="AS99" t="n">
-        <v>2.18</v>
+        <v>2.6</v>
       </c>
       <c r="AT99" t="n">
-        <v>2.85</v>
+        <v>3.45</v>
       </c>
       <c r="AU99" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="AV99" t="n">
-        <v>2.48</v>
+        <v>2.15</v>
       </c>
       <c r="AW99" t="n">
-        <v>1.92</v>
+        <v>1.7</v>
       </c>
       <c r="AX99" t="n">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="AY99" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AZ99" t="n">
-        <v>1.2</v>
+        <v>3.1</v>
       </c>
       <c r="BA99" t="n">
-        <v>5.3</v>
+        <v>1.47</v>
       </c>
       <c r="BB99" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="BC99" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="BD99" t="n">
-        <v>4.5</v>
+        <v>4.35</v>
       </c>
       <c r="BE99" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="BF99" t="n">
         <v>1.23</v>
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,133 +20107,133 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>9.199999999999999</v>
+        <v>1.33</v>
       </c>
       <c r="Q100" t="n">
         <v>5.2</v>
       </c>
       <c r="R100" t="n">
+        <v>9</v>
+      </c>
+      <c r="S100" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="T100" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="U100" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="V100" t="n">
         <v>1.33</v>
       </c>
-      <c r="S100" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="T100" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="U100" t="n">
+      <c r="W100" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="X100" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Y100" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Z100" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AA100" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB100" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC100" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD100" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE100" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AF100" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AG100" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AH100" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI100" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AJ100" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK100" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AL100" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AM100" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN100" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AO100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP100" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AQ100" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR100" t="n">
         <v>1.77</v>
       </c>
-      <c r="V100" t="n">
+      <c r="AS100" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AT100" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AU100" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV100" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AW100" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AX100" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AY100" t="n">
         <v>1.36</v>
       </c>
-      <c r="W100" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="X100" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="Y100" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z100" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AA100" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB100" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC100" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AD100" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AE100" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AF100" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG100" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AH100" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI100" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="AJ100" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK100" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AL100" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AM100" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AN100" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AO100" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP100" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AQ100" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AR100" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AS100" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AT100" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AU100" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV100" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AW100" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AX100" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AY100" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AZ100" t="n">
-        <v>3.7</v>
+        <v>1.2</v>
       </c>
       <c r="BA100" t="n">
-        <v>1.36</v>
+        <v>5.3</v>
       </c>
       <c r="BB100" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="BC100" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="BD100" t="n">
-        <v>4.15</v>
+        <v>4.5</v>
       </c>
       <c r="BE100" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="BF100" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="BG100" t="n">
         <v>0</v>
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,133 +20304,133 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>7.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q101" t="n">
-        <v>4.78</v>
+        <v>5.2</v>
       </c>
       <c r="R101" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S101" t="n">
-        <v>5.51</v>
+        <v>8.5</v>
       </c>
       <c r="T101" t="n">
-        <v>2.28</v>
+        <v>2.47</v>
       </c>
       <c r="U101" t="n">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="V101" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="W101" t="n">
-        <v>3.27</v>
+        <v>3.1</v>
       </c>
       <c r="X101" t="n">
-        <v>2.59</v>
+        <v>2.72</v>
       </c>
       <c r="Y101" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="Z101" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AA101" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AB101" t="n">
         <v>1.01</v>
       </c>
       <c r="AC101" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD101" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AE101" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF101" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG101" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AH101" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI101" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="AJ101" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK101" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AL101" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AM101" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN101" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AO101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP101" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AQ101" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AR101" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AS101" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AT101" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AU101" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV101" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AW101" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AX101" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AY101" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AZ101" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BA101" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BB101" t="n">
         <v>1.21</v>
       </c>
-      <c r="AD101" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AE101" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF101" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AG101" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AH101" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AI101" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AJ101" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK101" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AL101" t="n">
+      <c r="BC101" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BD101" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="BE101" t="n">
         <v>1.77</v>
       </c>
-      <c r="AM101" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AN101" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AO101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP101" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AQ101" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AR101" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS101" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AT101" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AU101" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AV101" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AW101" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AX101" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AY101" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AZ101" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BA101" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="BB101" t="n">
+      <c r="BF101" t="n">
         <v>1.19</v>
-      </c>
-      <c r="BC101" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="BD101" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="BE101" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BF101" t="n">
-        <v>1.23</v>
       </c>
       <c r="BG101" t="n">
         <v>0</v>
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,133 +20501,133 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>1.7</v>
+        <v>5</v>
       </c>
       <c r="Q102" t="n">
-        <v>3.68</v>
+        <v>4.26</v>
       </c>
       <c r="R102" t="n">
-        <v>5.1</v>
+        <v>1.63</v>
       </c>
       <c r="S102" t="n">
-        <v>2.31</v>
+        <v>5.05</v>
       </c>
       <c r="T102" t="n">
-        <v>2.09</v>
+        <v>2.35</v>
       </c>
       <c r="U102" t="n">
-        <v>4.54</v>
+        <v>2.16</v>
       </c>
       <c r="V102" t="n">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="W102" t="n">
-        <v>2.55</v>
+        <v>3.28</v>
       </c>
       <c r="X102" t="n">
-        <v>3.34</v>
+        <v>2.53</v>
       </c>
       <c r="Y102" t="n">
-        <v>1.32</v>
+        <v>1.51</v>
       </c>
       <c r="Z102" t="n">
-        <v>8.6</v>
+        <v>5.8</v>
       </c>
       <c r="AA102" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AB102" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AC102" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD102" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AE102" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF102" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AG102" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AH102" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI102" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AJ102" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK102" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AL102" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AM102" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN102" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AO102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP102" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AQ102" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AR102" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AS102" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AT102" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AU102" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AV102" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AW102" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AX102" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AY102" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AZ102" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BA102" t="n">
         <v>1.4</v>
       </c>
-      <c r="AD102" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AE102" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AF102" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AG102" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AH102" t="n">
+      <c r="BB102" t="n">
         <v>1.18</v>
       </c>
-      <c r="AI102" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AJ102" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK102" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AL102" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AM102" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN102" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AO102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP102" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AQ102" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR102" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AS102" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AT102" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AU102" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV102" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AW102" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AX102" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AY102" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AZ102" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BA102" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BB102" t="n">
-        <v>1.33</v>
-      </c>
       <c r="BC102" t="n">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="BD102" t="n">
-        <v>3.28</v>
+        <v>4.45</v>
       </c>
       <c r="BE102" t="n">
-        <v>1.52</v>
+        <v>1.88</v>
       </c>
       <c r="BF102" t="n">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="BG102" t="n">
         <v>0</v>
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q104" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -20940,10 +20940,10 @@
         <v>0</v>
       </c>
       <c r="AE104" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AF104" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG104" t="n">
         <v>0</v>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q105" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="R105" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Q106" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R106" t="n">
-        <v>7.25</v>
+        <v>0</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>2.29</v>
+        <v>1.32</v>
       </c>
       <c r="Q107" t="n">
-        <v>2.76</v>
+        <v>5.45</v>
       </c>
       <c r="R107" t="n">
-        <v>3.61</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q108" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="R108" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>1.32</v>
+        <v>2.8</v>
       </c>
       <c r="Q109" t="n">
-        <v>5.45</v>
+        <v>3.27</v>
       </c>
       <c r="R109" t="n">
-        <v>9.949999999999999</v>
+        <v>2.64</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -21925,10 +21925,10 @@
         <v>0</v>
       </c>
       <c r="AE109" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF109" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG109" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>2.8</v>
+        <v>1.51</v>
       </c>
       <c r="Q111" t="n">
-        <v>3.27</v>
+        <v>3.5</v>
       </c>
       <c r="R111" t="n">
-        <v>2.64</v>
+        <v>7.25</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22319,10 +22319,10 @@
         <v>0</v>
       </c>
       <c r="AE111" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF111" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG111" t="n">
         <v>0</v>
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="Q113" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="R113" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22817,22 +22817,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q116" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R116" t="n">
-        <v>4.83</v>
+        <v>0</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23304,10 +23304,10 @@
         <v>0</v>
       </c>
       <c r="AE116" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AF116" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AG116" t="n">
         <v>0</v>
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q122" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R122" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q125" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R125" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q127" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R127" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Q128" t="n">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="R128" t="n">
-        <v>6.19</v>
+        <v>0</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25674,10 +25674,10 @@
         <v>0</v>
       </c>
       <c r="AG128" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH128" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI128" t="n">
         <v>0</v>
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26017,13 +26017,13 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Q130" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="R130" t="n">
-        <v>0</v>
+        <v>6.19</v>
       </c>
       <c r="S130" t="n">
         <v>0</v>
@@ -26068,10 +26068,10 @@
         <v>0</v>
       </c>
       <c r="AG130" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH130" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI130" t="n">
         <v>0</v>
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q132" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="R132" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27396,13 +27396,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q137" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="R137" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -27545,7 +27545,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27593,13 +27593,13 @@
         </is>
       </c>
       <c r="P138" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q138" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="R138" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="S138" t="n">
         <v>0</v>
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27790,13 +27790,13 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Q139" t="n">
-        <v>5.24</v>
+        <v>0</v>
       </c>
       <c r="R139" t="n">
-        <v>7.08</v>
+        <v>0</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -27841,10 +27841,10 @@
         <v>0</v>
       </c>
       <c r="AG139" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH139" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI139" t="n">
         <v>0</v>
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28578,13 +28578,13 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Q143" t="n">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="R143" t="n">
-        <v>0</v>
+        <v>7.08</v>
       </c>
       <c r="S143" t="n">
         <v>0</v>
@@ -28629,10 +28629,10 @@
         <v>0</v>
       </c>
       <c r="AG143" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH143" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI143" t="n">
         <v>0</v>
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -28972,13 +28972,13 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q145" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="R145" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="S145" t="n">
         <v>0</v>
@@ -29017,10 +29017,10 @@
         <v>0</v>
       </c>
       <c r="AE145" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF145" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG145" t="n">
         <v>0</v>
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29169,13 +29169,13 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q146" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R146" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="S146" t="n">
         <v>0</v>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29366,14 +29366,14 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="Q147" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="R147" t="n">
         <v>3.42</v>
       </c>
-      <c r="R147" t="n">
-        <v>3.76</v>
-      </c>
       <c r="S147" t="n">
         <v>0</v>
       </c>
@@ -29411,10 +29411,10 @@
         <v>0</v>
       </c>
       <c r="AE147" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF147" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG147" t="n">
         <v>0</v>

--- a/jogos_2026-05-24.xlsx
+++ b/jogos_2026-05-24.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Shandong Luneng</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Wuhan Three Towns</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Shandong Luneng</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Wuhan Three Towns</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>5.14</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.54</v>
+        <v>1.57</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.42</v>
+        <v>4.1</v>
       </c>
       <c r="R21" t="n">
-        <v>2.59</v>
+        <v>5.14</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AL29" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AN29" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AS29" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AT29" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AU29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AV29" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BA29" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BC29" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="BD29" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AR30" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AS30" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AY30" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BA30" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="BB30" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BF30" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>4.92</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7156,10 +7156,10 @@
         <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.92</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7353,10 +7353,10 @@
         <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.33</v>
+        <v>3</v>
       </c>
       <c r="Q39" t="n">
-        <v>5</v>
+        <v>3.66</v>
       </c>
       <c r="R39" t="n">
-        <v>6</v>
+        <v>2.13</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.66</v>
+        <v>3.53</v>
       </c>
       <c r="R40" t="n">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.78</v>
+        <v>1.93</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.99</v>
+        <v>1.83</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.42</v>
+        <v>1.69</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.58</v>
+        <v>3.8</v>
       </c>
       <c r="R42" t="n">
-        <v>6</v>
+        <v>4.57</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.93</v>
+        <v>1.44</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.99</v>
+        <v>4.6</v>
       </c>
       <c r="R43" t="n">
-        <v>3.22</v>
+        <v>6.14</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.63</v>
+        <v>1.93</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.96</v>
+        <v>3.99</v>
       </c>
       <c r="R44" t="n">
-        <v>4.85</v>
+        <v>3.22</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.95</v>
+        <v>1.42</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.53</v>
+        <v>4.58</v>
       </c>
       <c r="R45" t="n">
-        <v>2.2</v>
+        <v>6</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>7</v>
+        <v>1.55</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.43</v>
+        <v>4.54</v>
       </c>
       <c r="R49" t="n">
-        <v>1.55</v>
+        <v>6.7</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.29</v>
+        <v>7</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.4</v>
+        <v>4.43</v>
       </c>
       <c r="R55" t="n">
-        <v>2.83</v>
+        <v>1.55</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF58" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12075,10 +12075,10 @@
         <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF59" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG59" t="n">
         <v>0</v>
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF60" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>2.25</v>
+        <v>2.52</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.73</v>
+        <v>3.6</v>
       </c>
       <c r="R62" t="n">
-        <v>3.31</v>
+        <v>2.94</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,10 +12666,10 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF62" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>4.54</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,22 +13361,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,133 +13409,133 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>8.25</v>
+        <v>1.53</v>
       </c>
       <c r="Q66" t="n">
-        <v>5.37</v>
+        <v>4.2</v>
       </c>
       <c r="R66" t="n">
-        <v>1.35</v>
+        <v>6.75</v>
       </c>
       <c r="S66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T66" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U66" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V66" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W66" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="X66" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Y66" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z66" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA66" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC66" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AD66" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="AE66" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF66" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG66" t="n">
-        <v>1.95</v>
+        <v>3.12</v>
       </c>
       <c r="AH66" t="n">
-        <v>1.85</v>
+        <v>1.31</v>
       </c>
       <c r="AI66" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AJ66" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL66" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AM66" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN66" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AO66" t="n">
         <v>0</v>
       </c>
       <c r="AP66" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ66" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AR66" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AS66" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AT66" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AU66" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AV66" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AW66" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AX66" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AY66" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ66" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BA66" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BB66" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BC66" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD66" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE66" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BF66" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG66" t="n">
         <v>0</v>
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,133 +13803,133 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T68" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U68" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="V68" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W68" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="X68" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Y68" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z68" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA68" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB68" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC68" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AD68" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF68" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG68" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AH68" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AI68" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AJ68" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK68" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL68" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AM68" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN68" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="AO68" t="n">
         <v>0</v>
       </c>
       <c r="AP68" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ68" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AR68" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AS68" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AT68" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AU68" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AV68" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AW68" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AX68" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AY68" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AZ68" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BA68" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BB68" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BC68" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BD68" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BE68" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BF68" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG68" t="n">
         <v>0</v>
@@ -13952,22 +13952,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>5.37</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14051,10 +14051,10 @@
         <v>0</v>
       </c>
       <c r="AG69" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH69" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI69" t="n">
         <v>0</v>
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14445,10 +14445,10 @@
         <v>0</v>
       </c>
       <c r="AG71" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH71" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AI71" t="n">
         <v>0</v>
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>4.15</v>
+        <v>3.77</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.73</v>
+        <v>4.17</v>
       </c>
       <c r="R72" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>2.59</v>
+        <v>1.67</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.42</v>
+        <v>4.17</v>
       </c>
       <c r="R73" t="n">
-        <v>2.75</v>
+        <v>4.94</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>4.46</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>6.22</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15030,10 +15030,10 @@
         <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF74" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG74" t="n">
         <v>0</v>
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="Q75" t="n">
-        <v>4.17</v>
+        <v>4.46</v>
       </c>
       <c r="R75" t="n">
-        <v>4.94</v>
+        <v>6.22</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF75" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,14 +15379,14 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>5.25</v>
+        <v>1.77</v>
       </c>
       <c r="Q76" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="R76" t="n">
         <v>4.22</v>
       </c>
-      <c r="R76" t="n">
-        <v>1.63</v>
-      </c>
       <c r="S76" t="n">
         <v>0</v>
       </c>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF76" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1.7</v>
+        <v>2.59</v>
       </c>
       <c r="Q77" t="n">
-        <v>4.53</v>
+        <v>3.42</v>
       </c>
       <c r="R77" t="n">
-        <v>4.32</v>
+        <v>2.75</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15627,10 +15627,10 @@
         <v>0</v>
       </c>
       <c r="AG77" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH77" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AI77" t="n">
         <v>0</v>
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>3.77</v>
+        <v>1.96</v>
       </c>
       <c r="Q78" t="n">
-        <v>4.17</v>
+        <v>3.81</v>
       </c>
       <c r="R78" t="n">
-        <v>1.86</v>
+        <v>3.73</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15818,10 +15818,10 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF78" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG78" t="n">
         <v>0</v>
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>5.88</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>3.19</v>
+        <v>5.25</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.19</v>
+        <v>4.22</v>
       </c>
       <c r="R80" t="n">
-        <v>2.41</v>
+        <v>1.63</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF80" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1.53</v>
+        <v>3.19</v>
       </c>
       <c r="Q81" t="n">
-        <v>4.33</v>
+        <v>3.19</v>
       </c>
       <c r="R81" t="n">
-        <v>6.19</v>
+        <v>2.41</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1.32</v>
+        <v>1.53</v>
       </c>
       <c r="Q82" t="n">
-        <v>5.88</v>
+        <v>4.33</v>
       </c>
       <c r="R82" t="n">
-        <v>8.4</v>
+        <v>6.19</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>1.77</v>
+        <v>4.15</v>
       </c>
       <c r="Q84" t="n">
-        <v>4.07</v>
+        <v>3.73</v>
       </c>
       <c r="R84" t="n">
-        <v>4.22</v>
+        <v>1.88</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17104,22 +17104,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>4.37</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>5.41</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,10 +17394,10 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF86" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>1.59</v>
+        <v>1.82</v>
       </c>
       <c r="Q87" t="n">
-        <v>4.37</v>
+        <v>4.06</v>
       </c>
       <c r="R87" t="n">
-        <v>5.41</v>
+        <v>4.06</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>5.21</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>5.21</v>
+        <v>0</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,133 +19713,133 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>1.7</v>
+        <v>5</v>
       </c>
       <c r="Q98" t="n">
-        <v>3.68</v>
+        <v>4.26</v>
       </c>
       <c r="R98" t="n">
-        <v>5.1</v>
+        <v>1.63</v>
       </c>
       <c r="S98" t="n">
-        <v>2.31</v>
+        <v>5.05</v>
       </c>
       <c r="T98" t="n">
-        <v>2.09</v>
+        <v>2.35</v>
       </c>
       <c r="U98" t="n">
-        <v>4.54</v>
+        <v>2.16</v>
       </c>
       <c r="V98" t="n">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="W98" t="n">
-        <v>2.55</v>
+        <v>3.28</v>
       </c>
       <c r="X98" t="n">
-        <v>3.34</v>
+        <v>2.53</v>
       </c>
       <c r="Y98" t="n">
-        <v>1.32</v>
+        <v>1.51</v>
       </c>
       <c r="Z98" t="n">
-        <v>8.6</v>
+        <v>5.8</v>
       </c>
       <c r="AA98" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AB98" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AC98" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD98" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AE98" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF98" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AG98" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AH98" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI98" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AJ98" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK98" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AL98" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AM98" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN98" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AO98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP98" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AQ98" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AR98" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AS98" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AT98" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AU98" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AV98" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AW98" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AX98" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AY98" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AZ98" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BA98" t="n">
         <v>1.4</v>
       </c>
-      <c r="AD98" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AE98" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AF98" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AG98" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AH98" t="n">
+      <c r="BB98" t="n">
         <v>1.18</v>
       </c>
-      <c r="AI98" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AJ98" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK98" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AL98" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AM98" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN98" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AO98" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP98" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AQ98" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR98" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AS98" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AT98" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AU98" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV98" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AW98" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AX98" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AY98" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AZ98" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BA98" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BB98" t="n">
-        <v>1.33</v>
-      </c>
       <c r="BC98" t="n">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="BD98" t="n">
-        <v>3.28</v>
+        <v>4.45</v>
       </c>
       <c r="BE98" t="n">
-        <v>1.52</v>
+        <v>1.88</v>
       </c>
       <c r="BF98" t="n">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="BG98" t="n">
         <v>0</v>
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,133 +19910,133 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>7.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q99" t="n">
-        <v>4.78</v>
+        <v>5.2</v>
       </c>
       <c r="R99" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S99" t="n">
-        <v>5.51</v>
+        <v>8.5</v>
       </c>
       <c r="T99" t="n">
-        <v>2.28</v>
+        <v>2.47</v>
       </c>
       <c r="U99" t="n">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="V99" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="W99" t="n">
-        <v>3.27</v>
+        <v>3.1</v>
       </c>
       <c r="X99" t="n">
-        <v>2.59</v>
+        <v>2.72</v>
       </c>
       <c r="Y99" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="Z99" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AA99" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AB99" t="n">
         <v>1.01</v>
       </c>
       <c r="AC99" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD99" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AE99" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF99" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG99" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AH99" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI99" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="AJ99" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK99" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AL99" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AM99" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN99" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AO99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP99" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AQ99" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AR99" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AS99" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AT99" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AU99" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV99" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AW99" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AX99" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AY99" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AZ99" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BA99" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BB99" t="n">
         <v>1.21</v>
       </c>
-      <c r="AD99" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AE99" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF99" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AG99" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AH99" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AI99" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AJ99" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK99" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AL99" t="n">
+      <c r="BC99" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BD99" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="BE99" t="n">
         <v>1.77</v>
       </c>
-      <c r="AM99" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AN99" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AO99" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP99" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AQ99" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AR99" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS99" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AT99" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AU99" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AV99" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AW99" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AX99" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AY99" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AZ99" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BA99" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="BB99" t="n">
+      <c r="BF99" t="n">
         <v>1.19</v>
-      </c>
-      <c r="BC99" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="BD99" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="BE99" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BF99" t="n">
-        <v>1.23</v>
       </c>
       <c r="BG99" t="n">
         <v>0</v>
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,28 +20107,28 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>1.33</v>
+        <v>7.5</v>
       </c>
       <c r="Q100" t="n">
-        <v>5.2</v>
+        <v>4.78</v>
       </c>
       <c r="R100" t="n">
-        <v>9</v>
+        <v>1.4</v>
       </c>
       <c r="S100" t="n">
-        <v>1.77</v>
+        <v>5.51</v>
       </c>
       <c r="T100" t="n">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="U100" t="n">
-        <v>8.1</v>
+        <v>1.86</v>
       </c>
       <c r="V100" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W100" t="n">
-        <v>3.25</v>
+        <v>3.27</v>
       </c>
       <c r="X100" t="n">
         <v>2.59</v>
@@ -20137,100 +20137,100 @@
         <v>1.49</v>
       </c>
       <c r="Z100" t="n">
-        <v>6.05</v>
+        <v>6</v>
       </c>
       <c r="AA100" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AB100" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC100" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AD100" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AE100" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF100" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AG100" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AH100" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AI100" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AJ100" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK100" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AL100" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AM100" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AN100" t="n">
         <v>1.09</v>
       </c>
-      <c r="AB100" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC100" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AD100" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE100" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AF100" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AG100" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="AH100" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI100" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AJ100" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK100" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AL100" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AM100" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AN100" t="n">
-        <v>3.44</v>
-      </c>
       <c r="AO100" t="n">
         <v>0</v>
       </c>
       <c r="AP100" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="AQ100" t="n">
-        <v>1.46</v>
+        <v>1.61</v>
       </c>
       <c r="AR100" t="n">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="AS100" t="n">
-        <v>2.18</v>
+        <v>2.6</v>
       </c>
       <c r="AT100" t="n">
-        <v>2.85</v>
+        <v>3.45</v>
       </c>
       <c r="AU100" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="AV100" t="n">
-        <v>2.48</v>
+        <v>2.15</v>
       </c>
       <c r="AW100" t="n">
-        <v>1.92</v>
+        <v>1.7</v>
       </c>
       <c r="AX100" t="n">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="AY100" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AZ100" t="n">
-        <v>1.2</v>
+        <v>3.1</v>
       </c>
       <c r="BA100" t="n">
-        <v>5.3</v>
+        <v>1.47</v>
       </c>
       <c r="BB100" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="BC100" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="BD100" t="n">
-        <v>4.5</v>
+        <v>4.35</v>
       </c>
       <c r="BE100" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="BF100" t="n">
         <v>1.23</v>
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,133 +20304,133 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>9.199999999999999</v>
+        <v>1.7</v>
       </c>
       <c r="Q101" t="n">
-        <v>5.2</v>
+        <v>3.68</v>
       </c>
       <c r="R101" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="S101" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="T101" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="U101" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="V101" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="W101" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="X101" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="Y101" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z101" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AA101" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB101" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC101" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD101" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AE101" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AF101" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG101" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AH101" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI101" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AJ101" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK101" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AL101" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AM101" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN101" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AO101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP101" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ101" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR101" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AS101" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AT101" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU101" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV101" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AW101" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AX101" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AY101" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AZ101" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BA101" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BB101" t="n">
         <v>1.33</v>
       </c>
-      <c r="S101" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="T101" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="U101" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="V101" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W101" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="X101" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="Y101" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z101" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AA101" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB101" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC101" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AD101" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AE101" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AF101" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG101" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AH101" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI101" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="AJ101" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK101" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AL101" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AM101" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AN101" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AO101" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP101" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AQ101" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AR101" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AS101" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AT101" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AU101" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV101" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AW101" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AX101" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AY101" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AZ101" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BA101" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BB101" t="n">
-        <v>1.21</v>
-      </c>
       <c r="BC101" t="n">
-        <v>1.94</v>
+        <v>2.5</v>
       </c>
       <c r="BD101" t="n">
-        <v>4.15</v>
+        <v>3.28</v>
       </c>
       <c r="BE101" t="n">
-        <v>1.77</v>
+        <v>1.52</v>
       </c>
       <c r="BF101" t="n">
-        <v>1.19</v>
+        <v>1.1</v>
       </c>
       <c r="BG101" t="n">
         <v>0</v>
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,40 +20501,40 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>5</v>
+        <v>1.33</v>
       </c>
       <c r="Q102" t="n">
-        <v>4.26</v>
+        <v>5.2</v>
       </c>
       <c r="R102" t="n">
-        <v>1.63</v>
+        <v>9</v>
       </c>
       <c r="S102" t="n">
-        <v>5.05</v>
+        <v>1.77</v>
       </c>
       <c r="T102" t="n">
         <v>2.35</v>
       </c>
       <c r="U102" t="n">
-        <v>2.16</v>
+        <v>8.1</v>
       </c>
       <c r="V102" t="n">
         <v>1.33</v>
       </c>
       <c r="W102" t="n">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="X102" t="n">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="Y102" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="Z102" t="n">
-        <v>5.8</v>
+        <v>6.05</v>
       </c>
       <c r="AA102" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AB102" t="n">
         <v>1</v>
@@ -20543,91 +20543,91 @@
         <v>1.2</v>
       </c>
       <c r="AD102" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="AE102" t="n">
-        <v>1.66</v>
+        <v>1.79</v>
       </c>
       <c r="AF102" t="n">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="AG102" t="n">
-        <v>2.66</v>
+        <v>2.81</v>
       </c>
       <c r="AH102" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AI102" t="n">
-        <v>4.65</v>
+        <v>4.8</v>
       </c>
       <c r="AJ102" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AK102" t="n">
-        <v>1.71</v>
+        <v>2.16</v>
       </c>
       <c r="AL102" t="n">
-        <v>2.04</v>
+        <v>1.63</v>
       </c>
       <c r="AM102" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN102" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AO102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP102" t="n">
         <v>1.26</v>
       </c>
-      <c r="AN102" t="n">
+      <c r="AQ102" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR102" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AS102" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AT102" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AU102" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV102" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AW102" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AX102" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AY102" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AZ102" t="n">
         <v>1.2</v>
       </c>
-      <c r="AO102" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP102" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AQ102" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AR102" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AS102" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AT102" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AU102" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AV102" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AW102" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AX102" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AY102" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AZ102" t="n">
-        <v>3.4</v>
-      </c>
       <c r="BA102" t="n">
-        <v>1.4</v>
+        <v>5.3</v>
       </c>
       <c r="BB102" t="n">
         <v>1.18</v>
       </c>
       <c r="BC102" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="BD102" t="n">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="BE102" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="BF102" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="BG102" t="n">
         <v>0</v>
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q103" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>1.77</v>
+        <v>2.8</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.32</v>
+        <v>3.27</v>
       </c>
       <c r="R104" t="n">
-        <v>4.83</v>
+        <v>2.64</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -20940,10 +20940,10 @@
         <v>0</v>
       </c>
       <c r="AE104" t="n">
-        <v>2.37</v>
+        <v>2.05</v>
       </c>
       <c r="AF104" t="n">
-        <v>1.51</v>
+        <v>1.8</v>
       </c>
       <c r="AG104" t="n">
         <v>0</v>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="Q105" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="R105" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q106" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="R106" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Q107" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>9.949999999999999</v>
+        <v>0</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="Q108" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="R108" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q109" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="R109" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -21925,10 +21925,10 @@
         <v>0</v>
       </c>
       <c r="AE109" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF109" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG109" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q110" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="R110" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,55 +22274,55 @@
         </is>
       </c>
       <c r="P111" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="R111" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="S111" t="n">
+        <v>0</v>
+      </c>
+      <c r="T111" t="n">
+        <v>0</v>
+      </c>
+      <c r="U111" t="n">
+        <v>0</v>
+      </c>
+      <c r="V111" t="n">
+        <v>0</v>
+      </c>
+      <c r="W111" t="n">
+        <v>0</v>
+      </c>
+      <c r="X111" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y111" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AF111" t="n">
         <v>1.51</v>
-      </c>
-      <c r="Q111" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R111" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="S111" t="n">
-        <v>0</v>
-      </c>
-      <c r="T111" t="n">
-        <v>0</v>
-      </c>
-      <c r="U111" t="n">
-        <v>0</v>
-      </c>
-      <c r="V111" t="n">
-        <v>0</v>
-      </c>
-      <c r="W111" t="n">
-        <v>0</v>
-      </c>
-      <c r="X111" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y111" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF111" t="n">
-        <v>0</v>
       </c>
       <c r="AG111" t="n">
         <v>0</v>
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,22 +22817,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Q116" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R116" t="n">
-        <v>0</v>
+        <v>7.25</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q118" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="R118" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -24047,13 +24047,13 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Q120" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R120" t="n">
-        <v>0</v>
+        <v>5.44</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -24092,10 +24092,10 @@
         <v>0</v>
       </c>
       <c r="AE120" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF120" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG120" t="n">
         <v>0</v>
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q127" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="R127" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Q128" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="R128" t="n">
-        <v>0</v>
+        <v>6.19</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25674,10 +25674,10 @@
         <v>0</v>
       </c>
       <c r="AG128" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH128" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI128" t="n">
         <v>0</v>
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26017,13 +26017,13 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>1.51</v>
+        <v>1.93</v>
       </c>
       <c r="Q130" t="n">
-        <v>4.84</v>
+        <v>2.85</v>
       </c>
       <c r="R130" t="n">
-        <v>6.19</v>
+        <v>4.35</v>
       </c>
       <c r="S130" t="n">
         <v>0</v>
@@ -26068,10 +26068,10 @@
         <v>0</v>
       </c>
       <c r="AG130" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH130" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI130" t="n">
         <v>0</v>
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q132" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R132" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q136" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="R136" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27396,13 +27396,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q137" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="R137" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28184,13 +28184,13 @@
         </is>
       </c>
       <c r="P141" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Q141" t="n">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="R141" t="n">
-        <v>0</v>
+        <v>7.08</v>
       </c>
       <c r="S141" t="n">
         <v>0</v>
@@ -28235,10 +28235,10 @@
         <v>0</v>
       </c>
       <c r="AG141" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH141" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI141" t="n">
         <v>0</v>
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28578,13 +28578,13 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Q143" t="n">
-        <v>5.24</v>
+        <v>0</v>
       </c>
       <c r="R143" t="n">
-        <v>7.08</v>
+        <v>0</v>
       </c>
       <c r="S143" t="n">
         <v>0</v>
@@ -28629,10 +28629,10 @@
         <v>0</v>
       </c>
       <c r="AG143" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH143" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI143" t="n">
         <v>0</v>
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -28972,13 +28972,13 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q145" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R145" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="S145" t="n">
         <v>0</v>
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29169,13 +29169,13 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q146" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R146" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="S146" t="n">
         <v>0</v>

--- a/jogos_2026-05-24.xlsx
+++ b/jogos_2026-05-24.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI150"/>
+  <dimension ref="A1:BI155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>5.14</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.92</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7156,10 +7156,10 @@
         <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>4.92</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7353,10 +7353,10 @@
         <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.33</v>
+        <v>1.82</v>
       </c>
       <c r="Q36" t="n">
-        <v>5</v>
+        <v>4.06</v>
       </c>
       <c r="R36" t="n">
-        <v>6</v>
+        <v>4.06</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7634,7 +7634,7 @@
         <v>0</v>
       </c>
       <c r="BI36" s="3" t="n">
-        <v>46166.47916666666</v>
+        <v>46166.46875</v>
       </c>
     </row>
     <row r="37">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.3</v>
+        <v>1.59</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.6</v>
+        <v>4.37</v>
       </c>
       <c r="R37" t="n">
-        <v>2.6</v>
+        <v>5.41</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7741,10 +7741,10 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
@@ -7831,7 +7831,7 @@
         <v>0</v>
       </c>
       <c r="BI37" s="3" t="n">
-        <v>46166.47916666666</v>
+        <v>46166.46875</v>
       </c>
     </row>
     <row r="38">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.28</v>
+        <v>1.69</v>
       </c>
       <c r="Q38" t="n">
-        <v>5.41</v>
+        <v>3.8</v>
       </c>
       <c r="R38" t="n">
-        <v>8.039999999999999</v>
+        <v>4.57</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>3</v>
+        <v>1.28</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.66</v>
+        <v>5.41</v>
       </c>
       <c r="R39" t="n">
-        <v>2.13</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.95</v>
+        <v>1.33</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.53</v>
+        <v>5</v>
       </c>
       <c r="R40" t="n">
-        <v>2.2</v>
+        <v>6</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.63</v>
+        <v>2.3</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.96</v>
+        <v>3.6</v>
       </c>
       <c r="R41" t="n">
-        <v>4.85</v>
+        <v>2.6</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.69</v>
+        <v>1.44</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="R42" t="n">
-        <v>4.57</v>
+        <v>6.14</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.6</v>
+        <v>3.96</v>
       </c>
       <c r="R43" t="n">
-        <v>6.14</v>
+        <v>4.85</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.42</v>
+        <v>3</v>
       </c>
       <c r="Q45" t="n">
-        <v>4.58</v>
+        <v>3.66</v>
       </c>
       <c r="R45" t="n">
-        <v>6</v>
+        <v>2.13</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9416,12 +9416,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9604,7 +9604,7 @@
         <v>0</v>
       </c>
       <c r="BI46" s="3" t="n">
-        <v>46166.5</v>
+        <v>46166.47916666666</v>
       </c>
     </row>
     <row r="47">
@@ -9613,12 +9613,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.8</v>
+        <v>2.95</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.81</v>
+        <v>3.53</v>
       </c>
       <c r="R47" t="n">
-        <v>2.53</v>
+        <v>2.2</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.6</v>
+        <v>1.93</v>
       </c>
       <c r="AF47" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9801,7 +9801,7 @@
         <v>0</v>
       </c>
       <c r="BI47" s="3" t="n">
-        <v>46166.5</v>
+        <v>46166.47916666666</v>
       </c>
     </row>
     <row r="48">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.55</v>
+        <v>3.82</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.54</v>
+        <v>3.82</v>
       </c>
       <c r="R49" t="n">
-        <v>6.7</v>
+        <v>2.03</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.25</v>
+        <v>2.63</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.73</v>
+        <v>3.82</v>
       </c>
       <c r="R50" t="n">
-        <v>3.31</v>
+        <v>2.68</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.54</v>
+        <v>7</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.62</v>
+        <v>4.43</v>
       </c>
       <c r="R56" t="n">
-        <v>2.89</v>
+        <v>1.55</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1.44</v>
+        <v>2.54</v>
       </c>
       <c r="Q57" t="n">
-        <v>5.57</v>
+        <v>3.62</v>
       </c>
       <c r="R57" t="n">
-        <v>7.02</v>
+        <v>2.89</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>5.57</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>7.02</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.63</v>
+        <v>1.55</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.82</v>
+        <v>4.54</v>
       </c>
       <c r="R60" t="n">
-        <v>2.68</v>
+        <v>6.7</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF60" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>3.82</v>
+        <v>2.52</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.82</v>
+        <v>3.6</v>
       </c>
       <c r="R61" t="n">
-        <v>2.03</v>
+        <v>2.94</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12469,10 +12469,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF61" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,10 +12666,10 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF62" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12962,12 +12962,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13060,10 +13060,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF64" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -13150,7 +13150,7 @@
         <v>0</v>
       </c>
       <c r="BI64" s="3" t="n">
-        <v>46166.54166666666</v>
+        <v>46166.5</v>
       </c>
     </row>
     <row r="65">
@@ -13159,12 +13159,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13347,7 +13347,7 @@
         <v>0</v>
       </c>
       <c r="BI65" s="3" t="n">
-        <v>46166.54166666666</v>
+        <v>46166.5</v>
       </c>
     </row>
     <row r="66">
@@ -13356,12 +13356,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,133 +13409,133 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T66" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U66" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="V66" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W66" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="X66" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Y66" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z66" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA66" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB66" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC66" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AD66" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF66" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG66" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AH66" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AI66" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AJ66" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL66" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AM66" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN66" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="AO66" t="n">
         <v>0</v>
       </c>
       <c r="AP66" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ66" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AR66" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AS66" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AT66" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AU66" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AV66" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AW66" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AX66" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AY66" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AZ66" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BA66" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BB66" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BC66" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BD66" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BE66" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BF66" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG66" t="n">
         <v>0</v>
@@ -13544,7 +13544,7 @@
         <v>0</v>
       </c>
       <c r="BI66" s="3" t="n">
-        <v>46166.54166666666</v>
+        <v>46166.5</v>
       </c>
     </row>
     <row r="67">
@@ -13553,12 +13553,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13741,7 +13741,7 @@
         <v>0</v>
       </c>
       <c r="BI67" s="3" t="n">
-        <v>46166.54166666666</v>
+        <v>46166.5</v>
       </c>
     </row>
     <row r="68">
@@ -13750,12 +13750,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13938,7 +13938,7 @@
         <v>0</v>
       </c>
       <c r="BI68" s="3" t="n">
-        <v>46166.54166666666</v>
+        <v>46166.5</v>
       </c>
     </row>
     <row r="69">
@@ -13947,27 +13947,27 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>5.37</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14051,10 +14051,10 @@
         <v>0</v>
       </c>
       <c r="AG69" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH69" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI69" t="n">
         <v>0</v>
@@ -14135,7 +14135,7 @@
         <v>0</v>
       </c>
       <c r="BI69" s="3" t="n">
-        <v>46166.54166666666</v>
+        <v>46166.5</v>
       </c>
     </row>
     <row r="70">
@@ -14144,12 +14144,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14332,7 +14332,7 @@
         <v>0</v>
       </c>
       <c r="BI70" s="3" t="n">
-        <v>46166.54166666666</v>
+        <v>46166.5</v>
       </c>
     </row>
     <row r="71">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14445,10 +14445,10 @@
         <v>0</v>
       </c>
       <c r="AG71" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH71" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AI71" t="n">
         <v>0</v>
@@ -14529,7 +14529,7 @@
         <v>0</v>
       </c>
       <c r="BI71" s="3" t="n">
-        <v>46166.5625</v>
+        <v>46166.54166666666</v>
       </c>
     </row>
     <row r="72">
@@ -14538,12 +14538,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14726,7 +14726,7 @@
         <v>0</v>
       </c>
       <c r="BI72" s="3" t="n">
-        <v>46166.5625</v>
+        <v>46166.54166666666</v>
       </c>
     </row>
     <row r="73">
@@ -14735,12 +14735,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>4.94</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14923,7 +14923,7 @@
         <v>0</v>
       </c>
       <c r="BI73" s="3" t="n">
-        <v>46166.5625</v>
+        <v>46166.54166666666</v>
       </c>
     </row>
     <row r="74">
@@ -14932,27 +14932,27 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15120,7 +15120,7 @@
         <v>0</v>
       </c>
       <c r="BI74" s="3" t="n">
-        <v>46166.5625</v>
+        <v>46166.54166666666</v>
       </c>
     </row>
     <row r="75">
@@ -15129,12 +15129,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>4.46</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>6.22</v>
+        <v>0</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF75" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15317,7 +15317,7 @@
         <v>0</v>
       </c>
       <c r="BI75" s="3" t="n">
-        <v>46166.5625</v>
+        <v>46166.54166666666</v>
       </c>
     </row>
     <row r="76">
@@ -15326,12 +15326,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,133 +15379,133 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1.77</v>
+        <v>1.53</v>
       </c>
       <c r="Q76" t="n">
-        <v>4.07</v>
+        <v>4.2</v>
       </c>
       <c r="R76" t="n">
-        <v>4.22</v>
+        <v>6.75</v>
       </c>
       <c r="S76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T76" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U76" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V76" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W76" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="X76" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Y76" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z76" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA76" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB76" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC76" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AD76" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="AE76" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF76" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG76" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AH76" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AI76" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AJ76" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL76" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AM76" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN76" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AO76" t="n">
         <v>0</v>
       </c>
       <c r="AP76" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ76" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AR76" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AS76" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AT76" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AU76" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AV76" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AW76" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AX76" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AY76" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ76" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BA76" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BB76" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BC76" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD76" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE76" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BF76" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG76" t="n">
         <v>0</v>
@@ -15514,7 +15514,7 @@
         <v>0</v>
       </c>
       <c r="BI76" s="3" t="n">
-        <v>46166.5625</v>
+        <v>46166.54166666666</v>
       </c>
     </row>
     <row r="77">
@@ -15523,27 +15523,27 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.59</v>
+        <v>8.25</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.42</v>
+        <v>5.37</v>
       </c>
       <c r="R77" t="n">
-        <v>2.75</v>
+        <v>1.35</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15627,10 +15627,10 @@
         <v>0</v>
       </c>
       <c r="AG77" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH77" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI77" t="n">
         <v>0</v>
@@ -15711,7 +15711,7 @@
         <v>0</v>
       </c>
       <c r="BI77" s="3" t="n">
-        <v>46166.5625</v>
+        <v>46166.54166666666</v>
       </c>
     </row>
     <row r="78">
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15818,10 +15818,10 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF78" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG78" t="n">
         <v>0</v>
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1.32</v>
+        <v>1.53</v>
       </c>
       <c r="Q79" t="n">
-        <v>5.88</v>
+        <v>4.33</v>
       </c>
       <c r="R79" t="n">
-        <v>8.4</v>
+        <v>6.19</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>5.25</v>
+        <v>1.67</v>
       </c>
       <c r="Q80" t="n">
-        <v>4.22</v>
+        <v>4.17</v>
       </c>
       <c r="R80" t="n">
-        <v>1.63</v>
+        <v>4.94</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF80" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>3.19</v>
+        <v>1.96</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.19</v>
+        <v>3.81</v>
       </c>
       <c r="R81" t="n">
-        <v>2.41</v>
+        <v>3.73</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16409,10 +16409,10 @@
         <v>0</v>
       </c>
       <c r="AE81" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF81" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="Q82" t="n">
-        <v>4.33</v>
+        <v>4.53</v>
       </c>
       <c r="R82" t="n">
-        <v>6.19</v>
+        <v>4.32</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16612,10 +16612,10 @@
         <v>0</v>
       </c>
       <c r="AG82" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH82" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AI82" t="n">
         <v>0</v>
@@ -16710,22 +16710,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>4.15</v>
+        <v>1.52</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.73</v>
+        <v>4.46</v>
       </c>
       <c r="R84" t="n">
-        <v>1.88</v>
+        <v>6.22</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17000,10 +17000,10 @@
         <v>0</v>
       </c>
       <c r="AE84" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF84" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG84" t="n">
         <v>0</v>
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>1.59</v>
+        <v>3.19</v>
       </c>
       <c r="Q85" t="n">
-        <v>4.37</v>
+        <v>3.19</v>
       </c>
       <c r="R85" t="n">
-        <v>5.41</v>
+        <v>2.41</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17301,22 +17301,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,10 +17394,10 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF86" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>4.06</v>
+        <v>0</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17690,27 +17690,27 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17878,7 +17878,7 @@
         <v>0</v>
       </c>
       <c r="BI88" s="3" t="n">
-        <v>46166.58333333334</v>
+        <v>46166.5625</v>
       </c>
     </row>
     <row r="89">
@@ -17887,12 +17887,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18075,7 +18075,7 @@
         <v>0</v>
       </c>
       <c r="BI89" s="3" t="n">
-        <v>46166.58333333334</v>
+        <v>46166.5625</v>
       </c>
     </row>
     <row r="90">
@@ -18084,12 +18084,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18272,7 +18272,7 @@
         <v>0</v>
       </c>
       <c r="BI90" s="3" t="n">
-        <v>46166.60416666666</v>
+        <v>46166.5625</v>
       </c>
     </row>
     <row r="91">
@@ -18281,12 +18281,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18469,7 +18469,7 @@
         <v>0</v>
       </c>
       <c r="BI91" s="3" t="n">
-        <v>46166.60416666666</v>
+        <v>46166.5625</v>
       </c>
     </row>
     <row r="92">
@@ -18478,12 +18478,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>5.88</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18666,7 +18666,7 @@
         <v>0</v>
       </c>
       <c r="BI92" s="3" t="n">
-        <v>46166.60416666666</v>
+        <v>46166.5625</v>
       </c>
     </row>
     <row r="93">
@@ -18675,27 +18675,27 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18863,7 +18863,7 @@
         <v>0</v>
       </c>
       <c r="BI93" s="3" t="n">
-        <v>46166.60416666666</v>
+        <v>46166.58333333334</v>
       </c>
     </row>
     <row r="94">
@@ -18872,12 +18872,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>5.21</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19060,7 +19060,7 @@
         <v>0</v>
       </c>
       <c r="BI94" s="3" t="n">
-        <v>46166.625</v>
+        <v>46166.58333333334</v>
       </c>
     </row>
     <row r="95">
@@ -19069,27 +19069,27 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19257,7 +19257,7 @@
         <v>0</v>
       </c>
       <c r="BI95" s="3" t="n">
-        <v>46166.625</v>
+        <v>46166.60416666666</v>
       </c>
     </row>
     <row r="96">
@@ -19266,27 +19266,27 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>4.97</v>
+        <v>0</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19454,7 +19454,7 @@
         <v>0</v>
       </c>
       <c r="BI96" s="3" t="n">
-        <v>46166.64583333334</v>
+        <v>46166.60416666666</v>
       </c>
     </row>
     <row r="97">
@@ -19463,27 +19463,27 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19651,7 +19651,7 @@
         <v>0</v>
       </c>
       <c r="BI97" s="3" t="n">
-        <v>46166.64583333334</v>
+        <v>46166.60416666666</v>
       </c>
     </row>
     <row r="98">
@@ -19660,12 +19660,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,133 +19713,133 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="S98" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="T98" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="U98" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="V98" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W98" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="X98" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Y98" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z98" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC98" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD98" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AE98" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF98" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AG98" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AH98" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AI98" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AJ98" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK98" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AL98" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AM98" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN98" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AO98" t="n">
         <v>0</v>
       </c>
       <c r="AP98" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AQ98" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AR98" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AS98" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AT98" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AU98" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AV98" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AW98" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AX98" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AY98" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AZ98" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BA98" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BB98" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC98" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD98" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="BE98" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="BF98" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BG98" t="n">
         <v>0</v>
@@ -19848,7 +19848,7 @@
         <v>0</v>
       </c>
       <c r="BI98" s="3" t="n">
-        <v>46166.65625</v>
+        <v>46166.60416666666</v>
       </c>
     </row>
     <row r="99">
@@ -19857,27 +19857,27 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,133 +19910,133 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>9.199999999999999</v>
+        <v>1.66</v>
       </c>
       <c r="Q99" t="n">
-        <v>5.2</v>
+        <v>3.46</v>
       </c>
       <c r="R99" t="n">
-        <v>1.33</v>
+        <v>5.21</v>
       </c>
       <c r="S99" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="T99" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="U99" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="V99" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W99" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="X99" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="Y99" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z99" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AA99" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB99" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC99" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AD99" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AE99" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF99" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG99" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="AH99" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI99" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="AJ99" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK99" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AL99" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AM99" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AN99" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AO99" t="n">
         <v>0</v>
       </c>
       <c r="AP99" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AQ99" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AR99" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AS99" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AT99" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AU99" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AV99" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AW99" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AX99" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AY99" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AZ99" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BA99" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BB99" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BC99" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="BD99" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="BE99" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="BF99" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="BG99" t="n">
         <v>0</v>
@@ -20045,7 +20045,7 @@
         <v>0</v>
       </c>
       <c r="BI99" s="3" t="n">
-        <v>46166.65625</v>
+        <v>46166.625</v>
       </c>
     </row>
     <row r="100">
@@ -20054,27 +20054,27 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,133 +20107,133 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S100" t="n">
-        <v>5.51</v>
+        <v>0</v>
       </c>
       <c r="T100" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="U100" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="V100" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W100" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="X100" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Y100" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z100" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA100" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC100" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AD100" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AE100" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF100" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AG100" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AH100" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AI100" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="AJ100" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK100" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AL100" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AM100" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AN100" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AO100" t="n">
         <v>0</v>
       </c>
       <c r="AP100" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AQ100" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AR100" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AS100" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AT100" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AU100" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AV100" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AW100" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AX100" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AY100" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AZ100" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BA100" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="BB100" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="BC100" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="BD100" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="BE100" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BF100" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BG100" t="n">
         <v>0</v>
@@ -20242,7 +20242,7 @@
         <v>0</v>
       </c>
       <c r="BI100" s="3" t="n">
-        <v>46166.65625</v>
+        <v>46166.625</v>
       </c>
     </row>
     <row r="101">
@@ -20251,27 +20251,27 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,133 +20304,133 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="Q101" t="n">
-        <v>3.68</v>
+        <v>3.19</v>
       </c>
       <c r="R101" t="n">
-        <v>5.1</v>
+        <v>4.97</v>
       </c>
       <c r="S101" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="T101" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="U101" t="n">
-        <v>4.54</v>
+        <v>0</v>
       </c>
       <c r="V101" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W101" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="X101" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="Y101" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z101" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AA101" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC101" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD101" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="AE101" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AF101" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG101" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AH101" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI101" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AJ101" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK101" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AL101" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AM101" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AN101" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AO101" t="n">
         <v>0</v>
       </c>
       <c r="AP101" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AQ101" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AR101" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AS101" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AT101" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AU101" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AV101" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AW101" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AX101" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AY101" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AZ101" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="BA101" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="BB101" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="BC101" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BD101" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="BE101" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="BF101" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="BG101" t="n">
         <v>0</v>
@@ -20439,7 +20439,7 @@
         <v>0</v>
       </c>
       <c r="BI101" s="3" t="n">
-        <v>46166.65625</v>
+        <v>46166.64583333334</v>
       </c>
     </row>
     <row r="102">
@@ -20448,27 +20448,27 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,133 +20501,133 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>1.33</v>
+        <v>2.8</v>
       </c>
       <c r="Q102" t="n">
-        <v>5.2</v>
+        <v>2.75</v>
       </c>
       <c r="R102" t="n">
-        <v>9</v>
+        <v>2.8</v>
       </c>
       <c r="S102" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="T102" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="U102" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="V102" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W102" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="X102" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Y102" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Z102" t="n">
-        <v>6.05</v>
+        <v>0</v>
       </c>
       <c r="AA102" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC102" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD102" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AE102" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF102" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AG102" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AH102" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI102" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AJ102" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK102" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AL102" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AM102" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN102" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="AO102" t="n">
         <v>0</v>
       </c>
       <c r="AP102" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AQ102" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AR102" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AS102" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AT102" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AU102" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AV102" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW102" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AX102" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AY102" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ102" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BA102" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="BB102" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC102" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="BD102" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BE102" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="BF102" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BG102" t="n">
         <v>0</v>
@@ -20636,7 +20636,7 @@
         <v>0</v>
       </c>
       <c r="BI102" s="3" t="n">
-        <v>46166.65625</v>
+        <v>46166.64583333334</v>
       </c>
     </row>
     <row r="103">
@@ -20645,27 +20645,27 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,133 +20698,133 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>1.32</v>
+        <v>5</v>
       </c>
       <c r="Q103" t="n">
-        <v>5.45</v>
+        <v>4.26</v>
       </c>
       <c r="R103" t="n">
-        <v>9.949999999999999</v>
+        <v>1.63</v>
       </c>
       <c r="S103" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="T103" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U103" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="V103" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W103" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="X103" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Y103" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z103" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA103" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC103" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD103" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AE103" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF103" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AG103" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AH103" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI103" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AJ103" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK103" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL103" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AM103" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN103" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AO103" t="n">
         <v>0</v>
       </c>
       <c r="AP103" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AQ103" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AR103" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AS103" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AT103" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AU103" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AV103" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AW103" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AX103" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AY103" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AZ103" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BA103" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BB103" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC103" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD103" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="BE103" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BF103" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BG103" t="n">
         <v>0</v>
@@ -20833,7 +20833,7 @@
         <v>0</v>
       </c>
       <c r="BI103" s="3" t="n">
-        <v>46166.66666666666</v>
+        <v>46166.65625</v>
       </c>
     </row>
     <row r="104">
@@ -20842,27 +20842,27 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,133 +20895,133 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.27</v>
+        <v>3.68</v>
       </c>
       <c r="R104" t="n">
-        <v>2.64</v>
+        <v>5.1</v>
       </c>
       <c r="S104" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T104" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="U104" t="n">
-        <v>0</v>
+        <v>4.54</v>
       </c>
       <c r="V104" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W104" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="X104" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Y104" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z104" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AA104" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB104" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC104" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD104" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AE104" t="n">
-        <v>2.05</v>
+        <v>2.39</v>
       </c>
       <c r="AF104" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AG104" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AH104" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI104" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AJ104" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK104" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AL104" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AM104" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AN104" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AO104" t="n">
         <v>0</v>
       </c>
       <c r="AP104" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AQ104" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR104" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AS104" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AT104" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AU104" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV104" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AW104" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AX104" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AY104" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AZ104" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BA104" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="BB104" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BC104" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BD104" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE104" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BF104" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG104" t="n">
         <v>0</v>
@@ -21030,7 +21030,7 @@
         <v>0</v>
       </c>
       <c r="BI104" s="3" t="n">
-        <v>46166.66666666666</v>
+        <v>46166.65625</v>
       </c>
     </row>
     <row r="105">
@@ -21039,27 +21039,27 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,133 +21092,133 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q105" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="R105" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S105" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="T105" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U105" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="V105" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W105" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="X105" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="Y105" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z105" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AA105" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB105" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC105" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AD105" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AE105" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF105" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG105" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AH105" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI105" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AJ105" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK105" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL105" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AM105" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN105" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AO105" t="n">
         <v>0</v>
       </c>
       <c r="AP105" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AQ105" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AR105" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AS105" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AT105" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AU105" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AV105" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AW105" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AX105" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AY105" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AZ105" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BA105" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BB105" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC105" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BD105" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="BE105" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="BF105" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BG105" t="n">
         <v>0</v>
@@ -21227,7 +21227,7 @@
         <v>0</v>
       </c>
       <c r="BI105" s="3" t="n">
-        <v>46166.66666666666</v>
+        <v>46166.65625</v>
       </c>
     </row>
     <row r="106">
@@ -21236,27 +21236,27 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,133 +21289,133 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>2.29</v>
+        <v>1.33</v>
       </c>
       <c r="Q106" t="n">
-        <v>2.76</v>
+        <v>5.2</v>
       </c>
       <c r="R106" t="n">
-        <v>3.61</v>
+        <v>9</v>
       </c>
       <c r="S106" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="T106" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U106" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="V106" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W106" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="X106" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Y106" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z106" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AA106" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC106" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD106" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE106" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF106" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AG106" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AH106" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI106" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AJ106" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK106" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AL106" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AM106" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN106" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AO106" t="n">
         <v>0</v>
       </c>
       <c r="AP106" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AQ106" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR106" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AS106" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AT106" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AU106" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AV106" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW106" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AX106" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY106" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ106" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BA106" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BB106" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC106" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BD106" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE106" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BF106" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG106" t="n">
         <v>0</v>
@@ -21424,7 +21424,7 @@
         <v>0</v>
       </c>
       <c r="BI106" s="3" t="n">
-        <v>46166.66666666666</v>
+        <v>46166.65625</v>
       </c>
     </row>
     <row r="107">
@@ -21433,27 +21433,27 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,133 +21486,133 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Q107" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="R107" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S107" t="n">
-        <v>0</v>
+        <v>5.51</v>
       </c>
       <c r="T107" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U107" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="V107" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W107" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="X107" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Y107" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z107" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA107" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB107" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC107" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AD107" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AE107" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF107" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG107" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AH107" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI107" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AJ107" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK107" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AL107" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AM107" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN107" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AO107" t="n">
         <v>0</v>
       </c>
       <c r="AP107" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AQ107" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AR107" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AS107" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AT107" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AU107" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AV107" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AW107" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AX107" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AY107" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AZ107" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BA107" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BB107" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BC107" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BD107" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="BE107" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF107" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG107" t="n">
         <v>0</v>
@@ -21621,7 +21621,7 @@
         <v>0</v>
       </c>
       <c r="BI107" s="3" t="n">
-        <v>46166.66666666666</v>
+        <v>46166.65625</v>
       </c>
     </row>
     <row r="108">
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>2.29</v>
+        <v>1.51</v>
       </c>
       <c r="Q110" t="n">
-        <v>2.69</v>
+        <v>3.5</v>
       </c>
       <c r="R110" t="n">
-        <v>3.43</v>
+        <v>7.25</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q111" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R111" t="n">
-        <v>4.83</v>
+        <v>0</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22319,10 +22319,10 @@
         <v>0</v>
       </c>
       <c r="AE111" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AF111" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AG111" t="n">
         <v>0</v>
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q113" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="R113" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Q114" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="R114" t="n">
-        <v>0</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>1.51</v>
+        <v>2.29</v>
       </c>
       <c r="Q116" t="n">
-        <v>3.5</v>
+        <v>2.69</v>
       </c>
       <c r="R116" t="n">
-        <v>7.25</v>
+        <v>3.43</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23403,12 +23403,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23591,7 +23591,7 @@
         <v>0</v>
       </c>
       <c r="BI117" s="3" t="n">
-        <v>46166.6875</v>
+        <v>46166.66666666666</v>
       </c>
     </row>
     <row r="118">
@@ -23600,12 +23600,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>1.78</v>
+        <v>2.8</v>
       </c>
       <c r="Q118" t="n">
-        <v>2.96</v>
+        <v>3.27</v>
       </c>
       <c r="R118" t="n">
-        <v>5.01</v>
+        <v>2.64</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23698,10 +23698,10 @@
         <v>0</v>
       </c>
       <c r="AE118" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF118" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG118" t="n">
         <v>0</v>
@@ -23788,7 +23788,7 @@
         <v>0</v>
       </c>
       <c r="BI118" s="3" t="n">
-        <v>46166.6875</v>
+        <v>46166.66666666666</v>
       </c>
     </row>
     <row r="119">
@@ -23797,12 +23797,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q119" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R119" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23895,10 +23895,10 @@
         <v>0</v>
       </c>
       <c r="AE119" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AF119" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG119" t="n">
         <v>0</v>
@@ -23985,7 +23985,7 @@
         <v>0</v>
       </c>
       <c r="BI119" s="3" t="n">
-        <v>46166.6875</v>
+        <v>46166.66666666666</v>
       </c>
     </row>
     <row r="120">
@@ -23994,27 +23994,27 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24047,13 +24047,13 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Q120" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="R120" t="n">
-        <v>5.44</v>
+        <v>0</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -24092,10 +24092,10 @@
         <v>0</v>
       </c>
       <c r="AE120" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF120" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG120" t="n">
         <v>0</v>
@@ -24182,7 +24182,7 @@
         <v>0</v>
       </c>
       <c r="BI120" s="3" t="n">
-        <v>46166.6875</v>
+        <v>46166.66666666666</v>
       </c>
     </row>
     <row r="121">
@@ -24191,12 +24191,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24379,7 +24379,7 @@
         <v>0</v>
       </c>
       <c r="BI121" s="3" t="n">
-        <v>46166.6875</v>
+        <v>46166.66666666666</v>
       </c>
     </row>
     <row r="122">
@@ -24388,7 +24388,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>2.33</v>
+        <v>1.78</v>
       </c>
       <c r="Q122" t="n">
-        <v>2.75</v>
+        <v>2.96</v>
       </c>
       <c r="R122" t="n">
-        <v>3.26</v>
+        <v>5.01</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24576,7 +24576,7 @@
         <v>0</v>
       </c>
       <c r="BI122" s="3" t="n">
-        <v>46166.70833333334</v>
+        <v>46166.6875</v>
       </c>
     </row>
     <row r="123">
@@ -24585,12 +24585,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24773,7 +24773,7 @@
         <v>0</v>
       </c>
       <c r="BI123" s="3" t="n">
-        <v>46166.70833333334</v>
+        <v>46166.6875</v>
       </c>
     </row>
     <row r="124">
@@ -24782,12 +24782,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Q124" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R124" t="n">
-        <v>0</v>
+        <v>5.44</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24880,10 +24880,10 @@
         <v>0</v>
       </c>
       <c r="AE124" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF124" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG124" t="n">
         <v>0</v>
@@ -24970,7 +24970,7 @@
         <v>0</v>
       </c>
       <c r="BI124" s="3" t="n">
-        <v>46166.70833333334</v>
+        <v>46166.6875</v>
       </c>
     </row>
     <row r="125">
@@ -24979,12 +24979,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25167,7 +25167,7 @@
         <v>0</v>
       </c>
       <c r="BI125" s="3" t="n">
-        <v>46166.70833333334</v>
+        <v>46166.6875</v>
       </c>
     </row>
     <row r="126">
@@ -25176,12 +25176,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25229,13 +25229,13 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Q126" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R126" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -25364,7 +25364,7 @@
         <v>0</v>
       </c>
       <c r="BI126" s="3" t="n">
-        <v>46166.72916666666</v>
+        <v>46166.6875</v>
       </c>
     </row>
     <row r="127">
@@ -25373,12 +25373,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25561,7 +25561,7 @@
         <v>0</v>
       </c>
       <c r="BI127" s="3" t="n">
-        <v>46166.75</v>
+        <v>46166.70833333334</v>
       </c>
     </row>
     <row r="128">
@@ -25570,12 +25570,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Q128" t="n">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="R128" t="n">
-        <v>6.19</v>
+        <v>0</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25674,10 +25674,10 @@
         <v>0</v>
       </c>
       <c r="AG128" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH128" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI128" t="n">
         <v>0</v>
@@ -25758,7 +25758,7 @@
         <v>0</v>
       </c>
       <c r="BI128" s="3" t="n">
-        <v>46166.75</v>
+        <v>46166.70833333334</v>
       </c>
     </row>
     <row r="129">
@@ -25767,12 +25767,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q129" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R129" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -25955,7 +25955,7 @@
         <v>0</v>
       </c>
       <c r="BI129" s="3" t="n">
-        <v>46166.75</v>
+        <v>46166.70833333334</v>
       </c>
     </row>
     <row r="130">
@@ -25964,12 +25964,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26017,13 +26017,13 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q130" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="R130" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="S130" t="n">
         <v>0</v>
@@ -26152,7 +26152,7 @@
         <v>0</v>
       </c>
       <c r="BI130" s="3" t="n">
-        <v>46166.75</v>
+        <v>46166.70833333334</v>
       </c>
     </row>
     <row r="131">
@@ -26161,12 +26161,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26214,13 +26214,13 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q131" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R131" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="S131" t="n">
         <v>0</v>
@@ -26349,7 +26349,7 @@
         <v>0</v>
       </c>
       <c r="BI131" s="3" t="n">
-        <v>46166.75</v>
+        <v>46166.72916666666</v>
       </c>
     </row>
     <row r="132">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q132" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="R132" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26555,12 +26555,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26743,7 +26743,7 @@
         <v>0</v>
       </c>
       <c r="BI133" s="3" t="n">
-        <v>46166.76041666666</v>
+        <v>46166.75</v>
       </c>
     </row>
     <row r="134">
@@ -26752,7 +26752,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>2.06</v>
+        <v>2.36</v>
       </c>
       <c r="Q134" t="n">
-        <v>3.32</v>
+        <v>3.04</v>
       </c>
       <c r="R134" t="n">
-        <v>3.49</v>
+        <v>3.12</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -26850,10 +26850,10 @@
         <v>0</v>
       </c>
       <c r="AE134" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF134" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG134" t="n">
         <v>0</v>
@@ -26940,7 +26940,7 @@
         <v>0</v>
       </c>
       <c r="BI134" s="3" t="n">
-        <v>46166.77083333334</v>
+        <v>46166.75</v>
       </c>
     </row>
     <row r="135">
@@ -26949,12 +26949,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>1.95</v>
+        <v>1.51</v>
       </c>
       <c r="Q135" t="n">
-        <v>3.38</v>
+        <v>4.84</v>
       </c>
       <c r="R135" t="n">
-        <v>4.32</v>
+        <v>6.19</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -27053,10 +27053,10 @@
         <v>0</v>
       </c>
       <c r="AG135" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH135" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI135" t="n">
         <v>0</v>
@@ -27137,7 +27137,7 @@
         <v>0</v>
       </c>
       <c r="BI135" s="3" t="n">
-        <v>46166.77083333334</v>
+        <v>46166.75</v>
       </c>
     </row>
     <row r="136">
@@ -27146,7 +27146,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>2.13</v>
+        <v>1.93</v>
       </c>
       <c r="Q136" t="n">
-        <v>2.73</v>
+        <v>2.85</v>
       </c>
       <c r="R136" t="n">
-        <v>3.79</v>
+        <v>4.35</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27334,7 +27334,7 @@
         <v>0</v>
       </c>
       <c r="BI136" s="3" t="n">
-        <v>46166.79166666666</v>
+        <v>46166.75</v>
       </c>
     </row>
     <row r="137">
@@ -27343,12 +27343,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27531,7 +27531,7 @@
         <v>0</v>
       </c>
       <c r="BI137" s="3" t="n">
-        <v>46166.79166666666</v>
+        <v>46166.75</v>
       </c>
     </row>
     <row r="138">
@@ -27540,12 +27540,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -27555,12 +27555,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -27728,7 +27728,7 @@
         <v>0</v>
       </c>
       <c r="BI138" s="3" t="n">
-        <v>46166.79166666666</v>
+        <v>46166.76041666666</v>
       </c>
     </row>
     <row r="139">
@@ -27737,12 +27737,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27790,13 +27790,13 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q139" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R139" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -27835,10 +27835,10 @@
         <v>0</v>
       </c>
       <c r="AE139" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF139" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG139" t="n">
         <v>0</v>
@@ -27925,7 +27925,7 @@
         <v>0</v>
       </c>
       <c r="BI139" s="3" t="n">
-        <v>46166.83333333334</v>
+        <v>46166.77083333334</v>
       </c>
     </row>
     <row r="140">
@@ -27934,12 +27934,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q140" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R140" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28122,7 +28122,7 @@
         <v>0</v>
       </c>
       <c r="BI140" s="3" t="n">
-        <v>46166.83333333334</v>
+        <v>46166.77083333334</v>
       </c>
     </row>
     <row r="141">
@@ -28131,12 +28131,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28184,13 +28184,13 @@
         </is>
       </c>
       <c r="P141" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Q141" t="n">
-        <v>5.24</v>
+        <v>0</v>
       </c>
       <c r="R141" t="n">
-        <v>7.08</v>
+        <v>0</v>
       </c>
       <c r="S141" t="n">
         <v>0</v>
@@ -28235,10 +28235,10 @@
         <v>0</v>
       </c>
       <c r="AG141" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH141" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI141" t="n">
         <v>0</v>
@@ -28319,7 +28319,7 @@
         <v>0</v>
       </c>
       <c r="BI141" s="3" t="n">
-        <v>46166.83333333334</v>
+        <v>46166.79166666666</v>
       </c>
     </row>
     <row r="142">
@@ -28328,12 +28328,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28516,7 +28516,7 @@
         <v>0</v>
       </c>
       <c r="BI142" s="3" t="n">
-        <v>46166.83333333334</v>
+        <v>46166.79166666666</v>
       </c>
     </row>
     <row r="143">
@@ -28525,12 +28525,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28578,13 +28578,13 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q143" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="R143" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="S143" t="n">
         <v>0</v>
@@ -28713,7 +28713,7 @@
         <v>0</v>
       </c>
       <c r="BI143" s="3" t="n">
-        <v>46166.83333333334</v>
+        <v>46166.79166666666</v>
       </c>
     </row>
     <row r="144">
@@ -28722,12 +28722,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28775,13 +28775,13 @@
         </is>
       </c>
       <c r="P144" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q144" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="R144" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S144" t="n">
         <v>0</v>
@@ -28910,7 +28910,7 @@
         <v>0</v>
       </c>
       <c r="BI144" s="3" t="n">
-        <v>46166.84027777778</v>
+        <v>46166.83333333334</v>
       </c>
     </row>
     <row r="145">
@@ -28919,12 +28919,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -28972,13 +28972,13 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q145" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R145" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="S145" t="n">
         <v>0</v>
@@ -29107,7 +29107,7 @@
         <v>0</v>
       </c>
       <c r="BI145" s="3" t="n">
-        <v>46166.85416666666</v>
+        <v>46166.83333333334</v>
       </c>
     </row>
     <row r="146">
@@ -29116,12 +29116,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29169,13 +29169,13 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Q146" t="n">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="R146" t="n">
-        <v>0</v>
+        <v>7.08</v>
       </c>
       <c r="S146" t="n">
         <v>0</v>
@@ -29220,10 +29220,10 @@
         <v>0</v>
       </c>
       <c r="AG146" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH146" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI146" t="n">
         <v>0</v>
@@ -29304,7 +29304,7 @@
         <v>0</v>
       </c>
       <c r="BI146" s="3" t="n">
-        <v>46166.85416666666</v>
+        <v>46166.83333333334</v>
       </c>
     </row>
     <row r="147">
@@ -29313,12 +29313,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29366,13 +29366,13 @@
         </is>
       </c>
       <c r="P147" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q147" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="R147" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="S147" t="n">
         <v>0</v>
@@ -29411,10 +29411,10 @@
         <v>0</v>
       </c>
       <c r="AE147" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF147" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG147" t="n">
         <v>0</v>
@@ -29501,7 +29501,7 @@
         <v>0</v>
       </c>
       <c r="BI147" s="3" t="n">
-        <v>46166.85416666666</v>
+        <v>46166.83333333334</v>
       </c>
     </row>
     <row r="148">
@@ -29510,12 +29510,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29698,7 +29698,7 @@
         <v>0</v>
       </c>
       <c r="BI148" s="3" t="n">
-        <v>46166.875</v>
+        <v>46166.83333333334</v>
       </c>
     </row>
     <row r="149">
@@ -29707,12 +29707,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29760,13 +29760,13 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q149" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R149" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -29895,7 +29895,7 @@
         <v>0</v>
       </c>
       <c r="BI149" s="3" t="n">
-        <v>46166.875</v>
+        <v>46166.84027777778</v>
       </c>
     </row>
     <row r="150">
@@ -29904,12 +29904,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -29957,141 +29957,1126 @@
         </is>
       </c>
       <c r="P150" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q150" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="R150" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="S150" t="n">
+        <v>0</v>
+      </c>
+      <c r="T150" t="n">
+        <v>0</v>
+      </c>
+      <c r="U150" t="n">
+        <v>0</v>
+      </c>
+      <c r="V150" t="n">
+        <v>0</v>
+      </c>
+      <c r="W150" t="n">
+        <v>0</v>
+      </c>
+      <c r="X150" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y150" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE150" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AF150" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY150" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ150" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA150" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB150" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC150" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD150" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE150" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF150" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG150" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH150" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI150" s="3" t="n">
+        <v>46166.85416666666</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Oriente Petrolero</t>
+        </is>
+      </c>
+      <c r="G151" t="n">
+        <v>0</v>
+      </c>
+      <c r="H151" t="n">
+        <v>0</v>
+      </c>
+      <c r="I151" t="n">
+        <v>0</v>
+      </c>
+      <c r="J151" t="n">
+        <v>0</v>
+      </c>
+      <c r="K151" t="n">
+        <v>0</v>
+      </c>
+      <c r="L151" t="n">
+        <v>0</v>
+      </c>
+      <c r="M151" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N151" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P151" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q151" t="n">
+        <v>0</v>
+      </c>
+      <c r="R151" t="n">
+        <v>0</v>
+      </c>
+      <c r="S151" t="n">
+        <v>0</v>
+      </c>
+      <c r="T151" t="n">
+        <v>0</v>
+      </c>
+      <c r="U151" t="n">
+        <v>0</v>
+      </c>
+      <c r="V151" t="n">
+        <v>0</v>
+      </c>
+      <c r="W151" t="n">
+        <v>0</v>
+      </c>
+      <c r="X151" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y151" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY151" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ151" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA151" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB151" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC151" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD151" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE151" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF151" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG151" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH151" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI151" s="3" t="n">
+        <v>46166.85416666666</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Vasco da Gama</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Bragantino</t>
+        </is>
+      </c>
+      <c r="G152" t="n">
+        <v>0</v>
+      </c>
+      <c r="H152" t="n">
+        <v>0</v>
+      </c>
+      <c r="I152" t="n">
+        <v>0</v>
+      </c>
+      <c r="J152" t="n">
+        <v>0</v>
+      </c>
+      <c r="K152" t="n">
+        <v>0</v>
+      </c>
+      <c r="L152" t="n">
+        <v>0</v>
+      </c>
+      <c r="M152" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N152" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P152" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Q152" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="R152" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="S152" t="n">
+        <v>0</v>
+      </c>
+      <c r="T152" t="n">
+        <v>0</v>
+      </c>
+      <c r="U152" t="n">
+        <v>0</v>
+      </c>
+      <c r="V152" t="n">
+        <v>0</v>
+      </c>
+      <c r="W152" t="n">
+        <v>0</v>
+      </c>
+      <c r="X152" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y152" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ152" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA152" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB152" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC152" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD152" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE152" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF152" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG152" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH152" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI152" s="3" t="n">
+        <v>46166.85416666666</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Chile Primera B</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>San Luis</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Magallanes</t>
+        </is>
+      </c>
+      <c r="G153" t="n">
+        <v>0</v>
+      </c>
+      <c r="H153" t="n">
+        <v>0</v>
+      </c>
+      <c r="I153" t="n">
+        <v>0</v>
+      </c>
+      <c r="J153" t="n">
+        <v>0</v>
+      </c>
+      <c r="K153" t="n">
+        <v>0</v>
+      </c>
+      <c r="L153" t="n">
+        <v>0</v>
+      </c>
+      <c r="M153" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N153" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P153" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q153" t="n">
+        <v>0</v>
+      </c>
+      <c r="R153" t="n">
+        <v>0</v>
+      </c>
+      <c r="S153" t="n">
+        <v>0</v>
+      </c>
+      <c r="T153" t="n">
+        <v>0</v>
+      </c>
+      <c r="U153" t="n">
+        <v>0</v>
+      </c>
+      <c r="V153" t="n">
+        <v>0</v>
+      </c>
+      <c r="W153" t="n">
+        <v>0</v>
+      </c>
+      <c r="X153" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y153" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY153" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ153" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA153" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB153" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC153" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD153" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE153" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF153" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG153" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH153" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI153" s="3" t="n">
+        <v>46166.875</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>USA MLS Next Pro</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Columbus Crew II</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Toronto II</t>
+        </is>
+      </c>
+      <c r="G154" t="n">
+        <v>0</v>
+      </c>
+      <c r="H154" t="n">
+        <v>0</v>
+      </c>
+      <c r="I154" t="n">
+        <v>0</v>
+      </c>
+      <c r="J154" t="n">
+        <v>0</v>
+      </c>
+      <c r="K154" t="n">
+        <v>0</v>
+      </c>
+      <c r="L154" t="n">
+        <v>0</v>
+      </c>
+      <c r="M154" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N154" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P154" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q154" t="n">
+        <v>0</v>
+      </c>
+      <c r="R154" t="n">
+        <v>0</v>
+      </c>
+      <c r="S154" t="n">
+        <v>0</v>
+      </c>
+      <c r="T154" t="n">
+        <v>0</v>
+      </c>
+      <c r="U154" t="n">
+        <v>0</v>
+      </c>
+      <c r="V154" t="n">
+        <v>0</v>
+      </c>
+      <c r="W154" t="n">
+        <v>0</v>
+      </c>
+      <c r="X154" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y154" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ154" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA154" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB154" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC154" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD154" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE154" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF154" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG154" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH154" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI154" s="3" t="n">
+        <v>46166.875</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Los Angeles FC</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Seattle Sounders</t>
+        </is>
+      </c>
+      <c r="G155" t="n">
+        <v>0</v>
+      </c>
+      <c r="H155" t="n">
+        <v>0</v>
+      </c>
+      <c r="I155" t="n">
+        <v>0</v>
+      </c>
+      <c r="J155" t="n">
+        <v>0</v>
+      </c>
+      <c r="K155" t="n">
+        <v>0</v>
+      </c>
+      <c r="L155" t="n">
+        <v>0</v>
+      </c>
+      <c r="M155" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N155" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P155" t="n">
         <v>2</v>
       </c>
-      <c r="Q150" t="n">
+      <c r="Q155" t="n">
         <v>3.83</v>
       </c>
-      <c r="R150" t="n">
+      <c r="R155" t="n">
         <v>3.72</v>
       </c>
-      <c r="S150" t="n">
-        <v>0</v>
-      </c>
-      <c r="T150" t="n">
-        <v>0</v>
-      </c>
-      <c r="U150" t="n">
-        <v>0</v>
-      </c>
-      <c r="V150" t="n">
-        <v>0</v>
-      </c>
-      <c r="W150" t="n">
-        <v>0</v>
-      </c>
-      <c r="X150" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y150" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE150" t="n">
+      <c r="S155" t="n">
+        <v>0</v>
+      </c>
+      <c r="T155" t="n">
+        <v>0</v>
+      </c>
+      <c r="U155" t="n">
+        <v>0</v>
+      </c>
+      <c r="V155" t="n">
+        <v>0</v>
+      </c>
+      <c r="W155" t="n">
+        <v>0</v>
+      </c>
+      <c r="X155" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y155" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE155" t="n">
         <v>1.62</v>
       </c>
-      <c r="AF150" t="n">
+      <c r="AF155" t="n">
         <v>2.15</v>
       </c>
-      <c r="AG150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY150" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ150" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA150" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB150" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC150" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD150" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE150" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF150" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG150" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH150" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI150" s="3" t="n">
+      <c r="AG155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ155" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA155" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB155" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC155" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD155" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE155" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF155" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG155" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH155" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI155" s="3" t="n">
         <v>46166.91666666666</v>
       </c>
     </row>

--- a/jogos_2026-05-24.xlsx
+++ b/jogos_2026-05-24.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI155"/>
+  <dimension ref="A1:BI156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.97</v>
+        <v>1.29</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.18</v>
+        <v>4.95</v>
       </c>
       <c r="R9" t="n">
-        <v>3.61</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.29</v>
+        <v>1.97</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.95</v>
+        <v>3.18</v>
       </c>
       <c r="R10" t="n">
-        <v>8.199999999999999</v>
+        <v>3.61</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="R24" t="n">
-        <v>5.14</v>
+        <v>3.8</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>4.92</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7156,10 +7156,10 @@
         <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>4.92</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7353,10 +7353,10 @@
         <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.82</v>
+        <v>1.59</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.06</v>
+        <v>4.37</v>
       </c>
       <c r="R36" t="n">
-        <v>4.06</v>
+        <v>5.41</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="AF36" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.59</v>
+        <v>1.82</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.37</v>
+        <v>4.06</v>
       </c>
       <c r="R37" t="n">
-        <v>5.41</v>
+        <v>4.06</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7741,10 +7741,10 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.69</v>
+        <v>1.44</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="R38" t="n">
-        <v>4.57</v>
+        <v>6.14</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.28</v>
+        <v>1.63</v>
       </c>
       <c r="Q39" t="n">
-        <v>5.41</v>
+        <v>3.96</v>
       </c>
       <c r="R39" t="n">
-        <v>8.039999999999999</v>
+        <v>4.85</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Q40" t="n">
-        <v>5</v>
+        <v>5.41</v>
       </c>
       <c r="R40" t="n">
-        <v>6</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.3</v>
+        <v>1.69</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="R41" t="n">
-        <v>2.6</v>
+        <v>4.57</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.6</v>
+        <v>4.58</v>
       </c>
       <c r="R42" t="n">
-        <v>6.14</v>
+        <v>6</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.63</v>
+        <v>2.95</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.96</v>
+        <v>3.53</v>
       </c>
       <c r="R43" t="n">
-        <v>4.85</v>
+        <v>2.2</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -8923,10 +8923,10 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.93</v>
+        <v>3</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.99</v>
+        <v>3.66</v>
       </c>
       <c r="R44" t="n">
-        <v>3.22</v>
+        <v>2.13</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.66</v>
+        <v>3.6</v>
       </c>
       <c r="R45" t="n">
-        <v>2.13</v>
+        <v>2.6</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.42</v>
+        <v>1.93</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.58</v>
+        <v>3.99</v>
       </c>
       <c r="R46" t="n">
-        <v>6</v>
+        <v>3.22</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.95</v>
+        <v>1.33</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.53</v>
+        <v>5</v>
       </c>
       <c r="R47" t="n">
-        <v>2.2</v>
+        <v>6</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>3.82</v>
+        <v>2.29</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.82</v>
+        <v>3.4</v>
       </c>
       <c r="R49" t="n">
-        <v>2.03</v>
+        <v>2.83</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.63</v>
+        <v>7</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.82</v>
+        <v>4.43</v>
       </c>
       <c r="R50" t="n">
-        <v>2.68</v>
+        <v>1.55</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.29</v>
+        <v>2.52</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R51" t="n">
-        <v>2.83</v>
+        <v>2.94</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1.44</v>
+        <v>2.25</v>
       </c>
       <c r="Q58" t="n">
-        <v>5.57</v>
+        <v>3.73</v>
       </c>
       <c r="R58" t="n">
-        <v>7.02</v>
+        <v>3.31</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>4.54</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>4.54</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12469,10 +12469,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF61" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>5.57</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>7.02</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13060,10 +13060,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF64" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF67" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF68" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>5.37</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15233,10 +15233,10 @@
         <v>0</v>
       </c>
       <c r="AG75" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH75" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,133 +15379,133 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T76" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U76" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="V76" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W76" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="X76" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z76" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA76" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB76" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC76" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AD76" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF76" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG76" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AH76" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AI76" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AJ76" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL76" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AM76" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN76" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="AO76" t="n">
         <v>0</v>
       </c>
       <c r="AP76" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ76" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AR76" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AS76" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AT76" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AU76" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AV76" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AW76" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AX76" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AY76" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AZ76" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BA76" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BB76" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BC76" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="BD76" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BE76" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="BF76" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG76" t="n">
         <v>0</v>
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,133 +15576,133 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>8.25</v>
+        <v>1.53</v>
       </c>
       <c r="Q77" t="n">
-        <v>5.37</v>
+        <v>4.2</v>
       </c>
       <c r="R77" t="n">
-        <v>1.35</v>
+        <v>6.75</v>
       </c>
       <c r="S77" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T77" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U77" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V77" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W77" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="X77" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Y77" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z77" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA77" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB77" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC77" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AD77" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="AE77" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF77" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG77" t="n">
-        <v>1.95</v>
+        <v>3.12</v>
       </c>
       <c r="AH77" t="n">
-        <v>1.85</v>
+        <v>1.31</v>
       </c>
       <c r="AI77" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AJ77" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK77" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL77" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AM77" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN77" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AO77" t="n">
         <v>0</v>
       </c>
       <c r="AP77" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ77" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AR77" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AS77" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AT77" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AU77" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AV77" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AW77" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AX77" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AY77" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ77" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BA77" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BB77" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BC77" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD77" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE77" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BF77" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG77" t="n">
         <v>0</v>
@@ -15725,22 +15725,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>6.19</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>6.19</v>
+        <v>0</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>4.94</v>
+        <v>0</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1.96</v>
+        <v>4.15</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.81</v>
+        <v>3.73</v>
       </c>
       <c r="R81" t="n">
-        <v>3.73</v>
+        <v>1.88</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16409,10 +16409,10 @@
         <v>0</v>
       </c>
       <c r="AE81" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF81" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG81" t="n">
         <v>0</v>
@@ -16513,22 +16513,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16612,10 +16612,10 @@
         <v>0</v>
       </c>
       <c r="AG82" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH82" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AI82" t="n">
         <v>0</v>
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>3.77</v>
+        <v>1.96</v>
       </c>
       <c r="Q83" t="n">
-        <v>4.17</v>
+        <v>3.81</v>
       </c>
       <c r="R83" t="n">
-        <v>1.86</v>
+        <v>3.73</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF83" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>UD Las Palmas</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Real Zaragoza</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="Q84" t="n">
-        <v>4.46</v>
+        <v>4.53</v>
       </c>
       <c r="R84" t="n">
-        <v>6.22</v>
+        <v>4.32</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17000,16 +17000,16 @@
         <v>0</v>
       </c>
       <c r="AE84" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF84" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG84" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH84" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AI84" t="n">
         <v>0</v>
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>3.19</v>
+        <v>5.25</v>
       </c>
       <c r="Q85" t="n">
-        <v>3.19</v>
+        <v>4.22</v>
       </c>
       <c r="R85" t="n">
-        <v>2.41</v>
+        <v>1.63</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17197,10 +17197,10 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF85" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG85" t="n">
         <v>0</v>
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>5.25</v>
+        <v>1.67</v>
       </c>
       <c r="Q86" t="n">
-        <v>4.22</v>
+        <v>4.17</v>
       </c>
       <c r="R86" t="n">
-        <v>1.63</v>
+        <v>4.94</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17394,10 +17394,10 @@
         <v>0</v>
       </c>
       <c r="AE86" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF86" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG86" t="n">
         <v>0</v>
@@ -17498,22 +17498,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>UD Las Palmas</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Real Zaragoza</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>6.22</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF87" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>4.15</v>
+        <v>1.77</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.73</v>
+        <v>4.07</v>
       </c>
       <c r="R88" t="n">
-        <v>1.88</v>
+        <v>4.22</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>2.59</v>
+        <v>3.19</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.42</v>
+        <v>3.19</v>
       </c>
       <c r="R90" t="n">
-        <v>2.75</v>
+        <v>2.41</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1.77</v>
+        <v>1.32</v>
       </c>
       <c r="Q91" t="n">
-        <v>4.07</v>
+        <v>5.88</v>
       </c>
       <c r="R91" t="n">
-        <v>4.22</v>
+        <v>8.4</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>1.32</v>
+        <v>3.77</v>
       </c>
       <c r="Q92" t="n">
-        <v>5.88</v>
+        <v>4.17</v>
       </c>
       <c r="R92" t="n">
-        <v>8.4</v>
+        <v>1.86</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19857,27 +19857,27 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Técnico Universitario</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q99" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>5.21</v>
+        <v>0</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -20045,7 +20045,7 @@
         <v>0</v>
       </c>
       <c r="BI99" s="3" t="n">
-        <v>46166.625</v>
+        <v>46166.60416666666</v>
       </c>
     </row>
     <row r="100">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Técnico Universitario</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Forge FC</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q100" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>5.21</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20251,12 +20251,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Chacarita Juniors</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Forge FC</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>4.97</v>
+        <v>0</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20439,7 +20439,7 @@
         <v>0</v>
       </c>
       <c r="BI101" s="3" t="n">
-        <v>46166.64583333334</v>
+        <v>46166.625</v>
       </c>
     </row>
     <row r="102">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Chacarita Juniors</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>2.8</v>
+        <v>1.76</v>
       </c>
       <c r="Q102" t="n">
-        <v>2.75</v>
+        <v>3.19</v>
       </c>
       <c r="R102" t="n">
-        <v>2.8</v>
+        <v>4.97</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20645,27 +20645,27 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,133 +20698,133 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>5</v>
+        <v>2.8</v>
       </c>
       <c r="Q103" t="n">
-        <v>4.26</v>
+        <v>2.75</v>
       </c>
       <c r="R103" t="n">
-        <v>1.63</v>
+        <v>2.8</v>
       </c>
       <c r="S103" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="T103" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="U103" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="V103" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W103" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="X103" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Y103" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z103" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AA103" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC103" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD103" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AE103" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF103" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="AG103" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AH103" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AI103" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AJ103" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK103" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AL103" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AM103" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN103" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AO103" t="n">
         <v>0</v>
       </c>
       <c r="AP103" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AQ103" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AR103" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AS103" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AT103" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AU103" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AV103" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AW103" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AX103" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AY103" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AZ103" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BA103" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="BB103" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC103" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="BD103" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="BE103" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="BF103" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="BG103" t="n">
         <v>0</v>
@@ -20833,7 +20833,7 @@
         <v>0</v>
       </c>
       <c r="BI103" s="3" t="n">
-        <v>46166.65625</v>
+        <v>46166.64583333334</v>
       </c>
     </row>
     <row r="104">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,133 +20895,133 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>1.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.68</v>
+        <v>5.2</v>
       </c>
       <c r="R104" t="n">
-        <v>5.1</v>
+        <v>1.33</v>
       </c>
       <c r="S104" t="n">
-        <v>2.31</v>
+        <v>8.5</v>
       </c>
       <c r="T104" t="n">
-        <v>2.09</v>
+        <v>2.47</v>
       </c>
       <c r="U104" t="n">
-        <v>4.54</v>
+        <v>1.77</v>
       </c>
       <c r="V104" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="W104" t="n">
-        <v>2.55</v>
+        <v>3.1</v>
       </c>
       <c r="X104" t="n">
-        <v>3.34</v>
+        <v>2.72</v>
       </c>
       <c r="Y104" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z104" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AA104" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB104" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC104" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD104" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AE104" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF104" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG104" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AH104" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI104" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="AJ104" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK104" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AL104" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AM104" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN104" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AO104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP104" t="n">
         <v>1.32</v>
       </c>
-      <c r="Z104" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AA104" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB104" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC104" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD104" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AE104" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AF104" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AG104" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AH104" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AI104" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AJ104" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK104" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AL104" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AM104" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN104" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AO104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP104" t="n">
+      <c r="AQ104" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AR104" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AS104" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AT104" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AU104" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV104" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AW104" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AX104" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AY104" t="n">
         <v>1.29</v>
       </c>
-      <c r="AQ104" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR104" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AS104" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AT104" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AU104" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV104" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AW104" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AX104" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AY104" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AZ104" t="n">
-        <v>1.35</v>
+        <v>3.7</v>
       </c>
       <c r="BA104" t="n">
-        <v>3.65</v>
+        <v>1.36</v>
       </c>
       <c r="BB104" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="BC104" t="n">
-        <v>2.5</v>
+        <v>1.94</v>
       </c>
       <c r="BD104" t="n">
-        <v>3.28</v>
+        <v>4.15</v>
       </c>
       <c r="BE104" t="n">
-        <v>1.52</v>
+        <v>1.77</v>
       </c>
       <c r="BF104" t="n">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="BG104" t="n">
         <v>0</v>
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,133 +21092,133 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>9.199999999999999</v>
+        <v>5</v>
       </c>
       <c r="Q105" t="n">
-        <v>5.2</v>
+        <v>4.26</v>
       </c>
       <c r="R105" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="S105" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="T105" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="U105" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="V105" t="n">
         <v>1.33</v>
       </c>
-      <c r="S105" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="T105" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="U105" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="V105" t="n">
+      <c r="W105" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="X105" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="Y105" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Z105" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AA105" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AB105" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC105" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD105" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AE105" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF105" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AG105" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AH105" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI105" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AJ105" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK105" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AL105" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AM105" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN105" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AO105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP105" t="n">
         <v>1.36</v>
       </c>
-      <c r="W105" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="X105" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="Y105" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z105" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AA105" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB105" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC105" t="n">
+      <c r="AQ105" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AR105" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AS105" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AT105" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AU105" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AV105" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AW105" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AX105" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AY105" t="n">
         <v>1.24</v>
       </c>
-      <c r="AD105" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AE105" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AF105" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG105" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AH105" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI105" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="AJ105" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK105" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AL105" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AM105" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AN105" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AO105" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP105" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AQ105" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AR105" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AS105" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AT105" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AU105" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV105" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AW105" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AX105" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AY105" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AZ105" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="BA105" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="BB105" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="BC105" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="BD105" t="n">
-        <v>4.15</v>
+        <v>4.45</v>
       </c>
       <c r="BE105" t="n">
-        <v>1.77</v>
+        <v>1.88</v>
       </c>
       <c r="BF105" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="BG105" t="n">
         <v>0</v>
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,28 +21289,28 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>1.33</v>
+        <v>7.5</v>
       </c>
       <c r="Q106" t="n">
-        <v>5.2</v>
+        <v>4.78</v>
       </c>
       <c r="R106" t="n">
-        <v>9</v>
+        <v>1.4</v>
       </c>
       <c r="S106" t="n">
-        <v>1.77</v>
+        <v>5.51</v>
       </c>
       <c r="T106" t="n">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="U106" t="n">
-        <v>8.1</v>
+        <v>1.86</v>
       </c>
       <c r="V106" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W106" t="n">
-        <v>3.25</v>
+        <v>3.27</v>
       </c>
       <c r="X106" t="n">
         <v>2.59</v>
@@ -21319,100 +21319,100 @@
         <v>1.49</v>
       </c>
       <c r="Z106" t="n">
-        <v>6.05</v>
+        <v>6</v>
       </c>
       <c r="AA106" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AB106" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC106" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AD106" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AE106" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF106" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AG106" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AH106" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AI106" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AJ106" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK106" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AL106" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AM106" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AN106" t="n">
         <v>1.09</v>
       </c>
-      <c r="AB106" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC106" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AD106" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE106" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AF106" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AG106" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="AH106" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI106" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AJ106" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK106" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AL106" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AM106" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AN106" t="n">
-        <v>3.44</v>
-      </c>
       <c r="AO106" t="n">
         <v>0</v>
       </c>
       <c r="AP106" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="AQ106" t="n">
-        <v>1.46</v>
+        <v>1.61</v>
       </c>
       <c r="AR106" t="n">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="AS106" t="n">
-        <v>2.18</v>
+        <v>2.6</v>
       </c>
       <c r="AT106" t="n">
-        <v>2.85</v>
+        <v>3.45</v>
       </c>
       <c r="AU106" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="AV106" t="n">
-        <v>2.48</v>
+        <v>2.15</v>
       </c>
       <c r="AW106" t="n">
-        <v>1.92</v>
+        <v>1.7</v>
       </c>
       <c r="AX106" t="n">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="AY106" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AZ106" t="n">
-        <v>1.2</v>
+        <v>3.1</v>
       </c>
       <c r="BA106" t="n">
-        <v>5.3</v>
+        <v>1.47</v>
       </c>
       <c r="BB106" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="BC106" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="BD106" t="n">
-        <v>4.5</v>
+        <v>4.35</v>
       </c>
       <c r="BE106" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="BF106" t="n">
         <v>1.23</v>
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,133 +21486,133 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>7.5</v>
+        <v>1.7</v>
       </c>
       <c r="Q107" t="n">
-        <v>4.78</v>
+        <v>3.68</v>
       </c>
       <c r="R107" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="S107" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="T107" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="U107" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="V107" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="W107" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="X107" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="Y107" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z107" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AA107" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB107" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC107" t="n">
         <v>1.4</v>
       </c>
-      <c r="S107" t="n">
-        <v>5.51</v>
-      </c>
-      <c r="T107" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="U107" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="V107" t="n">
+      <c r="AD107" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AE107" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AF107" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG107" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AH107" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI107" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AJ107" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK107" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AL107" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AM107" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN107" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AO107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP107" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AQ107" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AR107" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AS107" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AT107" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU107" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV107" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AW107" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AX107" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AY107" t="n">
         <v>1.32</v>
       </c>
-      <c r="W107" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="X107" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="Y107" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="Z107" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA107" t="n">
+      <c r="AZ107" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BA107" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BB107" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BC107" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BD107" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="BE107" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BF107" t="n">
         <v>1.1</v>
-      </c>
-      <c r="AB107" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC107" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AD107" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AE107" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF107" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AG107" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AH107" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AI107" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AJ107" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK107" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AL107" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AM107" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AN107" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AO107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP107" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AQ107" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AR107" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS107" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AT107" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AU107" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AV107" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AW107" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AX107" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AY107" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AZ107" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BA107" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="BB107" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="BC107" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="BD107" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="BE107" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BF107" t="n">
-        <v>1.23</v>
       </c>
       <c r="BG107" t="n">
         <v>0</v>
@@ -21630,27 +21630,27 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,133 +21683,133 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Q108" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="R108" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="S108" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="T108" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U108" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="V108" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W108" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="X108" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Y108" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z108" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AA108" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC108" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD108" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE108" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF108" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AG108" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AH108" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI108" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AJ108" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK108" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AL108" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AM108" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN108" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="AO108" t="n">
         <v>0</v>
       </c>
       <c r="AP108" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AQ108" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AR108" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AS108" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AT108" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AU108" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AV108" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW108" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AX108" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY108" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ108" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BA108" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BB108" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC108" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BD108" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE108" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BF108" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG108" t="n">
         <v>0</v>
@@ -21818,7 +21818,7 @@
         <v>0</v>
       </c>
       <c r="BI108" s="3" t="n">
-        <v>46166.66666666666</v>
+        <v>46166.65625</v>
       </c>
     </row>
     <row r="109">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Q110" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>7.25</v>
+        <v>0</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="Q113" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="R113" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>1.32</v>
+        <v>2.29</v>
       </c>
       <c r="Q114" t="n">
-        <v>5.45</v>
+        <v>2.69</v>
       </c>
       <c r="R114" t="n">
-        <v>9.949999999999999</v>
+        <v>3.43</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>2.29</v>
+        <v>1.51</v>
       </c>
       <c r="Q116" t="n">
-        <v>2.69</v>
+        <v>3.5</v>
       </c>
       <c r="R116" t="n">
-        <v>3.43</v>
+        <v>7.25</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q117" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="R117" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>2.8</v>
+        <v>1.32</v>
       </c>
       <c r="Q118" t="n">
-        <v>3.27</v>
+        <v>5.45</v>
       </c>
       <c r="R118" t="n">
-        <v>2.64</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23698,10 +23698,10 @@
         <v>0</v>
       </c>
       <c r="AE118" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF118" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG118" t="n">
         <v>0</v>
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q119" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R119" t="n">
-        <v>4.83</v>
+        <v>0</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23895,10 +23895,10 @@
         <v>0</v>
       </c>
       <c r="AE119" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AF119" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AG119" t="n">
         <v>0</v>
@@ -23999,22 +23999,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24047,13 +24047,13 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q120" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="R120" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -24092,10 +24092,10 @@
         <v>0</v>
       </c>
       <c r="AE120" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF120" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG120" t="n">
         <v>0</v>
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q121" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R121" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24289,10 +24289,10 @@
         <v>0</v>
       </c>
       <c r="AE121" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AF121" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG121" t="n">
         <v>0</v>
@@ -24388,12 +24388,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Q122" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="R122" t="n">
-        <v>5.01</v>
+        <v>0</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24576,7 +24576,7 @@
         <v>0</v>
       </c>
       <c r="BI122" s="3" t="n">
-        <v>46166.6875</v>
+        <v>46166.66666666666</v>
       </c>
     </row>
     <row r="123">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Itabaiana</t>
+          <t>Ferroviária</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Brusque</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Anápolis</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Q124" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="R124" t="n">
-        <v>5.44</v>
+        <v>0</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24880,10 +24880,10 @@
         <v>0</v>
       </c>
       <c r="AE124" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF124" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG124" t="n">
         <v>0</v>
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Brusque</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Anápolis</t>
+          <t>Itabaiana</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Ferroviária</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25229,13 +25229,13 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q126" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="R126" t="n">
-        <v>0</v>
+        <v>5.01</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -25373,12 +25373,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Q127" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R127" t="n">
-        <v>0</v>
+        <v>5.44</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25471,10 +25471,10 @@
         <v>0</v>
       </c>
       <c r="AE127" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF127" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG127" t="n">
         <v>0</v>
@@ -25561,7 +25561,7 @@
         <v>0</v>
       </c>
       <c r="BI127" s="3" t="n">
-        <v>46166.70833333334</v>
+        <v>46166.6875</v>
       </c>
     </row>
     <row r="128">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q129" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R129" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26017,13 +26017,13 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q130" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R130" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="S130" t="n">
         <v>0</v>
@@ -26161,12 +26161,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>CS Emelec</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26214,13 +26214,13 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Q131" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R131" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="S131" t="n">
         <v>0</v>
@@ -26349,7 +26349,7 @@
         <v>0</v>
       </c>
       <c r="BI131" s="3" t="n">
-        <v>46166.72916666666</v>
+        <v>46166.70833333334</v>
       </c>
     </row>
     <row r="132">
@@ -26358,12 +26358,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>CS Emelec</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q132" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R132" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26546,7 +26546,7 @@
         <v>0</v>
       </c>
       <c r="BI132" s="3" t="n">
-        <v>46166.75</v>
+        <v>46166.72916666666</v>
       </c>
     </row>
     <row r="133">
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26608,13 +26608,13 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Q133" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="R133" t="n">
-        <v>0</v>
+        <v>6.19</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -26659,10 +26659,10 @@
         <v>0</v>
       </c>
       <c r="AG133" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH133" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI133" t="n">
         <v>0</v>
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q134" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="R134" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Q135" t="n">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="R135" t="n">
-        <v>6.19</v>
+        <v>0</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -27053,10 +27053,10 @@
         <v>0</v>
       </c>
       <c r="AG135" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH135" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI135" t="n">
         <v>0</v>
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27790,13 +27790,13 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="Q139" t="n">
-        <v>3.32</v>
+        <v>3.38</v>
       </c>
       <c r="R139" t="n">
-        <v>3.49</v>
+        <v>4.32</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -27835,10 +27835,10 @@
         <v>0</v>
       </c>
       <c r="AE139" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF139" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG139" t="n">
         <v>0</v>
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="Q140" t="n">
-        <v>3.38</v>
+        <v>3.32</v>
       </c>
       <c r="R140" t="n">
-        <v>4.32</v>
+        <v>3.49</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28032,10 +28032,10 @@
         <v>0</v>
       </c>
       <c r="AE140" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF140" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG140" t="n">
         <v>0</v>
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28184,13 +28184,13 @@
         </is>
       </c>
       <c r="P141" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q141" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="R141" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="S141" t="n">
         <v>0</v>
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28578,13 +28578,13 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q143" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="R143" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="S143" t="n">
         <v>0</v>
@@ -28722,12 +28722,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28775,13 +28775,13 @@
         </is>
       </c>
       <c r="P144" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q144" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R144" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="S144" t="n">
         <v>0</v>
@@ -28820,10 +28820,10 @@
         <v>0</v>
       </c>
       <c r="AE144" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF144" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG144" t="n">
         <v>0</v>
@@ -28910,7 +28910,7 @@
         <v>0</v>
       </c>
       <c r="BI144" s="3" t="n">
-        <v>46166.83333333334</v>
+        <v>46166.79166666666</v>
       </c>
     </row>
     <row r="145">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Orlando City II</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29328,12 +29328,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Orlando City II</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29515,7 +29515,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29707,12 +29707,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Barcelona</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29760,13 +29760,13 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q149" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="R149" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S149" t="n">
         <v>0</v>
@@ -29895,7 +29895,7 @@
         <v>0</v>
       </c>
       <c r="BI149" s="3" t="n">
-        <v>46166.84027777778</v>
+        <v>46166.83333333334</v>
       </c>
     </row>
     <row r="150">
@@ -29904,12 +29904,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -29919,12 +29919,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Barcelona</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -29957,13 +29957,13 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="Q150" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="R150" t="n">
-        <v>3.42</v>
+        <v>2.65</v>
       </c>
       <c r="S150" t="n">
         <v>0</v>
@@ -30002,10 +30002,10 @@
         <v>0</v>
       </c>
       <c r="AE150" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF150" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG150" t="n">
         <v>0</v>
@@ -30092,7 +30092,7 @@
         <v>0</v>
       </c>
       <c r="BI150" s="3" t="n">
-        <v>46166.85416666666</v>
+        <v>46166.84027777778</v>
       </c>
     </row>
     <row r="151">
@@ -30495,12 +30495,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30548,13 +30548,13 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q153" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R153" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="S153" t="n">
         <v>0</v>
@@ -30593,10 +30593,10 @@
         <v>0</v>
       </c>
       <c r="AE153" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF153" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG153" t="n">
         <v>0</v>
@@ -30683,7 +30683,7 @@
         <v>0</v>
       </c>
       <c r="BI153" s="3" t="n">
-        <v>46166.875</v>
+        <v>46166.85416666666</v>
       </c>
     </row>
     <row r="154">
@@ -30889,12 +30889,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -30942,141 +30942,338 @@
         </is>
       </c>
       <c r="P155" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>0</v>
+      </c>
+      <c r="R155" t="n">
+        <v>0</v>
+      </c>
+      <c r="S155" t="n">
+        <v>0</v>
+      </c>
+      <c r="T155" t="n">
+        <v>0</v>
+      </c>
+      <c r="U155" t="n">
+        <v>0</v>
+      </c>
+      <c r="V155" t="n">
+        <v>0</v>
+      </c>
+      <c r="W155" t="n">
+        <v>0</v>
+      </c>
+      <c r="X155" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y155" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ155" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA155" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB155" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC155" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD155" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE155" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF155" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG155" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH155" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI155" s="3" t="n">
+        <v>46166.875</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Los Angeles FC</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Seattle Sounders</t>
+        </is>
+      </c>
+      <c r="G156" t="n">
+        <v>0</v>
+      </c>
+      <c r="H156" t="n">
+        <v>0</v>
+      </c>
+      <c r="I156" t="n">
+        <v>0</v>
+      </c>
+      <c r="J156" t="n">
+        <v>0</v>
+      </c>
+      <c r="K156" t="n">
+        <v>0</v>
+      </c>
+      <c r="L156" t="n">
+        <v>0</v>
+      </c>
+      <c r="M156" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N156" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P156" t="n">
         <v>2</v>
       </c>
-      <c r="Q155" t="n">
+      <c r="Q156" t="n">
         <v>3.83</v>
       </c>
-      <c r="R155" t="n">
+      <c r="R156" t="n">
         <v>3.72</v>
       </c>
-      <c r="S155" t="n">
-        <v>0</v>
-      </c>
-      <c r="T155" t="n">
-        <v>0</v>
-      </c>
-      <c r="U155" t="n">
-        <v>0</v>
-      </c>
-      <c r="V155" t="n">
-        <v>0</v>
-      </c>
-      <c r="W155" t="n">
-        <v>0</v>
-      </c>
-      <c r="X155" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y155" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE155" t="n">
+      <c r="S156" t="n">
+        <v>0</v>
+      </c>
+      <c r="T156" t="n">
+        <v>0</v>
+      </c>
+      <c r="U156" t="n">
+        <v>0</v>
+      </c>
+      <c r="V156" t="n">
+        <v>0</v>
+      </c>
+      <c r="W156" t="n">
+        <v>0</v>
+      </c>
+      <c r="X156" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y156" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE156" t="n">
         <v>1.62</v>
       </c>
-      <c r="AF155" t="n">
+      <c r="AF156" t="n">
         <v>2.15</v>
       </c>
-      <c r="AG155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY155" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ155" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA155" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB155" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC155" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD155" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE155" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF155" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG155" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH155" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI155" s="3" t="n">
+      <c r="AG156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ156" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA156" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB156" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC156" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD156" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE156" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF156" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG156" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH156" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI156" s="3" t="n">
         <v>46166.91666666666</v>
       </c>
     </row>

--- a/jogos_2026-05-24.xlsx
+++ b/jogos_2026-05-24.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Blacktown City</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sydney Olympic</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>Blacktown City</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>Sydney Olympic</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Meizhou Hakka</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Meizhou Hakka</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Slovan Liberec</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.83</v>
+        <v>2.54</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.75</v>
+        <v>3.42</v>
       </c>
       <c r="R24" t="n">
-        <v>3.8</v>
+        <v>2.59</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sparta Praha</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Slovan Liberec</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Sparta Praha</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>5.14</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AR29" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AS29" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AU29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV29" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AW29" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AX29" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AY29" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BA29" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="BB29" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BC29" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BD29" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE29" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BF29" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.6</v>
+        <v>1.75</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="R30" t="n">
-        <v>2.55</v>
+        <v>4.22</v>
       </c>
       <c r="S30" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AN30" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AS30" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AT30" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AU30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AV30" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BA30" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BC30" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="BD30" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Brann</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>4.92</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6959,10 +6959,10 @@
         <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Brann</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>4.92</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7156,10 +7156,10 @@
         <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="R38" t="n">
-        <v>6.14</v>
+        <v>6</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.63</v>
+        <v>1.28</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.96</v>
+        <v>5.41</v>
       </c>
       <c r="R39" t="n">
-        <v>4.85</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q40" t="n">
-        <v>5.41</v>
+        <v>3.6</v>
       </c>
       <c r="R40" t="n">
-        <v>8.039999999999999</v>
+        <v>2.6</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.42</v>
+        <v>2.95</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.58</v>
+        <v>3.53</v>
       </c>
       <c r="R42" t="n">
-        <v>6</v>
+        <v>2.2</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.95</v>
+        <v>1.44</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.53</v>
+        <v>4.6</v>
       </c>
       <c r="R43" t="n">
-        <v>2.2</v>
+        <v>6.14</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -8923,10 +8923,10 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.3</v>
+        <v>1.93</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.6</v>
+        <v>3.99</v>
       </c>
       <c r="R45" t="n">
-        <v>2.6</v>
+        <v>3.22</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.93</v>
+        <v>1.42</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.99</v>
+        <v>4.58</v>
       </c>
       <c r="R46" t="n">
-        <v>3.22</v>
+        <v>6</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.33</v>
+        <v>1.63</v>
       </c>
       <c r="Q47" t="n">
-        <v>5</v>
+        <v>3.96</v>
       </c>
       <c r="R47" t="n">
-        <v>6</v>
+        <v>4.85</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Makedonija GjP</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.43</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.52</v>
+        <v>2.8</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.6</v>
+        <v>3.81</v>
       </c>
       <c r="R51" t="n">
-        <v>2.94</v>
+        <v>2.53</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Makedonija GjP</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Shkupi</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="Q59" t="n">
-        <v>4.54</v>
+        <v>5.57</v>
       </c>
       <c r="R59" t="n">
-        <v>6.7</v>
+        <v>7.02</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>4.43</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>3.82</v>
+        <v>2.25</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.82</v>
+        <v>3.73</v>
       </c>
       <c r="R62" t="n">
-        <v>2.03</v>
+        <v>3.31</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="Q63" t="n">
-        <v>5.57</v>
+        <v>4.54</v>
       </c>
       <c r="R63" t="n">
-        <v>7.02</v>
+        <v>6.7</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Shkupi</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,22 +13361,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF67" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2.63</v>
+        <v>2.54</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.82</v>
+        <v>3.62</v>
       </c>
       <c r="R68" t="n">
-        <v>2.68</v>
+        <v>2.89</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF68" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF69" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Bokelj</t>
+          <t>Arsenal Tivat</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dečić</t>
+          <t>Mladost DG</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Arsenal Tivat</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mladost DG</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>5.37</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14642,10 +14642,10 @@
         <v>0</v>
       </c>
       <c r="AG72" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH72" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI72" t="n">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>FK Jezero Plav</t>
+          <t>Sutjeska</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Jedinstvo</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Kristiansund</t>
+          <t>FK Jezero Plav</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>5.37</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15233,10 +15233,10 @@
         <v>0</v>
       </c>
       <c r="AG75" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH75" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI75" t="n">
         <v>0</v>
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Sutjeska</t>
+          <t>Bokelj</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Jedinstvo</t>
+          <t>Dečić</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>RSC Anderlecht</t>
+          <t>KAA Gent</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>1.53</v>
+        <v>1.32</v>
       </c>
       <c r="Q78" t="n">
-        <v>4.33</v>
+        <v>5.88</v>
       </c>
       <c r="R78" t="n">
-        <v>6.19</v>
+        <v>8.4</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>TransINVEST Vilnius</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Concepción</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF80" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Sint-Truiden</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>KV Mechelen</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>4.15</v>
+        <v>1.77</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.73</v>
+        <v>4.07</v>
       </c>
       <c r="R81" t="n">
-        <v>1.88</v>
+        <v>4.22</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Concepción</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>1.96</v>
+        <v>4.15</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.81</v>
+        <v>3.73</v>
       </c>
       <c r="R83" t="n">
-        <v>3.73</v>
+        <v>1.88</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF83" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>5.25</v>
+        <v>1.67</v>
       </c>
       <c r="Q85" t="n">
-        <v>4.22</v>
+        <v>4.17</v>
       </c>
       <c r="R85" t="n">
-        <v>1.63</v>
+        <v>4.94</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17197,10 +17197,10 @@
         <v>0</v>
       </c>
       <c r="AE85" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF85" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG85" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>RSC Anderlecht</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="Q86" t="n">
-        <v>4.17</v>
+        <v>4.33</v>
       </c>
       <c r="R86" t="n">
-        <v>4.94</v>
+        <v>6.19</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Sint-Truiden</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>KV Mechelen</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>2.59</v>
+        <v>1.96</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.42</v>
+        <v>3.81</v>
       </c>
       <c r="R89" t="n">
-        <v>2.75</v>
+        <v>3.73</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17985,10 +17985,10 @@
         <v>0</v>
       </c>
       <c r="AE89" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF89" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG89" t="n">
         <v>0</v>
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>3.19</v>
+        <v>2.59</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.19</v>
+        <v>3.42</v>
       </c>
       <c r="R90" t="n">
-        <v>2.41</v>
+        <v>2.75</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>KAA Gent</t>
+          <t>TransINVEST Vilnius</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>5.88</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>3.77</v>
+        <v>3.19</v>
       </c>
       <c r="Q92" t="n">
-        <v>4.17</v>
+        <v>3.19</v>
       </c>
       <c r="R92" t="n">
-        <v>1.86</v>
+        <v>2.41</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>AC Milan</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,133 +20895,133 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>9.199999999999999</v>
+        <v>1.33</v>
       </c>
       <c r="Q104" t="n">
         <v>5.2</v>
       </c>
       <c r="R104" t="n">
+        <v>9</v>
+      </c>
+      <c r="S104" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="T104" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="U104" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="V104" t="n">
         <v>1.33</v>
       </c>
-      <c r="S104" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="T104" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="U104" t="n">
+      <c r="W104" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="X104" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Y104" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Z104" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AA104" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB104" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC104" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD104" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE104" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AF104" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AG104" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AH104" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI104" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AJ104" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK104" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AL104" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AM104" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AN104" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AO104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP104" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AQ104" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR104" t="n">
         <v>1.77</v>
       </c>
-      <c r="V104" t="n">
+      <c r="AS104" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AT104" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AU104" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV104" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AW104" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AX104" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AY104" t="n">
         <v>1.36</v>
       </c>
-      <c r="W104" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="X104" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="Y104" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z104" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AA104" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB104" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC104" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AD104" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AE104" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AF104" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG104" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AH104" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI104" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="AJ104" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK104" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AL104" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AM104" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AN104" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AO104" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP104" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AQ104" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AR104" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AS104" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AT104" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AU104" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV104" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AW104" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AX104" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AY104" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AZ104" t="n">
-        <v>3.7</v>
+        <v>1.2</v>
       </c>
       <c r="BA104" t="n">
-        <v>1.36</v>
+        <v>5.3</v>
       </c>
       <c r="BB104" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="BC104" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="BD104" t="n">
-        <v>4.15</v>
+        <v>4.5</v>
       </c>
       <c r="BE104" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="BF104" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="BG104" t="n">
         <v>0</v>
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Cremonese</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Roma</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,133 +21092,133 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q105" t="n">
-        <v>4.26</v>
+        <v>5.2</v>
       </c>
       <c r="R105" t="n">
-        <v>1.63</v>
+        <v>1.33</v>
       </c>
       <c r="S105" t="n">
-        <v>5.05</v>
+        <v>8.5</v>
       </c>
       <c r="T105" t="n">
-        <v>2.35</v>
+        <v>2.47</v>
       </c>
       <c r="U105" t="n">
-        <v>2.16</v>
+        <v>1.77</v>
       </c>
       <c r="V105" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W105" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="X105" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="Y105" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z105" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AA105" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB105" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC105" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD105" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AE105" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF105" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG105" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AH105" t="n">
         <v>1.33</v>
       </c>
-      <c r="W105" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="X105" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="Y105" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Z105" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AA105" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AB105" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC105" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AD105" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AE105" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AF105" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AG105" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AH105" t="n">
-        <v>1.41</v>
-      </c>
       <c r="AI105" t="n">
-        <v>4.65</v>
+        <v>5.45</v>
       </c>
       <c r="AJ105" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AK105" t="n">
-        <v>1.71</v>
+        <v>2.25</v>
       </c>
       <c r="AL105" t="n">
-        <v>2.04</v>
+        <v>1.58</v>
       </c>
       <c r="AM105" t="n">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="AN105" t="n">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="AO105" t="n">
         <v>0</v>
       </c>
       <c r="AP105" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AQ105" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AR105" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AS105" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AT105" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AU105" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV105" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AW105" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AX105" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AY105" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AZ105" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BA105" t="n">
         <v>1.36</v>
       </c>
-      <c r="AQ105" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AR105" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AS105" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AT105" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AU105" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AV105" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AW105" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AX105" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AY105" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AZ105" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BA105" t="n">
-        <v>1.4</v>
-      </c>
       <c r="BB105" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="BC105" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="BD105" t="n">
-        <v>4.45</v>
+        <v>4.15</v>
       </c>
       <c r="BE105" t="n">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="BF105" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="BG105" t="n">
         <v>0</v>
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Cremonese</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,133 +21486,133 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>1.7</v>
+        <v>5</v>
       </c>
       <c r="Q107" t="n">
-        <v>3.68</v>
+        <v>4.26</v>
       </c>
       <c r="R107" t="n">
-        <v>5.1</v>
+        <v>1.63</v>
       </c>
       <c r="S107" t="n">
-        <v>2.31</v>
+        <v>5.05</v>
       </c>
       <c r="T107" t="n">
-        <v>2.09</v>
+        <v>2.35</v>
       </c>
       <c r="U107" t="n">
-        <v>4.54</v>
+        <v>2.16</v>
       </c>
       <c r="V107" t="n">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="W107" t="n">
-        <v>2.55</v>
+        <v>3.28</v>
       </c>
       <c r="X107" t="n">
-        <v>3.34</v>
+        <v>2.53</v>
       </c>
       <c r="Y107" t="n">
-        <v>1.32</v>
+        <v>1.51</v>
       </c>
       <c r="Z107" t="n">
-        <v>8.6</v>
+        <v>5.8</v>
       </c>
       <c r="AA107" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AB107" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AC107" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD107" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AE107" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF107" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AG107" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AH107" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI107" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AJ107" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK107" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AL107" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AM107" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN107" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AO107" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP107" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AQ107" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AR107" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AS107" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AT107" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AU107" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AV107" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AW107" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AX107" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AY107" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AZ107" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BA107" t="n">
         <v>1.4</v>
       </c>
-      <c r="AD107" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AE107" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AF107" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AG107" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AH107" t="n">
+      <c r="BB107" t="n">
         <v>1.18</v>
       </c>
-      <c r="AI107" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AJ107" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK107" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AL107" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AM107" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN107" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AO107" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP107" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AQ107" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AR107" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AS107" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AT107" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AU107" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV107" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AW107" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AX107" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AY107" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AZ107" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BA107" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BB107" t="n">
-        <v>1.33</v>
-      </c>
       <c r="BC107" t="n">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="BD107" t="n">
-        <v>3.28</v>
+        <v>4.45</v>
       </c>
       <c r="BE107" t="n">
-        <v>1.52</v>
+        <v>1.88</v>
       </c>
       <c r="BF107" t="n">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="BG107" t="n">
         <v>0</v>
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AC Milan</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,133 +21683,133 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="Q108" t="n">
-        <v>5.2</v>
+        <v>3.68</v>
       </c>
       <c r="R108" t="n">
-        <v>9</v>
+        <v>5.1</v>
       </c>
       <c r="S108" t="n">
-        <v>1.77</v>
+        <v>2.31</v>
       </c>
       <c r="T108" t="n">
-        <v>2.35</v>
+        <v>2.09</v>
       </c>
       <c r="U108" t="n">
-        <v>8.1</v>
+        <v>4.54</v>
       </c>
       <c r="V108" t="n">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="W108" t="n">
-        <v>3.25</v>
+        <v>2.55</v>
       </c>
       <c r="X108" t="n">
-        <v>2.59</v>
+        <v>3.34</v>
       </c>
       <c r="Y108" t="n">
-        <v>1.49</v>
+        <v>1.32</v>
       </c>
       <c r="Z108" t="n">
-        <v>6.05</v>
+        <v>8.6</v>
       </c>
       <c r="AA108" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AB108" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AC108" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="AD108" t="n">
-        <v>4</v>
+        <v>2.82</v>
       </c>
       <c r="AE108" t="n">
-        <v>1.79</v>
+        <v>2.39</v>
       </c>
       <c r="AF108" t="n">
-        <v>2.19</v>
+        <v>1.68</v>
       </c>
       <c r="AG108" t="n">
-        <v>2.81</v>
+        <v>4.2</v>
       </c>
       <c r="AH108" t="n">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="AI108" t="n">
-        <v>4.8</v>
+        <v>10.5</v>
       </c>
       <c r="AJ108" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="AK108" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="AL108" t="n">
         <v>1.63</v>
       </c>
       <c r="AM108" t="n">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="AN108" t="n">
-        <v>3.44</v>
+        <v>2.17</v>
       </c>
       <c r="AO108" t="n">
         <v>0</v>
       </c>
       <c r="AP108" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AQ108" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AR108" t="n">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="AS108" t="n">
-        <v>2.18</v>
+        <v>2.33</v>
       </c>
       <c r="AT108" t="n">
-        <v>2.85</v>
+        <v>3.05</v>
       </c>
       <c r="AU108" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AV108" t="n">
-        <v>2.48</v>
+        <v>2.35</v>
       </c>
       <c r="AW108" t="n">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="AX108" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="AY108" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AZ108" t="n">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="BA108" t="n">
-        <v>5.3</v>
+        <v>3.65</v>
       </c>
       <c r="BB108" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="BC108" t="n">
-        <v>1.97</v>
+        <v>2.5</v>
       </c>
       <c r="BD108" t="n">
-        <v>4.5</v>
+        <v>3.28</v>
       </c>
       <c r="BE108" t="n">
-        <v>1.86</v>
+        <v>1.52</v>
       </c>
       <c r="BF108" t="n">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="BG108" t="n">
         <v>0</v>
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Club Atlético Güemes</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Patronato</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Quilmes</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22868,10 +22868,10 @@
         <v>2.29</v>
       </c>
       <c r="Q114" t="n">
-        <v>2.69</v>
+        <v>2.76</v>
       </c>
       <c r="R114" t="n">
-        <v>3.43</v>
+        <v>3.61</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="Q115" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="R115" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23211,22 +23211,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Q116" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R116" t="n">
-        <v>7.25</v>
+        <v>0</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Club Atlético Güemes</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Quilmes</t>
+          <t>Patronato</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="Q117" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="R117" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Q119" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R119" t="n">
-        <v>0</v>
+        <v>7.25</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24047,13 +24047,13 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q120" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="R120" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -24092,10 +24092,10 @@
         <v>0</v>
       </c>
       <c r="AE120" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF120" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG120" t="n">
         <v>0</v>
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Atlético GO</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>1.77</v>
+        <v>2.8</v>
       </c>
       <c r="Q121" t="n">
-        <v>3.32</v>
+        <v>3.27</v>
       </c>
       <c r="R121" t="n">
-        <v>4.83</v>
+        <v>2.64</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24289,10 +24289,10 @@
         <v>0</v>
       </c>
       <c r="AE121" t="n">
-        <v>2.37</v>
+        <v>2.05</v>
       </c>
       <c r="AF121" t="n">
-        <v>1.51</v>
+        <v>1.8</v>
       </c>
       <c r="AG121" t="n">
         <v>0</v>
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Atlético GO</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q122" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R122" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24486,10 +24486,10 @@
         <v>0</v>
       </c>
       <c r="AE122" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AF122" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG122" t="n">
         <v>0</v>
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Portland Timbers II</t>
+          <t>Chicago Fire II</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Houston Dynamo FC II</t>
+          <t>Huntsville City</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Gimnasia y Tiro</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Gimnasia Jujuy</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q129" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R129" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Gimnasia y Tiro</t>
+          <t>Portland Timbers II</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Gimnasia Jujuy</t>
+          <t>Houston Dynamo FC II</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26017,13 +26017,13 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q130" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R130" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="S130" t="n">
         <v>0</v>
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Chicago Fire II</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Huntsville City</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26608,13 +26608,13 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Q133" t="n">
-        <v>4.84</v>
+        <v>0</v>
       </c>
       <c r="R133" t="n">
-        <v>6.19</v>
+        <v>0</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -26659,10 +26659,10 @@
         <v>0</v>
       </c>
       <c r="AG133" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH133" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AI133" t="n">
         <v>0</v>
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q134" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R134" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -26954,7 +26954,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -26964,12 +26964,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Cavalry FC</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Figueirense</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27151,7 +27151,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -27161,12 +27161,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q136" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="R136" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27348,7 +27348,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -27358,12 +27358,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Figueirense</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27396,13 +27396,13 @@
         </is>
       </c>
       <c r="P137" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Q137" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="R137" t="n">
-        <v>0</v>
+        <v>6.19</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>
@@ -27447,10 +27447,10 @@
         <v>0</v>
       </c>
       <c r="AG137" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH137" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI137" t="n">
         <v>0</v>
@@ -27742,7 +27742,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -27752,12 +27752,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -27790,13 +27790,13 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="Q139" t="n">
-        <v>3.38</v>
+        <v>3.32</v>
       </c>
       <c r="R139" t="n">
-        <v>4.32</v>
+        <v>3.49</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -27835,10 +27835,10 @@
         <v>0</v>
       </c>
       <c r="AE139" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF139" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG139" t="n">
         <v>0</v>
@@ -27939,7 +27939,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -27949,12 +27949,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -27987,13 +27987,13 @@
         </is>
       </c>
       <c r="P140" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="Q140" t="n">
-        <v>3.32</v>
+        <v>3.38</v>
       </c>
       <c r="R140" t="n">
-        <v>3.49</v>
+        <v>4.32</v>
       </c>
       <c r="S140" t="n">
         <v>0</v>
@@ -28032,10 +28032,10 @@
         <v>0</v>
       </c>
       <c r="AE140" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF140" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG140" t="n">
         <v>0</v>
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -28146,12 +28146,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Atlanta</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -28184,13 +28184,13 @@
         </is>
       </c>
       <c r="P141" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Q141" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="R141" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="S141" t="n">
         <v>0</v>
@@ -28333,7 +28333,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -28343,12 +28343,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Atlanta</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -28381,13 +28381,13 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q142" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="R142" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="S142" t="n">
         <v>0</v>
@@ -28530,7 +28530,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -28540,12 +28540,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Goiás</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -28578,13 +28578,13 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q143" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R143" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="S143" t="n">
         <v>0</v>
@@ -28623,10 +28623,10 @@
         <v>0</v>
       </c>
       <c r="AE143" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF143" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG143" t="n">
         <v>0</v>
@@ -28727,7 +28727,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -28737,12 +28737,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Goiás</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -28775,13 +28775,13 @@
         </is>
       </c>
       <c r="P144" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q144" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="R144" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="S144" t="n">
         <v>0</v>
@@ -28820,10 +28820,10 @@
         <v>0</v>
       </c>
       <c r="AE144" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AF144" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG144" t="n">
         <v>0</v>
@@ -28924,7 +28924,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -28934,12 +28934,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>New York RB II</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Connecticut United</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29121,7 +29121,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -29131,12 +29131,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Real Monarchs</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29169,13 +29169,13 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Q146" t="n">
-        <v>5.24</v>
+        <v>0</v>
       </c>
       <c r="R146" t="n">
-        <v>7.08</v>
+        <v>0</v>
       </c>
       <c r="S146" t="n">
         <v>0</v>
@@ -29220,10 +29220,10 @@
         <v>0</v>
       </c>
       <c r="AG146" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH146" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI146" t="n">
         <v>0</v>
@@ -29515,7 +29515,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -29525,12 +29525,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Real Monarchs</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29563,13 +29563,13 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Q148" t="n">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="R148" t="n">
-        <v>0</v>
+        <v>7.08</v>
       </c>
       <c r="S148" t="n">
         <v>0</v>
@@ -29614,10 +29614,10 @@
         <v>0</v>
       </c>
       <c r="AG148" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH148" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI148" t="n">
         <v>0</v>
@@ -29712,7 +29712,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -29722,12 +29722,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>New York RB II</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Connecticut United</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -30106,7 +30106,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -30116,12 +30116,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Aurora</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -30154,13 +30154,13 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q151" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R151" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="S151" t="n">
         <v>0</v>
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -30351,14 +30351,14 @@
         </is>
       </c>
       <c r="P152" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="Q152" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="R152" t="n">
         <v>3.42</v>
       </c>
-      <c r="R152" t="n">
-        <v>3.76</v>
-      </c>
       <c r="S152" t="n">
         <v>0</v>
       </c>
@@ -30396,10 +30396,10 @@
         <v>0</v>
       </c>
       <c r="AE152" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF152" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG152" t="n">
         <v>0</v>
@@ -30500,7 +30500,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -30510,12 +30510,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30548,13 +30548,13 @@
         </is>
       </c>
       <c r="P153" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q153" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="R153" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="S153" t="n">
         <v>0</v>
@@ -30593,10 +30593,10 @@
         <v>0</v>
       </c>
       <c r="AE153" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF153" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG153" t="n">
         <v>0</v>
@@ -30697,7 +30697,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -30707,12 +30707,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>San Luis</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Toronto II</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30894,7 +30894,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -30904,12 +30904,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>San Luis</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Toronto II</t>
         </is>
       </c>
       <c r="G155" t="n">

--- a/jogos_2026-05-24.xlsx
+++ b/jogos_2026-05-24.xlsx
@@ -763,12 +763,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>APIA Leichhardt Tigers</t>
+          <t>Wollongong Wolves</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Marconi Stallions</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>APIA Leichhardt Tigers</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Western Sydney W. II</t>
+          <t>Marconi Stallions</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Wollongong Wolves</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Western Sydney W. II</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Daegu</t>
+          <t>Seoul E-Land</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.29</v>
+        <v>1.97</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.95</v>
+        <v>3.18</v>
       </c>
       <c r="R9" t="n">
-        <v>8.199999999999999</v>
+        <v>3.61</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Seoul E-Land</t>
+          <t>Daegu</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.97</v>
+        <v>1.29</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.18</v>
+        <v>4.95</v>
       </c>
       <c r="R10" t="n">
-        <v>3.61</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Binh Duong</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Song Lam Nghe An</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Hà Nội II</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Công An Nhân Dân</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Hà Nội II</t>
+          <t>Binh Duong</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Công An Nhân Dân</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>4.93</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.83</v>
+        <v>2.54</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.75</v>
+        <v>3.42</v>
       </c>
       <c r="R21" t="n">
-        <v>3.8</v>
+        <v>2.59</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Shanghai Shenhua</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sichuan Jiuniu</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Slavia Praha</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Viktoria Plzeň</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>5.14</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Slavia Praha</t>
+          <t>Shanghai Shenhua</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Viktoria Plzeň</t>
+          <t>Sichuan Jiuniu</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Parma</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AL29" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AN29" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AS29" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AT29" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AU29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AV29" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="BA29" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="BC29" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="BD29" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Parma</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.75</v>
+        <v>2.6</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="R30" t="n">
-        <v>4.22</v>
+        <v>2.55</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AR30" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AS30" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AY30" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BA30" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="BB30" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BF30" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Śląsk Wrocław</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Ruch Chorzów</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.33</v>
+        <v>3</v>
       </c>
       <c r="Q38" t="n">
-        <v>5</v>
+        <v>3.66</v>
       </c>
       <c r="R38" t="n">
-        <v>6</v>
+        <v>2.13</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -7938,10 +7938,10 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG38" t="n">
         <v>0</v>
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Malmö FF</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.28</v>
+        <v>1.63</v>
       </c>
       <c r="Q39" t="n">
-        <v>5.41</v>
+        <v>3.96</v>
       </c>
       <c r="R39" t="n">
-        <v>8.039999999999999</v>
+        <v>4.85</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Odra Opole</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Polonia Bytom</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.3</v>
+        <v>2.95</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.6</v>
+        <v>3.53</v>
       </c>
       <c r="R40" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Miedź Legnica</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.69</v>
+        <v>1.44</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="R41" t="n">
-        <v>4.57</v>
+        <v>6.14</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Odra Opole</t>
+          <t>Tychy 71</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.95</v>
+        <v>1.93</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.53</v>
+        <v>3.99</v>
       </c>
       <c r="R42" t="n">
-        <v>2.2</v>
+        <v>3.22</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="Q43" t="n">
-        <v>4.6</v>
+        <v>4.58</v>
       </c>
       <c r="R43" t="n">
-        <v>6.14</v>
+        <v>6</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Miedź Legnica</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ruch Chorzów</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>3</v>
+        <v>1.69</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.66</v>
+        <v>3.8</v>
       </c>
       <c r="R44" t="n">
-        <v>2.13</v>
+        <v>4.57</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Tychy 71</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Polonia Bytom</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.93</v>
+        <v>2.3</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.99</v>
+        <v>3.6</v>
       </c>
       <c r="R45" t="n">
-        <v>3.22</v>
+        <v>2.6</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Śląsk Wrocław</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,10 +9469,10 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.58</v>
+        <v>5</v>
       </c>
       <c r="R46" t="n">
         <v>6</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Malmö FF</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.63</v>
+        <v>1.28</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.96</v>
+        <v>5.41</v>
       </c>
       <c r="R47" t="n">
-        <v>4.85</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
  